--- a/Raw Data/single force (10 trials)(perturbed)/Validation(1.5)(3tendon).xlsx
+++ b/Raw Data/single force (10 trials)(perturbed)/Validation(1.5)(3tendon).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/Raw Data/single force (10 trials)(perturbed)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4327" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E053C78-8FF1-4563-A9E8-EE554E4686D8}"/>
+  <xr:revisionPtr revIDLastSave="4350" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82CA90CF-99A7-466F-B68F-196908267B01}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="42">
   <si>
     <t>Fx (N)</t>
   </si>
@@ -517,6 +517,9 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -527,9 +530,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1894,11 +1894,11 @@
       </c>
       <c r="R1" s="27"/>
       <c r="S1" s="27"/>
-      <c r="T1" s="34" t="s">
+      <c r="T1" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
       <c r="W1" s="28"/>
       <c r="X1" s="28"/>
       <c r="Y1" s="28"/>
@@ -2934,11 +2934,11 @@
       </c>
       <c r="R1" s="27"/>
       <c r="S1" s="27"/>
-      <c r="T1" s="34" t="s">
+      <c r="T1" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
       <c r="W1" s="28"/>
       <c r="X1" s="28"/>
       <c r="Y1" s="28"/>
@@ -3907,11 +3907,11 @@
       </c>
     </row>
     <row r="14" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="31"/>
-      <c r="C14" s="32"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="33"/>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15">
@@ -5391,11 +5391,11 @@
       </c>
       <c r="R1" s="27"/>
       <c r="S1" s="27"/>
-      <c r="T1" s="34" t="s">
+      <c r="T1" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
       <c r="W1" s="28"/>
       <c r="X1" s="28"/>
       <c r="Y1" s="28"/>
@@ -6364,11 +6364,11 @@
       </c>
     </row>
     <row r="14" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="31"/>
-      <c r="C14" s="32"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="33"/>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15">
@@ -7839,11 +7839,11 @@
       </c>
       <c r="R1" s="27"/>
       <c r="S1" s="27"/>
-      <c r="T1" s="34" t="s">
+      <c r="T1" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
       <c r="W1" s="28"/>
       <c r="X1" s="28"/>
       <c r="Y1" s="28"/>
@@ -8812,11 +8812,11 @@
       </c>
     </row>
     <row r="14" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="31"/>
-      <c r="C14" s="32"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="33"/>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15">
@@ -10241,22 +10241,22 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="32"/>
-      <c r="H1" s="33" t="s">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="33"/>
+      <c r="H1" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="33"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -16595,7 +16595,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="49" spans="26:37" x14ac:dyDescent="0.25">
+    <row r="49" spans="26:48" x14ac:dyDescent="0.25">
       <c r="Z49" t="s">
         <v>29</v>
       </c>
@@ -16629,8 +16629,32 @@
       <c r="AJ49" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="50" spans="26:37" x14ac:dyDescent="0.25">
+      <c r="AO49" t="s">
+        <v>29</v>
+      </c>
+      <c r="AP49">
+        <v>0.4</v>
+      </c>
+      <c r="AQ49">
+        <v>0.06</v>
+      </c>
+      <c r="AR49">
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AS49">
+        <v>0</v>
+      </c>
+      <c r="AT49">
+        <v>0</v>
+      </c>
+      <c r="AU49">
+        <v>0</v>
+      </c>
+      <c r="AV49" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="50" spans="26:48" x14ac:dyDescent="0.25">
       <c r="Z50" t="s">
         <v>29</v>
       </c>
@@ -16664,8 +16688,29 @@
       <c r="AJ50" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="51" spans="26:37" x14ac:dyDescent="0.25">
+      <c r="AP50">
+        <v>0.8</v>
+      </c>
+      <c r="AQ50">
+        <v>0.06</v>
+      </c>
+      <c r="AR50">
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AS50">
+        <v>0</v>
+      </c>
+      <c r="AT50">
+        <v>0</v>
+      </c>
+      <c r="AU50">
+        <v>0</v>
+      </c>
+      <c r="AV50" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51" spans="26:48" x14ac:dyDescent="0.25">
       <c r="Z51" t="s">
         <v>29</v>
       </c>
@@ -16699,8 +16744,29 @@
       <c r="AJ51" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="52" spans="26:37" x14ac:dyDescent="0.25">
+      <c r="AP51">
+        <v>0.3</v>
+      </c>
+      <c r="AQ51">
+        <v>0.08</v>
+      </c>
+      <c r="AR51">
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AS51">
+        <v>0</v>
+      </c>
+      <c r="AT51">
+        <v>0</v>
+      </c>
+      <c r="AU51">
+        <v>0</v>
+      </c>
+      <c r="AV51" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="52" spans="26:48" x14ac:dyDescent="0.25">
       <c r="Z52" t="s">
         <v>29</v>
       </c>
@@ -16734,8 +16800,26 @@
       <c r="AJ52" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="53" spans="26:37" x14ac:dyDescent="0.25">
+      <c r="AP52">
+        <v>0.5</v>
+      </c>
+      <c r="AQ52">
+        <v>0.1</v>
+      </c>
+      <c r="AR52">
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AS52">
+        <v>0</v>
+      </c>
+      <c r="AT52">
+        <v>0</v>
+      </c>
+      <c r="AU52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="26:48" x14ac:dyDescent="0.25">
       <c r="Z53" t="s">
         <v>29</v>
       </c>
@@ -16769,8 +16853,29 @@
       <c r="AJ53" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="54" spans="26:37" x14ac:dyDescent="0.25">
+      <c r="AP53">
+        <v>0.7</v>
+      </c>
+      <c r="AQ53">
+        <v>0.1</v>
+      </c>
+      <c r="AR53">
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AS53">
+        <v>0</v>
+      </c>
+      <c r="AT53">
+        <v>0</v>
+      </c>
+      <c r="AU53">
+        <v>0</v>
+      </c>
+      <c r="AV53" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="54" spans="26:48" x14ac:dyDescent="0.25">
       <c r="Z54" t="s">
         <v>29</v>
       </c>
@@ -16804,8 +16909,29 @@
       <c r="AJ54" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="55" spans="26:37" x14ac:dyDescent="0.25">
+      <c r="AP54">
+        <v>0.4</v>
+      </c>
+      <c r="AQ54">
+        <v>0.16</v>
+      </c>
+      <c r="AR54">
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AS54">
+        <v>0</v>
+      </c>
+      <c r="AT54">
+        <v>0</v>
+      </c>
+      <c r="AU54">
+        <v>0</v>
+      </c>
+      <c r="AV54" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55" spans="26:48" x14ac:dyDescent="0.25">
       <c r="Z55" t="s">
         <v>29</v>
       </c>
@@ -16839,8 +16965,29 @@
       <c r="AJ55" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="56" spans="26:37" x14ac:dyDescent="0.25">
+      <c r="AP55">
+        <v>0.6</v>
+      </c>
+      <c r="AQ55">
+        <v>0.16</v>
+      </c>
+      <c r="AR55">
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AS55">
+        <v>0</v>
+      </c>
+      <c r="AT55">
+        <v>0</v>
+      </c>
+      <c r="AU55">
+        <v>0</v>
+      </c>
+      <c r="AV55" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="56" spans="26:48" x14ac:dyDescent="0.25">
       <c r="Z56" t="s">
         <v>29</v>
       </c>
@@ -16876,6 +17023,73 @@
       </c>
       <c r="AK56" t="s">
         <v>38</v>
+      </c>
+      <c r="AP56">
+        <v>0.8</v>
+      </c>
+      <c r="AQ56">
+        <v>0.18</v>
+      </c>
+      <c r="AR56">
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AS56">
+        <v>0</v>
+      </c>
+      <c r="AT56">
+        <v>0</v>
+      </c>
+      <c r="AU56">
+        <v>0</v>
+      </c>
+      <c r="AV56" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57" spans="26:48" x14ac:dyDescent="0.25">
+      <c r="AP57">
+        <v>0.3</v>
+      </c>
+      <c r="AQ57">
+        <v>0.2</v>
+      </c>
+      <c r="AR57">
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AS57">
+        <v>0</v>
+      </c>
+      <c r="AT57">
+        <v>0</v>
+      </c>
+      <c r="AU57">
+        <v>0</v>
+      </c>
+      <c r="AV57" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="58" spans="26:48" x14ac:dyDescent="0.25">
+      <c r="AP58">
+        <v>0.7</v>
+      </c>
+      <c r="AQ58">
+        <v>0.2</v>
+      </c>
+      <c r="AR58">
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AS58">
+        <v>0</v>
+      </c>
+      <c r="AT58">
+        <v>0</v>
+      </c>
+      <c r="AU58">
+        <v>0</v>
+      </c>
+      <c r="AV58" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -17398,16 +17612,16 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Raw Data/single force (10 trials)(perturbed)/Validation(1.5)(3tendon).xlsx
+++ b/Raw Data/single force (10 trials)(perturbed)/Validation(1.5)(3tendon).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/Raw Data/single force (10 trials)(perturbed)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4350" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82CA90CF-99A7-466F-B68F-196908267B01}"/>
+  <xr:revisionPtr revIDLastSave="4394" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6F38BCE-4A35-4BEE-B254-BF9BA35E0E1B}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="43">
   <si>
     <t>Fx (N)</t>
   </si>
@@ -186,10 +186,13 @@
     <t>SoRoSim get_distal_value (lambda = 0.5)</t>
   </si>
   <si>
-    <t>SoRoSim get_distal_value (lambda = 1)</t>
+    <t>ABS Distal Errors</t>
   </si>
   <si>
-    <t>ABS Distal Errors</t>
+    <t>3 Perturbations</t>
+  </si>
+  <si>
+    <t>3 Perturbations (relative only)</t>
   </si>
 </sst>
 </file>
@@ -456,7 +459,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -527,6 +530,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1895,7 +1901,7 @@
       <c r="R1" s="27"/>
       <c r="S1" s="27"/>
       <c r="T1" s="30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U1" s="30"/>
       <c r="V1" s="30"/>
@@ -2935,7 +2941,7 @@
       <c r="R1" s="27"/>
       <c r="S1" s="27"/>
       <c r="T1" s="30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U1" s="30"/>
       <c r="V1" s="30"/>
@@ -3066,40 +3072,40 @@
         <v>0.37637501955032299</v>
       </c>
       <c r="M3" s="5">
-        <v>0.32015596989685213</v>
+        <v>0.41842605547502415</v>
       </c>
       <c r="N3" s="5">
-        <v>7.4349412889797087E-2</v>
+        <v>7.2239826660410636E-2</v>
       </c>
       <c r="O3" s="5">
-        <v>1.5815741073832734</v>
+        <v>1.5755253492704424</v>
       </c>
       <c r="P3" s="11">
-        <v>8.0772011529654023E-7</v>
+        <v>2.310517408478807E-4</v>
       </c>
       <c r="Q3" s="5">
         <f>M3-A3</f>
-        <v>-7.9844030103147889E-2</v>
+        <v>1.8426055475024128E-2</v>
       </c>
       <c r="R3" s="5">
         <f>N3-B3</f>
-        <v>1.4349412889797089E-2</v>
+        <v>1.2239826660410638E-2</v>
       </c>
       <c r="S3" s="5">
         <f>O3-C3</f>
-        <v>1.0777780588376862E-2</v>
+        <v>4.7290224755458521E-3</v>
       </c>
       <c r="T3" s="5">
         <f>ABS(Q3)</f>
-        <v>7.9844030103147889E-2</v>
+        <v>1.8426055475024128E-2</v>
       </c>
       <c r="U3" s="5">
         <f t="shared" ref="U3:V12" si="0">ABS(R3)</f>
-        <v>1.4349412889797089E-2</v>
+        <v>1.2239826660410638E-2</v>
       </c>
       <c r="V3" s="5">
         <f t="shared" si="0"/>
-        <v>1.0777780588376862E-2</v>
+        <v>4.7290224755458521E-3</v>
       </c>
       <c r="W3" s="1" t="s">
         <v>23</v>
@@ -3161,52 +3167,52 @@
         <v>0.81632339954376198</v>
       </c>
       <c r="M4" s="8">
-        <v>0.6982155667678972</v>
+        <v>0.75391514132687054</v>
       </c>
       <c r="N4" s="8">
-        <v>7.3979062385175223E-2</v>
+        <v>7.3114233075238164E-2</v>
       </c>
       <c r="O4" s="8">
-        <v>1.5907214026383494</v>
+        <v>1.5947576526931535</v>
       </c>
       <c r="P4" s="12">
-        <v>1.9682557604891809E-6</v>
+        <v>6.0886896719607815E-4</v>
       </c>
       <c r="Q4" s="5">
         <f t="shared" ref="Q4:Q12" si="1">M4-A4</f>
-        <v>-0.10178443323210284</v>
+        <v>-4.6084858673129503E-2</v>
       </c>
       <c r="R4" s="5">
         <f t="shared" ref="R4:R12" si="2">N4-B4</f>
-        <v>1.3979062385175225E-2</v>
+        <v>1.3114233075238166E-2</v>
       </c>
       <c r="S4" s="5">
         <f t="shared" ref="S4:S12" si="3">O4-C4</f>
-        <v>1.9925075843452822E-2</v>
+        <v>2.3961325898256947E-2</v>
       </c>
       <c r="T4" s="5">
         <f t="shared" ref="T4:T12" si="4">ABS(Q4)</f>
-        <v>0.10178443323210284</v>
+        <v>4.6084858673129503E-2</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" si="0"/>
-        <v>1.3979062385175225E-2</v>
+        <v>1.3114233075238166E-2</v>
       </c>
       <c r="V4" s="5">
         <f t="shared" si="0"/>
-        <v>1.9925075843452822E-2</v>
+        <v>2.3961325898256947E-2</v>
       </c>
       <c r="W4" s="6" cm="1">
         <f t="array" ref="W4">AVERAGE(ABS(Q3:Q12))</f>
-        <v>0.19289272277733249</v>
+        <v>4.5169067287390799E-2</v>
       </c>
       <c r="X4" s="6" cm="1">
         <f t="array" ref="X4">AVERAGE(ABS(R3:R12))</f>
-        <v>4.3909568893726339E-2</v>
+        <v>1.592443351299563E-2</v>
       </c>
       <c r="Y4" s="6" cm="1">
         <f t="array" ref="Y4">AVERAGE(ABS(S3:S12))</f>
-        <v>1.7218481597561008E-2</v>
+        <v>2.4517618809561759E-2</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
@@ -3259,40 +3265,40 @@
         <v>0.24872186779975899</v>
       </c>
       <c r="M5" s="5">
-        <v>0.40706031351242317</v>
+        <v>0.29191363684574867</v>
       </c>
       <c r="N5" s="5">
-        <v>5.2825521084303918E-2</v>
+        <v>8.7335290853829614E-2</v>
       </c>
       <c r="O5" s="5">
-        <v>1.5833216442223561</v>
+        <v>1.5874002175974913</v>
       </c>
       <c r="P5" s="11">
-        <v>1.1801999343493295E-7</v>
+        <v>4.9943127456156075E-5</v>
       </c>
       <c r="Q5" s="5">
         <f t="shared" si="1"/>
-        <v>0.10706031351242318</v>
+        <v>-8.0863631542513192E-3</v>
       </c>
       <c r="R5" s="5">
         <f t="shared" si="2"/>
-        <v>-2.7174478915696083E-2</v>
+        <v>7.3352908538296124E-3</v>
       </c>
       <c r="S5" s="5">
         <f t="shared" si="3"/>
-        <v>1.2525317427459548E-2</v>
+        <v>1.6603890802594723E-2</v>
       </c>
       <c r="T5" s="5">
         <f t="shared" si="4"/>
-        <v>0.10706031351242318</v>
+        <v>8.0863631542513192E-3</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="0"/>
-        <v>2.7174478915696083E-2</v>
+        <v>7.3352908538296124E-3</v>
       </c>
       <c r="V5" s="5">
         <f t="shared" si="0"/>
-        <v>1.2525317427459548E-2</v>
+        <v>1.6603890802594723E-2</v>
       </c>
       <c r="W5" s="24"/>
       <c r="X5" s="24"/>
@@ -3348,40 +3354,40 @@
         <v>0.46851912140846302</v>
       </c>
       <c r="M6" s="5">
-        <v>0.47779040349859048</v>
+        <v>0.50454258482216741</v>
       </c>
       <c r="N6" s="5">
-        <v>0.11198161769074509</v>
+        <v>0.10805125225655324</v>
       </c>
       <c r="O6" s="5">
-        <v>1.5823239796913706</v>
+        <v>1.5698912177279192</v>
       </c>
       <c r="P6" s="11">
-        <v>3.9705271593139793E-7</v>
+        <v>1.2594866902726018E-4</v>
       </c>
       <c r="Q6" s="5">
         <f t="shared" si="1"/>
-        <v>-2.2209596501409523E-2</v>
+        <v>4.5425848221674059E-3</v>
       </c>
       <c r="R6" s="5">
         <f t="shared" si="2"/>
-        <v>1.1981617690745086E-2</v>
+        <v>8.0512522565532318E-3</v>
       </c>
       <c r="S6" s="5">
         <f t="shared" si="3"/>
-        <v>1.1527652896474061E-2</v>
+        <v>-9.0510906697738314E-4</v>
       </c>
       <c r="T6" s="5">
         <f t="shared" si="4"/>
-        <v>2.2209596501409523E-2</v>
+        <v>4.5425848221674059E-3</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="0"/>
-        <v>1.1981617690745086E-2</v>
+        <v>8.0512522565532318E-3</v>
       </c>
       <c r="V6" s="5">
         <f t="shared" si="0"/>
-        <v>1.1527652896474061E-2</v>
+        <v>9.0510906697738314E-4</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
@@ -3434,40 +3440,40 @@
         <v>0.62586665153503396</v>
       </c>
       <c r="M7" s="5">
-        <v>0.68224677016028745</v>
+        <v>0.74900663153694746</v>
       </c>
       <c r="N7" s="5">
-        <v>0.11043632280109458</v>
+        <v>0.10419114600637572</v>
       </c>
       <c r="O7" s="5">
-        <v>1.589952405356523</v>
+        <v>1.5883946707431085</v>
       </c>
       <c r="P7" s="11">
-        <v>8.5486519650530557E-7</v>
+        <v>2.2753188201586066E-4</v>
       </c>
       <c r="Q7" s="5">
         <f t="shared" si="1"/>
-        <v>-1.7753229839712503E-2</v>
+        <v>4.9006631536947509E-2</v>
       </c>
       <c r="R7" s="5">
         <f t="shared" si="2"/>
-        <v>1.0436322801094577E-2</v>
+        <v>4.1911460063757122E-3</v>
       </c>
       <c r="S7" s="5">
         <f t="shared" si="3"/>
-        <v>1.9156078561626488E-2</v>
+        <v>1.7598343948211914E-2</v>
       </c>
       <c r="T7" s="5">
         <f t="shared" si="4"/>
-        <v>1.7753229839712503E-2</v>
+        <v>4.9006631536947509E-2</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="0"/>
-        <v>1.0436322801094577E-2</v>
+        <v>4.1911460063757122E-3</v>
       </c>
       <c r="V7" s="5">
         <f t="shared" si="0"/>
-        <v>1.9156078561626488E-2</v>
+        <v>1.7598343948211914E-2</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
@@ -3520,40 +3526,40 @@
         <v>0.316497713327408</v>
       </c>
       <c r="M8" s="5">
-        <v>0.94485419717330477</v>
+        <v>0.34959328798688843</v>
       </c>
       <c r="N8" s="5">
-        <v>6.7086281025113187E-2</v>
+        <v>0.15969011930872445</v>
       </c>
       <c r="O8" s="5">
-        <v>1.586184563844633</v>
+        <v>1.5457720217980624</v>
       </c>
       <c r="P8" s="11">
-        <v>7.7270993517013119E-7</v>
+        <v>5.4004468020721439E-4</v>
       </c>
       <c r="Q8" s="5">
         <f t="shared" si="1"/>
-        <v>0.54485419717330474</v>
+        <v>-5.0406712013111588E-2</v>
       </c>
       <c r="R8" s="5">
         <f t="shared" si="2"/>
-        <v>-9.2913718974886816E-2</v>
+        <v>-3.0988069127554918E-4</v>
       </c>
       <c r="S8" s="5">
         <f t="shared" si="3"/>
-        <v>1.5388237049736464E-2</v>
+        <v>-2.5024304996834168E-2</v>
       </c>
       <c r="T8" s="5">
         <f t="shared" si="4"/>
-        <v>0.54485419717330474</v>
+        <v>5.0406712013111588E-2</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="0"/>
-        <v>9.2913718974886816E-2</v>
+        <v>3.0988069127554918E-4</v>
       </c>
       <c r="V8" s="5">
         <f t="shared" si="0"/>
-        <v>1.5388237049736464E-2</v>
+        <v>2.5024304996834168E-2</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
@@ -3606,40 +3612,40 @@
         <v>0.39143002033233598</v>
       </c>
       <c r="M9" s="5">
-        <v>0.97582032599681501</v>
+        <v>0.71265372507349656</v>
       </c>
       <c r="N9" s="5">
-        <v>0.10408582299286044</v>
+        <v>0.13362845348804642</v>
       </c>
       <c r="O9" s="5">
-        <v>1.5851030740995868</v>
+        <v>1.564418464218599</v>
       </c>
       <c r="P9" s="11">
-        <v>1.1445244169616772E-6</v>
+        <v>3.1582003402976015E-4</v>
       </c>
       <c r="Q9" s="5">
         <f t="shared" si="1"/>
-        <v>0.37582032599681503</v>
+        <v>0.11265372507349658</v>
       </c>
       <c r="R9" s="5">
         <f t="shared" si="2"/>
-        <v>-5.5914177007139562E-2</v>
+        <v>-2.6371546511953586E-2</v>
       </c>
       <c r="S9" s="5">
         <f t="shared" si="3"/>
-        <v>1.4306747304690282E-2</v>
+        <v>-6.3778625762975771E-3</v>
       </c>
       <c r="T9" s="5">
         <f t="shared" si="4"/>
-        <v>0.37582032599681503</v>
+        <v>0.11265372507349658</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="0"/>
-        <v>5.5914177007139562E-2</v>
+        <v>2.6371546511953586E-2</v>
       </c>
       <c r="V9" s="5">
         <f t="shared" si="0"/>
-        <v>1.4306747304690282E-2</v>
+        <v>6.3778625762975771E-3</v>
       </c>
       <c r="W9" s="7"/>
       <c r="X9" s="7"/>
@@ -3695,40 +3701,40 @@
         <v>0.13168570399284399</v>
       </c>
       <c r="M10" s="5">
-        <v>0.9999999999999778</v>
+        <v>0.8038340682610956</v>
       </c>
       <c r="N10" s="5">
-        <v>0.13086426327276435</v>
+        <v>0.14965332296161285</v>
       </c>
       <c r="O10" s="5">
-        <v>1.6032375191745383</v>
+        <v>1.6227511680571338</v>
       </c>
       <c r="P10" s="11">
-        <v>4.7553642808940994E-6</v>
+        <v>3.3327361829210467E-4</v>
       </c>
       <c r="Q10" s="5">
         <f t="shared" si="1"/>
-        <v>0.19999999999997775</v>
+        <v>3.8340682610955579E-3</v>
       </c>
       <c r="R10" s="5">
         <f t="shared" si="2"/>
-        <v>-4.9135736727235646E-2</v>
+        <v>-3.0346677038387143E-2</v>
       </c>
       <c r="S10" s="5">
         <f t="shared" si="3"/>
-        <v>3.2441192379641715E-2</v>
+        <v>5.1954841262237261E-2</v>
       </c>
       <c r="T10" s="5">
         <f t="shared" si="4"/>
-        <v>0.19999999999997775</v>
+        <v>3.8340682610955579E-3</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="0"/>
-        <v>4.9135736727235646E-2</v>
+        <v>3.0346677038387143E-2</v>
       </c>
       <c r="V10" s="5">
         <f t="shared" si="0"/>
-        <v>3.2441192379641715E-2</v>
+        <v>5.1954841262237261E-2</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
@@ -3781,40 +3787,40 @@
         <v>0.18086977303028101</v>
       </c>
       <c r="M11" s="5">
-        <v>0.47960110145628043</v>
+        <v>0.28964087448800452</v>
       </c>
       <c r="N11" s="5">
-        <v>0.11108921678051314</v>
+        <v>0.19999999999988483</v>
       </c>
       <c r="O11" s="5">
-        <v>1.5852289221896079</v>
+        <v>1.5720494323891605</v>
       </c>
       <c r="P11" s="11">
-        <v>1.5635033243411613E-6</v>
+        <v>8.0054398910298162E-4</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" si="1"/>
-        <v>0.17960110145628044</v>
+        <v>-1.0359125511995471E-2</v>
       </c>
       <c r="R11" s="5">
         <f t="shared" si="2"/>
-        <v>-8.8910783219486866E-2</v>
+        <v>-1.1518563880485999E-13</v>
       </c>
       <c r="S11" s="5">
         <f t="shared" si="3"/>
-        <v>1.4432595394711312E-2</v>
+        <v>1.253105594263948E-3</v>
       </c>
       <c r="T11" s="5">
         <f t="shared" si="4"/>
-        <v>0.17960110145628044</v>
+        <v>1.0359125511995471E-2</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="0"/>
-        <v>8.8910783219486866E-2</v>
+        <v>1.1518563880485999E-13</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" si="0"/>
-        <v>1.4432595394711312E-2</v>
+        <v>1.253105594263948E-3</v>
       </c>
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
@@ -3870,40 +3876,40 @@
         <v>6.6542282700538594E-2</v>
       </c>
       <c r="M12" s="5">
-        <v>0.99999999995815092</v>
+        <v>0.84829054835268891</v>
       </c>
       <c r="N12" s="5">
-        <v>0.12569962167399359</v>
+        <v>0.14271551796418253</v>
       </c>
       <c r="O12" s="5">
-        <v>1.5925004653243371</v>
+        <v>1.6675647082692944</v>
       </c>
       <c r="P12" s="11">
-        <v>5.2926135829915201E-6</v>
+        <v>4.7704038006776792E-4</v>
       </c>
       <c r="Q12" s="5">
         <f t="shared" si="1"/>
-        <v>0.29999999995815096</v>
+        <v>0.14829054835268896</v>
       </c>
       <c r="R12" s="5">
         <f t="shared" si="2"/>
-        <v>-7.4300378326006417E-2</v>
+        <v>-5.7284482035817486E-2</v>
       </c>
       <c r="S12" s="5">
         <f t="shared" si="3"/>
-        <v>2.1704138529440531E-2</v>
+        <v>9.6768381474397813E-2</v>
       </c>
       <c r="T12" s="5">
         <f t="shared" si="4"/>
-        <v>0.29999999995815096</v>
+        <v>0.14829054835268896</v>
       </c>
       <c r="U12" s="5">
         <f t="shared" si="0"/>
-        <v>7.4300378326006417E-2</v>
+        <v>5.7284482035817486E-2</v>
       </c>
       <c r="V12" s="5">
         <f t="shared" si="0"/>
-        <v>2.1704138529440531E-2</v>
+        <v>9.6768381474397813E-2</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
@@ -5341,7 +5347,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EAE0736-1722-4350-9DE0-8A911956EF0F}">
-  <dimension ref="A1:Y60"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
@@ -5363,1030 +5369,2051 @@
     <col min="22" max="22" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="AA1" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB1" s="34"/>
+      <c r="AC1" s="34"/>
+      <c r="AD1" s="34"/>
+      <c r="AE1" s="34"/>
+      <c r="AF1" s="34"/>
+      <c r="AG1" s="34"/>
+      <c r="AH1" s="34"/>
+      <c r="AI1" s="34"/>
+      <c r="AJ1" s="34"/>
+      <c r="AK1" s="34"/>
+      <c r="AL1" s="34"/>
+      <c r="AM1" s="34"/>
+      <c r="AN1" s="34"/>
+      <c r="AO1" s="34"/>
+      <c r="AP1" s="34"/>
+      <c r="AQ1" s="34"/>
+      <c r="AR1" s="34"/>
+      <c r="AS1" s="34"/>
+      <c r="AT1" s="34"/>
+      <c r="AU1" s="34"/>
+      <c r="AV1" s="34"/>
+      <c r="AW1" s="34"/>
+      <c r="AX1" s="34"/>
+      <c r="AY1" s="34"/>
+    </row>
+    <row r="2" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="17" t="s">
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="25" t="s">
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="27" t="s">
+      <c r="U2" s="30"/>
+      <c r="V2" s="30"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="28"/>
+      <c r="AA2" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB2" s="15"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="15"/>
+      <c r="AE2" s="15"/>
+      <c r="AF2" s="16"/>
+      <c r="AG2" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH2" s="18"/>
+      <c r="AI2" s="18"/>
+      <c r="AJ2" s="18"/>
+      <c r="AK2" s="18"/>
+      <c r="AL2" s="18"/>
+      <c r="AM2" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN2" s="26"/>
+      <c r="AO2" s="26"/>
+      <c r="AP2" s="26"/>
+      <c r="AQ2" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-    </row>
-    <row r="2" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="AR2" s="27"/>
+      <c r="AS2" s="27"/>
+      <c r="AT2" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="AU2" s="30"/>
+      <c r="AV2" s="30"/>
+      <c r="AW2" s="28"/>
+      <c r="AX2" s="28"/>
+      <c r="AY2" s="28"/>
+    </row>
+    <row r="3" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="J3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="T3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="W2" s="29" t="s">
+      <c r="W3" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="X2" s="29"/>
-      <c r="Y2" s="29"/>
-    </row>
-    <row r="3" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
+      <c r="X3" s="29"/>
+      <c r="Y3" s="29"/>
+      <c r="AA3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AS3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AU3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AV3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW3" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="AX3" s="29"/>
+      <c r="AY3" s="29"/>
+    </row>
+    <row r="4" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
         <f>'Proximal Validation'!A3</f>
         <v>0.4</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B4" s="5">
         <f>'Proximal Validation'!B3</f>
         <v>0.06</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C4" s="5">
         <f>'Proximal Validation'!C3</f>
         <v>1.5707963267948966</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D4" s="5">
         <f>'Proximal Validation'!D3</f>
         <v>0</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E4" s="5">
         <f>'Proximal Validation'!E3</f>
         <v>0</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F4" s="5">
         <f>'Proximal Validation'!F3</f>
         <v>0</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G4" s="5">
         <f>'Proximal Validation'!G3</f>
         <v>-2.8477585874497901E-4</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H4" s="5">
         <f>'Proximal Validation'!H3</f>
         <v>-5.8327373117208502E-2</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I4" s="5">
         <f>'Proximal Validation'!I3</f>
         <v>-1.50670297443867E-4</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J4" s="5">
         <f>'Proximal Validation'!J3</f>
         <v>6.01342367008328E-3</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K4" s="5">
         <f>'Proximal Validation'!K3</f>
         <v>2.2609531879425001E-3</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L4" s="5">
         <f>'Proximal Validation'!L3</f>
         <v>0.37637501955032299</v>
       </c>
-      <c r="M3" s="5">
-        <v>0.32045428003752091</v>
-      </c>
-      <c r="N3" s="5">
-        <v>7.4266226386429254E-2</v>
-      </c>
-      <c r="O3" s="5">
-        <v>1.5820521439163795</v>
-      </c>
-      <c r="P3" s="11">
-        <v>3.3601525123292944E-6</v>
-      </c>
-      <c r="Q3" s="5">
-        <f>M3-A3</f>
-        <v>-7.9545719962479111E-2</v>
-      </c>
-      <c r="R3" s="5">
-        <f>N3-B3</f>
-        <v>1.4266226386429257E-2</v>
-      </c>
-      <c r="S3" s="5">
-        <f>O3-C3</f>
-        <v>1.1255817121482936E-2</v>
-      </c>
-      <c r="T3" s="5">
-        <f>ABS(Q3)</f>
-        <v>7.9545719962479111E-2</v>
-      </c>
-      <c r="U3" s="5">
-        <f t="shared" ref="U3:V12" si="0">ABS(R3)</f>
-        <v>1.4266226386429257E-2</v>
-      </c>
-      <c r="V3" s="5">
+      <c r="M4" s="5">
+        <v>0.44724256908776044</v>
+      </c>
+      <c r="N4" s="5">
+        <v>7.1236217769058335E-2</v>
+      </c>
+      <c r="O4" s="5">
+        <v>1.5725247256626125</v>
+      </c>
+      <c r="P4" s="11">
+        <v>1.8044117511545598E-4</v>
+      </c>
+      <c r="Q4" s="5">
+        <f>M4-A4</f>
+        <v>4.7242569087760422E-2</v>
+      </c>
+      <c r="R4" s="5">
+        <f>N4-B4</f>
+        <v>1.1236217769058338E-2</v>
+      </c>
+      <c r="S4" s="5">
+        <f>O4-C4</f>
+        <v>1.728398867715919E-3</v>
+      </c>
+      <c r="T4" s="5">
+        <f>ABS(Q4)</f>
+        <v>4.7242569087760422E-2</v>
+      </c>
+      <c r="U4" s="5">
+        <f t="shared" ref="U4:V13" si="0">ABS(R4)</f>
+        <v>1.1236217769058338E-2</v>
+      </c>
+      <c r="V4" s="5">
         <f t="shared" si="0"/>
-        <v>1.1255817121482936E-2</v>
-      </c>
-      <c r="W3" s="1" t="s">
+        <v>1.728398867715919E-3</v>
+      </c>
+      <c r="W4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Y3" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+      <c r="AA4" s="5">
+        <f>'Proximal Validation'!A3</f>
+        <v>0.4</v>
+      </c>
+      <c r="AB4" s="5">
+        <f>'Proximal Validation'!B3</f>
+        <v>0.06</v>
+      </c>
+      <c r="AC4" s="5">
+        <f>'Proximal Validation'!C3</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AD4" s="5">
+        <f>'Proximal Validation'!D3</f>
+        <v>0</v>
+      </c>
+      <c r="AE4" s="5">
+        <f>'Proximal Validation'!E3</f>
+        <v>0</v>
+      </c>
+      <c r="AF4" s="5">
+        <f>'Proximal Validation'!F3</f>
+        <v>0</v>
+      </c>
+      <c r="AG4" s="5">
+        <f>'Proximal Validation'!G3</f>
+        <v>-2.8477585874497901E-4</v>
+      </c>
+      <c r="AH4" s="5">
+        <f>'Proximal Validation'!H3</f>
+        <v>-5.8327373117208502E-2</v>
+      </c>
+      <c r="AI4" s="5">
+        <f>'Proximal Validation'!I3</f>
+        <v>-1.50670297443867E-4</v>
+      </c>
+      <c r="AJ4" s="5">
+        <f>'Proximal Validation'!J3</f>
+        <v>6.01342367008328E-3</v>
+      </c>
+      <c r="AK4" s="5">
+        <f>'Proximal Validation'!K3</f>
+        <v>2.2609531879425001E-3</v>
+      </c>
+      <c r="AL4" s="5">
+        <f>'Proximal Validation'!L3</f>
+        <v>0.37637501955032299</v>
+      </c>
+      <c r="AM4" s="5">
+        <v>0.93080923022377193</v>
+      </c>
+      <c r="AN4" s="5">
+        <v>7.4280472363654759E-2</v>
+      </c>
+      <c r="AO4" s="5">
+        <v>1.5698072215661012</v>
+      </c>
+      <c r="AP4" s="11">
+        <v>1.150785826051848E-4</v>
+      </c>
+      <c r="AQ4" s="5">
+        <f>AM4-AA4</f>
+        <v>0.53080923022377191</v>
+      </c>
+      <c r="AR4" s="5">
+        <f>AN4-AB4</f>
+        <v>1.4280472363654761E-2</v>
+      </c>
+      <c r="AS4" s="5">
+        <f>AO4-AC4</f>
+        <v>-9.8910522879536167E-4</v>
+      </c>
+      <c r="AT4" s="5">
+        <f>ABS(AQ4)</f>
+        <v>0.53080923022377191</v>
+      </c>
+      <c r="AU4" s="5">
+        <f t="shared" ref="AU4:AU13" si="1">ABS(AR4)</f>
+        <v>1.4280472363654761E-2</v>
+      </c>
+      <c r="AV4" s="5">
+        <f t="shared" ref="AV4:AV13" si="2">ABS(AS4)</f>
+        <v>9.8910522879536167E-4</v>
+      </c>
+      <c r="AW4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AX4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AY4" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
         <f>'Proximal Validation'!A4</f>
         <v>0.8</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B5" s="8">
         <f>'Proximal Validation'!B4</f>
         <v>0.06</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C5" s="8">
         <f>'Proximal Validation'!C4</f>
         <v>1.5707963267948966</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D5" s="8">
         <f>'Proximal Validation'!D4</f>
         <v>0</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E5" s="8">
         <f>'Proximal Validation'!E4</f>
         <v>0</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F5" s="8">
         <f>'Proximal Validation'!F4</f>
         <v>0</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G5" s="8">
         <f>'Proximal Validation'!G4</f>
         <v>-1.3759520370513201E-3</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H5" s="8">
         <f>'Proximal Validation'!H4</f>
         <v>-0.12723180651664701</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I5" s="8">
         <f>'Proximal Validation'!I4</f>
         <v>-1.5217980835586799E-3</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J5" s="8">
         <f>'Proximal Validation'!J4</f>
         <v>-8.26666504144669E-2</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K5" s="8">
         <f>'Proximal Validation'!K4</f>
         <v>-4.7411769628524798E-3</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L5" s="8">
         <f>'Proximal Validation'!L4</f>
         <v>0.81632339954376198</v>
       </c>
-      <c r="M4" s="8">
-        <v>0.69952918421871013</v>
-      </c>
-      <c r="N4" s="8">
-        <v>7.39223109112708E-2</v>
-      </c>
-      <c r="O4" s="8">
-        <v>1.5912729721829617</v>
-      </c>
-      <c r="P4" s="12">
-        <v>7.1321463003380412E-6</v>
-      </c>
-      <c r="Q4" s="5">
-        <f t="shared" ref="Q4:S12" si="1">M4-A4</f>
-        <v>-0.10047081578128991</v>
-      </c>
-      <c r="R4" s="5">
+      <c r="M5" s="8">
+        <v>0.72482627445411119</v>
+      </c>
+      <c r="N5" s="8">
+        <v>7.4627258714440189E-2</v>
+      </c>
+      <c r="O5" s="8">
+        <v>1.595856178375745</v>
+      </c>
+      <c r="P5" s="12">
+        <v>1.9585030527773247E-4</v>
+      </c>
+      <c r="Q5" s="5">
+        <f t="shared" ref="Q5:S13" si="3">M5-A5</f>
+        <v>-7.5173725545888859E-2</v>
+      </c>
+      <c r="R5" s="5">
+        <f t="shared" si="3"/>
+        <v>1.4627258714440192E-2</v>
+      </c>
+      <c r="S5" s="5">
+        <f t="shared" si="3"/>
+        <v>2.5059851580848447E-2</v>
+      </c>
+      <c r="T5" s="5">
+        <f t="shared" ref="T5:T13" si="4">ABS(Q5)</f>
+        <v>7.5173725545888859E-2</v>
+      </c>
+      <c r="U5" s="5">
+        <f t="shared" si="0"/>
+        <v>1.4627258714440192E-2</v>
+      </c>
+      <c r="V5" s="5">
+        <f t="shared" si="0"/>
+        <v>2.5059851580848447E-2</v>
+      </c>
+      <c r="W5" s="6" cm="1">
+        <f t="array" ref="W5">AVERAGE(ABS(Q4:Q13))</f>
+        <v>3.8162384263215735E-2</v>
+      </c>
+      <c r="X5" s="6" cm="1">
+        <f t="array" ref="X5">AVERAGE(ABS(R4:R13))</f>
+        <v>1.3003252954498617E-2</v>
+      </c>
+      <c r="Y5" s="6" cm="1">
+        <f t="array" ref="Y5">AVERAGE(ABS(S4:S13))</f>
+        <v>1.6045352321544228E-2</v>
+      </c>
+      <c r="AA5" s="8">
+        <f>'Proximal Validation'!A4</f>
+        <v>0.8</v>
+      </c>
+      <c r="AB5" s="8">
+        <f>'Proximal Validation'!B4</f>
+        <v>0.06</v>
+      </c>
+      <c r="AC5" s="8">
+        <f>'Proximal Validation'!C4</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AD5" s="8">
+        <f>'Proximal Validation'!D4</f>
+        <v>0</v>
+      </c>
+      <c r="AE5" s="8">
+        <f>'Proximal Validation'!E4</f>
+        <v>0</v>
+      </c>
+      <c r="AF5" s="8">
+        <f>'Proximal Validation'!F4</f>
+        <v>0</v>
+      </c>
+      <c r="AG5" s="8">
+        <f>'Proximal Validation'!G4</f>
+        <v>-1.3759520370513201E-3</v>
+      </c>
+      <c r="AH5" s="8">
+        <f>'Proximal Validation'!H4</f>
+        <v>-0.12723180651664701</v>
+      </c>
+      <c r="AI5" s="8">
+        <f>'Proximal Validation'!I4</f>
+        <v>-1.5217980835586799E-3</v>
+      </c>
+      <c r="AJ5" s="8">
+        <f>'Proximal Validation'!J4</f>
+        <v>-8.26666504144669E-2</v>
+      </c>
+      <c r="AK5" s="8">
+        <f>'Proximal Validation'!K4</f>
+        <v>-4.7411769628524798E-3</v>
+      </c>
+      <c r="AL5" s="8">
+        <f>'Proximal Validation'!L4</f>
+        <v>0.81632339954376198</v>
+      </c>
+      <c r="AM5" s="8">
+        <v>0.91833498490248799</v>
+      </c>
+      <c r="AN5" s="8">
+        <v>8.040059852944742E-2</v>
+      </c>
+      <c r="AO5" s="8">
+        <v>1.5960797470783472</v>
+      </c>
+      <c r="AP5" s="12">
+        <v>2.3695018871766488E-4</v>
+      </c>
+      <c r="AQ5" s="5">
+        <f t="shared" ref="AQ5:AQ13" si="5">AM5-AA5</f>
+        <v>0.11833498490248795</v>
+      </c>
+      <c r="AR5" s="5">
+        <f t="shared" ref="AR5:AR13" si="6">AN5-AB5</f>
+        <v>2.0400598529447422E-2</v>
+      </c>
+      <c r="AS5" s="5">
+        <f t="shared" ref="AS5:AS13" si="7">AO5-AC5</f>
+        <v>2.5283420283450653E-2</v>
+      </c>
+      <c r="AT5" s="5">
+        <f t="shared" ref="AT5:AT13" si="8">ABS(AQ5)</f>
+        <v>0.11833498490248795</v>
+      </c>
+      <c r="AU5" s="5">
         <f t="shared" si="1"/>
-        <v>1.3922310911270802E-2</v>
-      </c>
-      <c r="S4" s="5">
-        <f t="shared" si="1"/>
-        <v>2.0476645388065151E-2</v>
-      </c>
-      <c r="T4" s="5">
-        <f t="shared" ref="T4:T12" si="2">ABS(Q4)</f>
-        <v>0.10047081578128991</v>
-      </c>
-      <c r="U4" s="5">
-        <f t="shared" si="0"/>
-        <v>1.3922310911270802E-2</v>
-      </c>
-      <c r="V4" s="5">
-        <f t="shared" si="0"/>
-        <v>2.0476645388065151E-2</v>
-      </c>
-      <c r="W4" s="6" cm="1">
-        <f t="array" ref="W4">AVERAGE(ABS(Q3:Q12))</f>
-        <v>0.17312640555746397</v>
-      </c>
-      <c r="X4" s="6" cm="1">
-        <f t="array" ref="X4">AVERAGE(ABS(R3:R12))</f>
-        <v>4.167234524607185E-2</v>
-      </c>
-      <c r="Y4" s="6" cm="1">
-        <f t="array" ref="Y4">AVERAGE(ABS(S3:S12))</f>
-        <v>1.6943422852808875E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+        <v>2.0400598529447422E-2</v>
+      </c>
+      <c r="AV5" s="5">
+        <f t="shared" si="2"/>
+        <v>2.5283420283450653E-2</v>
+      </c>
+      <c r="AW5" s="6" cm="1">
+        <f t="array" ref="AW5">AVERAGE(ABS(AQ4:AQ13))</f>
+        <v>0.18453175682454409</v>
+      </c>
+      <c r="AX5" s="6" cm="1">
+        <f t="array" ref="AX5">AVERAGE(ABS(AR4:AR13))</f>
+        <v>1.3022282717788505E-2</v>
+      </c>
+      <c r="AY5" s="6" cm="1">
+        <f t="array" ref="AY5">AVERAGE(ABS(AS4:AS13))</f>
+        <v>1.5310297539590168E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
         <f>'Proximal Validation'!A5</f>
         <v>0.3</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B6" s="5">
         <f>'Proximal Validation'!B5</f>
         <v>0.08</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C6" s="5">
         <f>'Proximal Validation'!C5</f>
         <v>1.5707963267948966</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D6" s="5">
         <f>'Proximal Validation'!D5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E6" s="5">
         <f>'Proximal Validation'!E5</f>
         <v>0</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F6" s="5">
         <f>'Proximal Validation'!F5</f>
         <v>0</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G6" s="5">
         <f>'Proximal Validation'!G5</f>
         <v>-2.8428673977032298E-4</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H6" s="5">
         <f>'Proximal Validation'!H5</f>
         <v>-4.3962169438600499E-2</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I6" s="5">
         <f>'Proximal Validation'!I5</f>
         <v>-1.9410930690355599E-4</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J6" s="5">
         <f>'Proximal Validation'!J5</f>
         <v>-1.4232989400625199E-2</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K6" s="5">
         <f>'Proximal Validation'!K5</f>
         <v>8.0315023660659801E-4</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L6" s="5">
         <f>'Proximal Validation'!L5</f>
         <v>0.24872186779975899</v>
       </c>
-      <c r="M5" s="5">
-        <v>0.35394142231527698</v>
-      </c>
-      <c r="N5" s="5">
-        <v>6.0804262771734868E-2</v>
-      </c>
-      <c r="O5" s="5">
-        <v>1.5808759141763677</v>
-      </c>
-      <c r="P5" s="11">
-        <v>4.7600296401340745E-7</v>
-      </c>
-      <c r="Q5" s="5">
+      <c r="M6" s="5">
+        <v>0.30067881278286518</v>
+      </c>
+      <c r="N6" s="5">
+        <v>8.8419965347717039E-2</v>
+      </c>
+      <c r="O6" s="5">
+        <v>1.5781920946365151</v>
+      </c>
+      <c r="P6" s="11">
+        <v>3.1521521810203471E-5</v>
+      </c>
+      <c r="Q6" s="5">
+        <f t="shared" si="3"/>
+        <v>6.788127828651902E-4</v>
+      </c>
+      <c r="R6" s="5">
+        <f t="shared" si="3"/>
+        <v>8.4199653477170372E-3</v>
+      </c>
+      <c r="S6" s="5">
+        <f t="shared" si="3"/>
+        <v>7.3957678416185502E-3</v>
+      </c>
+      <c r="T6" s="5">
+        <f t="shared" si="4"/>
+        <v>6.788127828651902E-4</v>
+      </c>
+      <c r="U6" s="5">
+        <f t="shared" si="0"/>
+        <v>8.4199653477170372E-3</v>
+      </c>
+      <c r="V6" s="5">
+        <f t="shared" si="0"/>
+        <v>7.3957678416185502E-3</v>
+      </c>
+      <c r="W6" s="24"/>
+      <c r="X6" s="24"/>
+      <c r="Y6" s="24"/>
+      <c r="AA6" s="5">
+        <f>'Proximal Validation'!A5</f>
+        <v>0.3</v>
+      </c>
+      <c r="AB6" s="5">
+        <f>'Proximal Validation'!B5</f>
+        <v>0.08</v>
+      </c>
+      <c r="AC6" s="5">
+        <f>'Proximal Validation'!C5</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AD6" s="5">
+        <f>'Proximal Validation'!D5</f>
+        <v>0</v>
+      </c>
+      <c r="AE6" s="5">
+        <f>'Proximal Validation'!E5</f>
+        <v>0</v>
+      </c>
+      <c r="AF6" s="5">
+        <f>'Proximal Validation'!F5</f>
+        <v>0</v>
+      </c>
+      <c r="AG6" s="5">
+        <f>'Proximal Validation'!G5</f>
+        <v>-2.8428673977032298E-4</v>
+      </c>
+      <c r="AH6" s="5">
+        <f>'Proximal Validation'!H5</f>
+        <v>-4.3962169438600499E-2</v>
+      </c>
+      <c r="AI6" s="5">
+        <f>'Proximal Validation'!I5</f>
+        <v>-1.9410930690355599E-4</v>
+      </c>
+      <c r="AJ6" s="5">
+        <f>'Proximal Validation'!J5</f>
+        <v>-1.4232989400625199E-2</v>
+      </c>
+      <c r="AK6" s="5">
+        <f>'Proximal Validation'!K5</f>
+        <v>8.0315023660659801E-4</v>
+      </c>
+      <c r="AL6" s="5">
+        <f>'Proximal Validation'!L5</f>
+        <v>0.24872186779975899</v>
+      </c>
+      <c r="AM6" s="5">
+        <v>0.49728631181273564</v>
+      </c>
+      <c r="AN6" s="5">
+        <v>8.7942568172972774E-2</v>
+      </c>
+      <c r="AO6" s="5">
+        <v>1.5781110314585332</v>
+      </c>
+      <c r="AP6" s="11">
+        <v>1.0945855357198722E-5</v>
+      </c>
+      <c r="AQ6" s="5">
+        <f t="shared" si="5"/>
+        <v>0.19728631181273565</v>
+      </c>
+      <c r="AR6" s="5">
+        <f t="shared" si="6"/>
+        <v>7.9425681729727721E-3</v>
+      </c>
+      <c r="AS6" s="5">
+        <f t="shared" si="7"/>
+        <v>7.3147046636365953E-3</v>
+      </c>
+      <c r="AT6" s="5">
+        <f t="shared" si="8"/>
+        <v>0.19728631181273565</v>
+      </c>
+      <c r="AU6" s="5">
         <f t="shared" si="1"/>
-        <v>5.3941422315276988E-2</v>
-      </c>
-      <c r="R5" s="5">
-        <f t="shared" si="1"/>
-        <v>-1.9195737228265133E-2</v>
-      </c>
-      <c r="S5" s="5">
-        <f t="shared" si="1"/>
-        <v>1.0079587381471189E-2</v>
-      </c>
-      <c r="T5" s="5">
+        <v>7.9425681729727721E-3</v>
+      </c>
+      <c r="AV6" s="5">
         <f t="shared" si="2"/>
-        <v>5.3941422315276988E-2</v>
-      </c>
-      <c r="U5" s="5">
-        <f t="shared" si="0"/>
-        <v>1.9195737228265133E-2</v>
-      </c>
-      <c r="V5" s="5">
-        <f t="shared" si="0"/>
-        <v>1.0079587381471189E-2</v>
-      </c>
-      <c r="W5" s="24"/>
-      <c r="X5" s="24"/>
-      <c r="Y5" s="24"/>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+        <v>7.3147046636365953E-3</v>
+      </c>
+      <c r="AW6" s="24"/>
+      <c r="AX6" s="24"/>
+      <c r="AY6" s="24"/>
+    </row>
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
         <f>'Proximal Validation'!A6</f>
         <v>0.5</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B7" s="5">
         <f>'Proximal Validation'!B6</f>
         <v>0.1</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C7" s="5">
         <f>'Proximal Validation'!C6</f>
         <v>1.5707963267948966</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D7" s="5">
         <f>'Proximal Validation'!D6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E7" s="5">
         <f>'Proximal Validation'!E6</f>
         <v>0</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F7" s="5">
         <f>'Proximal Validation'!F6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G7" s="5">
         <f>'Proximal Validation'!G6</f>
         <v>-9.02065541595221E-4</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H7" s="5">
         <f>'Proximal Validation'!H6</f>
         <v>-9.5010705292224898E-2</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I7" s="5">
         <f>'Proximal Validation'!I6</f>
         <v>-3.1485431827604798E-4</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J7" s="5">
         <f>'Proximal Validation'!J6</f>
         <v>-0.14170777797699</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K7" s="5">
         <f>'Proximal Validation'!K6</f>
         <v>3.2724365592002899E-3</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L7" s="5">
         <f>'Proximal Validation'!L6</f>
         <v>0.46851912140846302</v>
       </c>
-      <c r="M6" s="5">
-        <v>0.47339149285628018</v>
-      </c>
-      <c r="N6" s="5">
-        <v>0.11306568793870092</v>
-      </c>
-      <c r="O6" s="5">
-        <v>1.5823644772093757</v>
-      </c>
-      <c r="P6" s="11">
-        <v>1.4079231411891688E-6</v>
-      </c>
-      <c r="Q6" s="5">
+      <c r="M7" s="5">
+        <v>0.50010643412132028</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0.11069487751659678</v>
+      </c>
+      <c r="O7" s="5">
+        <v>1.5808506255606938</v>
+      </c>
+      <c r="P7" s="11">
+        <v>8.7772175198983751E-5</v>
+      </c>
+      <c r="Q7" s="5">
+        <f t="shared" si="3"/>
+        <v>1.0643412132027574E-4</v>
+      </c>
+      <c r="R7" s="5">
+        <f t="shared" si="3"/>
+        <v>1.0694877516596771E-2</v>
+      </c>
+      <c r="S7" s="5">
+        <f t="shared" si="3"/>
+        <v>1.005429876579722E-2</v>
+      </c>
+      <c r="T7" s="5">
+        <f t="shared" si="4"/>
+        <v>1.0643412132027574E-4</v>
+      </c>
+      <c r="U7" s="5">
+        <f t="shared" si="0"/>
+        <v>1.0694877516596771E-2</v>
+      </c>
+      <c r="V7" s="5">
+        <f t="shared" si="0"/>
+        <v>1.005429876579722E-2</v>
+      </c>
+      <c r="AA7" s="5">
+        <f>'Proximal Validation'!A6</f>
+        <v>0.5</v>
+      </c>
+      <c r="AB7" s="5">
+        <f>'Proximal Validation'!B6</f>
+        <v>0.1</v>
+      </c>
+      <c r="AC7" s="5">
+        <f>'Proximal Validation'!C6</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AD7" s="5">
+        <f>'Proximal Validation'!D6</f>
+        <v>0</v>
+      </c>
+      <c r="AE7" s="5">
+        <f>'Proximal Validation'!E6</f>
+        <v>0</v>
+      </c>
+      <c r="AF7" s="5">
+        <f>'Proximal Validation'!F6</f>
+        <v>0</v>
+      </c>
+      <c r="AG7" s="5">
+        <f>'Proximal Validation'!G6</f>
+        <v>-9.02065541595221E-4</v>
+      </c>
+      <c r="AH7" s="5">
+        <f>'Proximal Validation'!H6</f>
+        <v>-9.5010705292224898E-2</v>
+      </c>
+      <c r="AI7" s="5">
+        <f>'Proximal Validation'!I6</f>
+        <v>-3.1485431827604798E-4</v>
+      </c>
+      <c r="AJ7" s="5">
+        <f>'Proximal Validation'!J6</f>
+        <v>-0.14170777797699</v>
+      </c>
+      <c r="AK7" s="5">
+        <f>'Proximal Validation'!K6</f>
+        <v>3.2724365592002899E-3</v>
+      </c>
+      <c r="AL7" s="5">
+        <f>'Proximal Validation'!L6</f>
+        <v>0.46851912140846302</v>
+      </c>
+      <c r="AM7" s="5">
+        <v>0.7276062255889908</v>
+      </c>
+      <c r="AN7" s="5">
+        <v>0.11093944883306532</v>
+      </c>
+      <c r="AO7" s="5">
+        <v>1.5798657137560832</v>
+      </c>
+      <c r="AP7" s="11">
+        <v>1.0518135936770494E-4</v>
+      </c>
+      <c r="AQ7" s="5">
+        <f t="shared" si="5"/>
+        <v>0.2276062255889908</v>
+      </c>
+      <c r="AR7" s="5">
+        <f t="shared" si="6"/>
+        <v>1.0939448833065316E-2</v>
+      </c>
+      <c r="AS7" s="5">
+        <f t="shared" si="7"/>
+        <v>9.0693869611866429E-3</v>
+      </c>
+      <c r="AT7" s="5">
+        <f t="shared" si="8"/>
+        <v>0.2276062255889908</v>
+      </c>
+      <c r="AU7" s="5">
         <f t="shared" si="1"/>
-        <v>-2.6608507143719817E-2</v>
-      </c>
-      <c r="R6" s="5">
-        <f t="shared" si="1"/>
-        <v>1.3065687938700915E-2</v>
-      </c>
-      <c r="S6" s="5">
-        <f t="shared" si="1"/>
-        <v>1.1568150414479117E-2</v>
-      </c>
-      <c r="T6" s="5">
+        <v>1.0939448833065316E-2</v>
+      </c>
+      <c r="AV7" s="5">
         <f t="shared" si="2"/>
-        <v>2.6608507143719817E-2</v>
-      </c>
-      <c r="U6" s="5">
-        <f t="shared" si="0"/>
-        <v>1.3065687938700915E-2</v>
-      </c>
-      <c r="V6" s="5">
-        <f t="shared" si="0"/>
-        <v>1.1568150414479117E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
+        <v>9.0693869611866429E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
         <f>'Proximal Validation'!A7</f>
         <v>0.7</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B8" s="5">
         <f>'Proximal Validation'!B7</f>
         <v>0.1</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C8" s="5">
         <f>'Proximal Validation'!C7</f>
         <v>1.5707963267948966</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D8" s="5">
         <f>'Proximal Validation'!D7</f>
         <v>0</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E8" s="5">
         <f>'Proximal Validation'!E7</f>
         <v>0</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F8" s="5">
         <f>'Proximal Validation'!F7</f>
         <v>0</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G8" s="5">
         <f>'Proximal Validation'!G7</f>
         <v>-1.3697715476155301E-3</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H8" s="5">
         <f>'Proximal Validation'!H7</f>
         <v>-0.129899337887764</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I8" s="5">
         <f>'Proximal Validation'!I7</f>
         <v>-1.1154995299875699E-3</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J8" s="5">
         <f>'Proximal Validation'!J7</f>
         <v>-0.27736902236938499</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K8" s="5">
         <f>'Proximal Validation'!K7</f>
         <v>2.9984340071678201E-3</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L8" s="5">
         <f>'Proximal Validation'!L7</f>
         <v>0.62586665153503396</v>
       </c>
-      <c r="M7" s="5">
-        <v>0.66953869115774001</v>
-      </c>
-      <c r="N7" s="5">
-        <v>0.1127205855050233</v>
-      </c>
-      <c r="O7" s="5">
-        <v>1.5898913605901939</v>
-      </c>
-      <c r="P7" s="11">
-        <v>2.3938320312070323E-6</v>
-      </c>
-      <c r="Q7" s="5">
+      <c r="M8" s="5">
+        <v>0.69555108323175452</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0.10817761612007287</v>
+      </c>
+      <c r="O8" s="5">
+        <v>1.5877814041874156</v>
+      </c>
+      <c r="P8" s="11">
+        <v>5.8431032249773554E-5</v>
+      </c>
+      <c r="Q8" s="5">
+        <f t="shared" si="3"/>
+        <v>-4.4489167682454367E-3</v>
+      </c>
+      <c r="R8" s="5">
+        <f t="shared" si="3"/>
+        <v>8.177616120072867E-3</v>
+      </c>
+      <c r="S8" s="5">
+        <f t="shared" si="3"/>
+        <v>1.6985077392519088E-2</v>
+      </c>
+      <c r="T8" s="5">
+        <f t="shared" si="4"/>
+        <v>4.4489167682454367E-3</v>
+      </c>
+      <c r="U8" s="5">
+        <f t="shared" si="0"/>
+        <v>8.177616120072867E-3</v>
+      </c>
+      <c r="V8" s="5">
+        <f t="shared" si="0"/>
+        <v>1.6985077392519088E-2</v>
+      </c>
+      <c r="AA8" s="5">
+        <f>'Proximal Validation'!A7</f>
+        <v>0.7</v>
+      </c>
+      <c r="AB8" s="5">
+        <f>'Proximal Validation'!B7</f>
+        <v>0.1</v>
+      </c>
+      <c r="AC8" s="5">
+        <f>'Proximal Validation'!C7</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AD8" s="5">
+        <f>'Proximal Validation'!D7</f>
+        <v>0</v>
+      </c>
+      <c r="AE8" s="5">
+        <f>'Proximal Validation'!E7</f>
+        <v>0</v>
+      </c>
+      <c r="AF8" s="5">
+        <f>'Proximal Validation'!F7</f>
+        <v>0</v>
+      </c>
+      <c r="AG8" s="5">
+        <f>'Proximal Validation'!G7</f>
+        <v>-1.3697715476155301E-3</v>
+      </c>
+      <c r="AH8" s="5">
+        <f>'Proximal Validation'!H7</f>
+        <v>-0.129899337887764</v>
+      </c>
+      <c r="AI8" s="5">
+        <f>'Proximal Validation'!I7</f>
+        <v>-1.1154995299875699E-3</v>
+      </c>
+      <c r="AJ8" s="5">
+        <f>'Proximal Validation'!J7</f>
+        <v>-0.27736902236938499</v>
+      </c>
+      <c r="AK8" s="5">
+        <f>'Proximal Validation'!K7</f>
+        <v>2.9984340071678201E-3</v>
+      </c>
+      <c r="AL8" s="5">
+        <f>'Proximal Validation'!L7</f>
+        <v>0.62586665153503396</v>
+      </c>
+      <c r="AM8" s="5">
+        <v>0.89351580808552333</v>
+      </c>
+      <c r="AN8" s="5">
+        <v>0.10862710095052713</v>
+      </c>
+      <c r="AO8" s="5">
+        <v>1.5864782205146963</v>
+      </c>
+      <c r="AP8" s="11">
+        <v>9.8187916179511055E-5</v>
+      </c>
+      <c r="AQ8" s="5">
+        <f t="shared" si="5"/>
+        <v>0.19351580808552338</v>
+      </c>
+      <c r="AR8" s="5">
+        <f t="shared" si="6"/>
+        <v>8.6271009505271279E-3</v>
+      </c>
+      <c r="AS8" s="5">
+        <f t="shared" si="7"/>
+        <v>1.5681893719799778E-2</v>
+      </c>
+      <c r="AT8" s="5">
+        <f t="shared" si="8"/>
+        <v>0.19351580808552338</v>
+      </c>
+      <c r="AU8" s="5">
         <f t="shared" si="1"/>
-        <v>-3.0461308842259949E-2</v>
-      </c>
-      <c r="R7" s="5">
-        <f t="shared" si="1"/>
-        <v>1.2720585505023294E-2</v>
-      </c>
-      <c r="S7" s="5">
-        <f t="shared" si="1"/>
-        <v>1.9095033795297311E-2</v>
-      </c>
-      <c r="T7" s="5">
+        <v>8.6271009505271279E-3</v>
+      </c>
+      <c r="AV8" s="5">
         <f t="shared" si="2"/>
-        <v>3.0461308842259949E-2</v>
-      </c>
-      <c r="U7" s="5">
-        <f t="shared" si="0"/>
-        <v>1.2720585505023294E-2</v>
-      </c>
-      <c r="V7" s="5">
-        <f t="shared" si="0"/>
-        <v>1.9095033795297311E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
+        <v>1.5681893719799778E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
         <f>'Proximal Validation'!A8</f>
         <v>0.4</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B9" s="5">
         <f>'Proximal Validation'!B8</f>
         <v>0.16</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C9" s="5">
         <f>'Proximal Validation'!C8</f>
         <v>1.5707963267948966</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D9" s="5">
         <f>'Proximal Validation'!D8</f>
         <v>0</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E9" s="5">
         <f>'Proximal Validation'!E8</f>
         <v>0</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F9" s="5">
         <f>'Proximal Validation'!F8</f>
         <v>0</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G9" s="5">
         <f>'Proximal Validation'!G8</f>
         <v>-1.30162085406482E-3</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H9" s="5">
         <f>'Proximal Validation'!H8</f>
         <v>-9.1771319508552607E-2</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I9" s="5">
         <f>'Proximal Validation'!I8</f>
         <v>-6.8558257771655895E-4</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J9" s="5">
         <f>'Proximal Validation'!J8</f>
         <v>-0.188138782978058</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K9" s="5">
         <f>'Proximal Validation'!K8</f>
         <v>3.5599116235971499E-3</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L9" s="5">
         <f>'Proximal Validation'!L8</f>
         <v>0.316497713327408</v>
       </c>
-      <c r="M8" s="5">
-        <v>0.86211058492308323</v>
-      </c>
-      <c r="N8" s="5">
-        <v>7.3601607688535187E-2</v>
-      </c>
-      <c r="O8" s="5">
-        <v>1.5866289348989331</v>
-      </c>
-      <c r="P8" s="11">
-        <v>1.8506032896424492E-6</v>
-      </c>
-      <c r="Q8" s="5">
+      <c r="M9" s="5">
+        <v>0.37708508200985424</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0.16990423837519988</v>
+      </c>
+      <c r="O9" s="5">
+        <v>1.5783103974769122</v>
+      </c>
+      <c r="P9" s="11">
+        <v>2.9633396187254003E-4</v>
+      </c>
+      <c r="Q9" s="5">
+        <f t="shared" si="3"/>
+        <v>-2.2914917990145778E-2</v>
+      </c>
+      <c r="R9" s="5">
+        <f t="shared" si="3"/>
+        <v>9.9042383751998808E-3</v>
+      </c>
+      <c r="S9" s="5">
+        <f t="shared" si="3"/>
+        <v>7.5140706820155945E-3</v>
+      </c>
+      <c r="T9" s="5">
+        <f t="shared" si="4"/>
+        <v>2.2914917990145778E-2</v>
+      </c>
+      <c r="U9" s="5">
+        <f t="shared" si="0"/>
+        <v>9.9042383751998808E-3</v>
+      </c>
+      <c r="V9" s="5">
+        <f t="shared" si="0"/>
+        <v>7.5140706820155945E-3</v>
+      </c>
+      <c r="AA9" s="5">
+        <f>'Proximal Validation'!A8</f>
+        <v>0.4</v>
+      </c>
+      <c r="AB9" s="5">
+        <f>'Proximal Validation'!B8</f>
+        <v>0.16</v>
+      </c>
+      <c r="AC9" s="5">
+        <f>'Proximal Validation'!C8</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AD9" s="5">
+        <f>'Proximal Validation'!D8</f>
+        <v>0</v>
+      </c>
+      <c r="AE9" s="5">
+        <f>'Proximal Validation'!E8</f>
+        <v>0</v>
+      </c>
+      <c r="AF9" s="5">
+        <f>'Proximal Validation'!F8</f>
+        <v>0</v>
+      </c>
+      <c r="AG9" s="5">
+        <f>'Proximal Validation'!G8</f>
+        <v>-1.30162085406482E-3</v>
+      </c>
+      <c r="AH9" s="5">
+        <f>'Proximal Validation'!H8</f>
+        <v>-9.1771319508552607E-2</v>
+      </c>
+      <c r="AI9" s="5">
+        <f>'Proximal Validation'!I8</f>
+        <v>-6.8558257771655895E-4</v>
+      </c>
+      <c r="AJ9" s="5">
+        <f>'Proximal Validation'!J8</f>
+        <v>-0.188138782978058</v>
+      </c>
+      <c r="AK9" s="5">
+        <f>'Proximal Validation'!K8</f>
+        <v>3.5599116235971499E-3</v>
+      </c>
+      <c r="AL9" s="5">
+        <f>'Proximal Validation'!L8</f>
+        <v>0.316497713327408</v>
+      </c>
+      <c r="AM9" s="5">
+        <v>0.32723128078591002</v>
+      </c>
+      <c r="AN9" s="5">
+        <v>0.16889019177444919</v>
+      </c>
+      <c r="AO9" s="5">
+        <v>1.5727231209828236</v>
+      </c>
+      <c r="AP9" s="11">
+        <v>4.2686043312899446E-4</v>
+      </c>
+      <c r="AQ9" s="5">
+        <f t="shared" si="5"/>
+        <v>-7.2768719214090005E-2</v>
+      </c>
+      <c r="AR9" s="5">
+        <f t="shared" si="6"/>
+        <v>8.890191774449191E-3</v>
+      </c>
+      <c r="AS9" s="5">
+        <f t="shared" si="7"/>
+        <v>1.9267941879270722E-3</v>
+      </c>
+      <c r="AT9" s="5">
+        <f t="shared" si="8"/>
+        <v>7.2768719214090005E-2</v>
+      </c>
+      <c r="AU9" s="5">
         <f t="shared" si="1"/>
-        <v>0.46211058492308321</v>
-      </c>
-      <c r="R8" s="5">
-        <f t="shared" si="1"/>
-        <v>-8.6398392311464817E-2</v>
-      </c>
-      <c r="S8" s="5">
-        <f t="shared" si="1"/>
-        <v>1.5832608104036527E-2</v>
-      </c>
-      <c r="T8" s="5">
+        <v>8.890191774449191E-3</v>
+      </c>
+      <c r="AV9" s="5">
         <f t="shared" si="2"/>
-        <v>0.46211058492308321</v>
-      </c>
-      <c r="U8" s="5">
-        <f t="shared" si="0"/>
-        <v>8.6398392311464817E-2</v>
-      </c>
-      <c r="V8" s="5">
-        <f t="shared" si="0"/>
-        <v>1.5832608104036527E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
+        <v>1.9267941879270722E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
         <f>'Proximal Validation'!A9</f>
         <v>0.6</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B10" s="5">
         <f>'Proximal Validation'!B9</f>
         <v>0.16</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C10" s="5">
         <f>'Proximal Validation'!C9</f>
         <v>1.5707963267948966</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D10" s="5">
         <f>'Proximal Validation'!D9</f>
         <v>0</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E10" s="5">
         <f>'Proximal Validation'!E9</f>
         <v>0</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F10" s="5">
         <f>'Proximal Validation'!F9</f>
         <v>0</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G10" s="5">
         <f>'Proximal Validation'!G9</f>
         <v>-2.1819151006638999E-3</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H10" s="5">
         <f>'Proximal Validation'!H9</f>
         <v>-0.134275212883949</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I10" s="5">
         <f>'Proximal Validation'!I9</f>
         <v>-2.8121363720856602E-4</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J10" s="5">
         <f>'Proximal Validation'!J9</f>
         <v>-0.47822567820549</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K10" s="5">
         <f>'Proximal Validation'!K9</f>
         <v>1.2040870264172601E-2</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L10" s="5">
         <f>'Proximal Validation'!L9</f>
         <v>0.39143002033233598</v>
       </c>
-      <c r="M9" s="5">
-        <v>0.92404273537717529</v>
-      </c>
-      <c r="N9" s="5">
-        <v>0.11030829182948827</v>
-      </c>
-      <c r="O9" s="5">
-        <v>1.5847443455959052</v>
-      </c>
-      <c r="P9" s="11">
-        <v>3.3432947546319747E-6</v>
-      </c>
-      <c r="Q9" s="5">
+      <c r="M10" s="5">
+        <v>0.66507098493429329</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0.15884717317673197</v>
+      </c>
+      <c r="O10" s="5">
+        <v>1.5774823942649623</v>
+      </c>
+      <c r="P10" s="11">
+        <v>7.8056946302724385E-5</v>
+      </c>
+      <c r="Q10" s="5">
+        <f t="shared" si="3"/>
+        <v>6.5070984934293308E-2</v>
+      </c>
+      <c r="R10" s="5">
+        <f t="shared" si="3"/>
+        <v>-1.1528268232680328E-3</v>
+      </c>
+      <c r="S10" s="5">
+        <f t="shared" si="3"/>
+        <v>6.6860674700657263E-3</v>
+      </c>
+      <c r="T10" s="5">
+        <f t="shared" si="4"/>
+        <v>6.5070984934293308E-2</v>
+      </c>
+      <c r="U10" s="5">
+        <f t="shared" si="0"/>
+        <v>1.1528268232680328E-3</v>
+      </c>
+      <c r="V10" s="5">
+        <f t="shared" si="0"/>
+        <v>6.6860674700657263E-3</v>
+      </c>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7"/>
+      <c r="AA10" s="5">
+        <f>'Proximal Validation'!A9</f>
+        <v>0.6</v>
+      </c>
+      <c r="AB10" s="5">
+        <f>'Proximal Validation'!B9</f>
+        <v>0.16</v>
+      </c>
+      <c r="AC10" s="5">
+        <f>'Proximal Validation'!C9</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AD10" s="5">
+        <f>'Proximal Validation'!D9</f>
+        <v>0</v>
+      </c>
+      <c r="AE10" s="5">
+        <f>'Proximal Validation'!E9</f>
+        <v>0</v>
+      </c>
+      <c r="AF10" s="5">
+        <f>'Proximal Validation'!F9</f>
+        <v>0</v>
+      </c>
+      <c r="AG10" s="5">
+        <f>'Proximal Validation'!G9</f>
+        <v>-2.1819151006638999E-3</v>
+      </c>
+      <c r="AH10" s="5">
+        <f>'Proximal Validation'!H9</f>
+        <v>-0.134275212883949</v>
+      </c>
+      <c r="AI10" s="5">
+        <f>'Proximal Validation'!I9</f>
+        <v>-2.8121363720856602E-4</v>
+      </c>
+      <c r="AJ10" s="5">
+        <f>'Proximal Validation'!J9</f>
+        <v>-0.47822567820549</v>
+      </c>
+      <c r="AK10" s="5">
+        <f>'Proximal Validation'!K9</f>
+        <v>1.2040870264172601E-2</v>
+      </c>
+      <c r="AL10" s="5">
+        <f>'Proximal Validation'!L9</f>
+        <v>0.39143002033233598</v>
+      </c>
+      <c r="AM10" s="5">
+        <v>0.57262647284169976</v>
+      </c>
+      <c r="AN10" s="5">
+        <v>0.15712241098479002</v>
+      </c>
+      <c r="AO10" s="5">
+        <v>1.5745722592756153</v>
+      </c>
+      <c r="AP10" s="11">
+        <v>3.0106499277766225E-4</v>
+      </c>
+      <c r="AQ10" s="5">
+        <f t="shared" si="5"/>
+        <v>-2.7373527158300215E-2</v>
+      </c>
+      <c r="AR10" s="5">
+        <f t="shared" si="6"/>
+        <v>-2.8775890152099859E-3</v>
+      </c>
+      <c r="AS10" s="5">
+        <f t="shared" si="7"/>
+        <v>3.7759324807187244E-3</v>
+      </c>
+      <c r="AT10" s="5">
+        <f t="shared" si="8"/>
+        <v>2.7373527158300215E-2</v>
+      </c>
+      <c r="AU10" s="5">
         <f t="shared" si="1"/>
-        <v>0.32404273537717532</v>
-      </c>
-      <c r="R9" s="5">
-        <f t="shared" si="1"/>
-        <v>-4.9691708170511731E-2</v>
-      </c>
-      <c r="S9" s="5">
-        <f t="shared" si="1"/>
-        <v>1.3948018801008599E-2</v>
-      </c>
-      <c r="T9" s="5">
+        <v>2.8775890152099859E-3</v>
+      </c>
+      <c r="AV10" s="5">
         <f t="shared" si="2"/>
-        <v>0.32404273537717532</v>
-      </c>
-      <c r="U9" s="5">
-        <f t="shared" si="0"/>
-        <v>4.9691708170511731E-2</v>
-      </c>
-      <c r="V9" s="5">
-        <f t="shared" si="0"/>
-        <v>1.3948018801008599E-2</v>
-      </c>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
+        <v>3.7759324807187244E-3</v>
+      </c>
+      <c r="AW10" s="7"/>
+      <c r="AX10" s="7"/>
+      <c r="AY10" s="7"/>
+    </row>
+    <row r="11" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
         <f>'Proximal Validation'!A10</f>
         <v>0.8</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B11" s="5">
         <f>'Proximal Validation'!B10</f>
         <v>0.18</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C11" s="5">
         <f>'Proximal Validation'!C10</f>
         <v>1.5707963267948966</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D11" s="5">
         <f>'Proximal Validation'!D10</f>
         <v>0</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E11" s="5">
         <f>'Proximal Validation'!E10</f>
         <v>0</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F11" s="5">
         <f>'Proximal Validation'!F10</f>
         <v>0</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G11" s="5">
         <f>'Proximal Validation'!G10</f>
         <v>-1.05854228604585E-3</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H11" s="5">
         <f>'Proximal Validation'!H10</f>
         <v>-0.13548035919666301</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I11" s="5">
         <f>'Proximal Validation'!I10</f>
         <v>-1.24974839854985E-3</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J11" s="5">
         <f>'Proximal Validation'!J10</f>
         <v>-0.72550737857818604</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K11" s="5">
         <f>'Proximal Validation'!K10</f>
         <v>2.9684353619813902E-2</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L11" s="5">
         <f>'Proximal Validation'!L10</f>
         <v>0.13168570399284399</v>
       </c>
-      <c r="M10" s="5">
-        <v>0.98059920337760931</v>
-      </c>
-      <c r="N10" s="5">
-        <v>0.1341840796006761</v>
-      </c>
-      <c r="O10" s="5">
-        <v>1.6028214611252756</v>
-      </c>
-      <c r="P10" s="11">
-        <v>1.1929197429600041E-5</v>
-      </c>
-      <c r="Q10" s="5">
+      <c r="M11" s="5">
+        <v>0.66551650736094825</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0.19999999999997781</v>
+      </c>
+      <c r="O11" s="5">
+        <v>1.5825969070776229</v>
+      </c>
+      <c r="P11" s="11">
+        <v>1.1596894895439893E-3</v>
+      </c>
+      <c r="Q11" s="5">
+        <f t="shared" si="3"/>
+        <v>-0.13448349263905179</v>
+      </c>
+      <c r="R11" s="5">
+        <f t="shared" si="3"/>
+        <v>1.9999999999977813E-2</v>
+      </c>
+      <c r="S11" s="5">
+        <f t="shared" si="3"/>
+        <v>1.1800580282726347E-2</v>
+      </c>
+      <c r="T11" s="5">
+        <f t="shared" si="4"/>
+        <v>0.13448349263905179</v>
+      </c>
+      <c r="U11" s="5">
+        <f t="shared" si="0"/>
+        <v>1.9999999999977813E-2</v>
+      </c>
+      <c r="V11" s="5">
+        <f t="shared" si="0"/>
+        <v>1.1800580282726347E-2</v>
+      </c>
+      <c r="AA11" s="5">
+        <f>'Proximal Validation'!A10</f>
+        <v>0.8</v>
+      </c>
+      <c r="AB11" s="5">
+        <f>'Proximal Validation'!B10</f>
+        <v>0.18</v>
+      </c>
+      <c r="AC11" s="5">
+        <f>'Proximal Validation'!C10</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AD11" s="5">
+        <f>'Proximal Validation'!D10</f>
+        <v>0</v>
+      </c>
+      <c r="AE11" s="5">
+        <f>'Proximal Validation'!E10</f>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="5">
+        <f>'Proximal Validation'!F10</f>
+        <v>0</v>
+      </c>
+      <c r="AG11" s="5">
+        <f>'Proximal Validation'!G10</f>
+        <v>-1.05854228604585E-3</v>
+      </c>
+      <c r="AH11" s="5">
+        <f>'Proximal Validation'!H10</f>
+        <v>-0.13548035919666301</v>
+      </c>
+      <c r="AI11" s="5">
+        <f>'Proximal Validation'!I10</f>
+        <v>-1.24974839854985E-3</v>
+      </c>
+      <c r="AJ11" s="5">
+        <f>'Proximal Validation'!J10</f>
+        <v>-0.72550737857818604</v>
+      </c>
+      <c r="AK11" s="5">
+        <f>'Proximal Validation'!K10</f>
+        <v>2.9684353619813902E-2</v>
+      </c>
+      <c r="AL11" s="5">
+        <f>'Proximal Validation'!L10</f>
+        <v>0.13168570399284399</v>
+      </c>
+      <c r="AM11" s="5">
+        <v>0.6137662179915454</v>
+      </c>
+      <c r="AN11" s="5">
+        <v>0.19999999999997781</v>
+      </c>
+      <c r="AO11" s="5">
+        <v>1.5863923086009721</v>
+      </c>
+      <c r="AP11" s="11">
+        <v>1.2011069005304861E-3</v>
+      </c>
+      <c r="AQ11" s="5">
+        <f t="shared" si="5"/>
+        <v>-0.18623378200845464</v>
+      </c>
+      <c r="AR11" s="5">
+        <f t="shared" si="6"/>
+        <v>1.9999999999977813E-2</v>
+      </c>
+      <c r="AS11" s="5">
+        <f t="shared" si="7"/>
+        <v>1.5595981806075576E-2</v>
+      </c>
+      <c r="AT11" s="5">
+        <f t="shared" si="8"/>
+        <v>0.18623378200845464</v>
+      </c>
+      <c r="AU11" s="5">
         <f t="shared" si="1"/>
-        <v>0.18059920337760926</v>
-      </c>
-      <c r="R10" s="5">
-        <f t="shared" si="1"/>
-        <v>-4.5815920399323889E-2</v>
-      </c>
-      <c r="S10" s="5">
-        <f t="shared" si="1"/>
-        <v>3.2025134330379013E-2</v>
-      </c>
-      <c r="T10" s="5">
+        <v>1.9999999999977813E-2</v>
+      </c>
+      <c r="AV11" s="5">
         <f t="shared" si="2"/>
-        <v>0.18059920337760926</v>
-      </c>
-      <c r="U10" s="5">
-        <f t="shared" si="0"/>
-        <v>4.5815920399323889E-2</v>
-      </c>
-      <c r="V10" s="5">
-        <f t="shared" si="0"/>
-        <v>3.2025134330379013E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
+        <v>1.5595981806075576E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
         <f>'Proximal Validation'!A11</f>
         <v>0.3</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B12" s="5">
         <f>'Proximal Validation'!B11</f>
         <v>0.2</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C12" s="5">
         <f>'Proximal Validation'!C11</f>
         <v>1.5707963267948966</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D12" s="5">
         <f>'Proximal Validation'!D11</f>
         <v>0</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E12" s="5">
         <f>'Proximal Validation'!E11</f>
         <v>0</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F12" s="5">
         <f>'Proximal Validation'!F11</f>
         <v>0</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G12" s="5">
         <f>'Proximal Validation'!G11</f>
         <v>-8.8630802929401398E-4</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H12" s="5">
         <f>'Proximal Validation'!H11</f>
         <v>-6.7533724009990706E-2</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I12" s="5">
         <f>'Proximal Validation'!I11</f>
         <v>-4.7554963384754999E-4</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J12" s="5">
         <f>'Proximal Validation'!J11</f>
         <v>-0.16650235652923601</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K12" s="5">
         <f>'Proximal Validation'!K11</f>
         <v>2.7373749762773501E-3</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L12" s="5">
         <f>'Proximal Validation'!L11</f>
         <v>0.18086977303028101</v>
       </c>
-      <c r="M11" s="5">
-        <v>0.47479016254336448</v>
-      </c>
-      <c r="N11" s="5">
-        <v>0.11236682582436873</v>
-      </c>
-      <c r="O11" s="5">
-        <v>1.5846787833168812</v>
-      </c>
-      <c r="P11" s="11">
-        <v>5.6695137414913777E-6</v>
-      </c>
-      <c r="Q11" s="5">
+      <c r="M12" s="5">
+        <v>0.30864665682971698</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0.19999999940303573</v>
+      </c>
+      <c r="O12" s="5">
+        <v>1.588784373862187</v>
+      </c>
+      <c r="P12" s="11">
+        <v>5.6320515319711688E-4</v>
+      </c>
+      <c r="Q12" s="5">
+        <f t="shared" si="3"/>
+        <v>8.6466568297169921E-3</v>
+      </c>
+      <c r="R12" s="5">
+        <f t="shared" si="3"/>
+        <v>-5.9696428356126319E-10</v>
+      </c>
+      <c r="S12" s="5">
+        <f t="shared" si="3"/>
+        <v>1.7988047067290402E-2</v>
+      </c>
+      <c r="T12" s="5">
+        <f t="shared" si="4"/>
+        <v>8.6466568297169921E-3</v>
+      </c>
+      <c r="U12" s="5">
+        <f t="shared" si="0"/>
+        <v>5.9696428356126319E-10</v>
+      </c>
+      <c r="V12" s="5">
+        <f t="shared" si="0"/>
+        <v>1.7988047067290402E-2</v>
+      </c>
+      <c r="W12" s="7"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
+      <c r="AA12" s="5">
+        <f>'Proximal Validation'!A11</f>
+        <v>0.3</v>
+      </c>
+      <c r="AB12" s="5">
+        <f>'Proximal Validation'!B11</f>
+        <v>0.2</v>
+      </c>
+      <c r="AC12" s="5">
+        <f>'Proximal Validation'!C11</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AD12" s="5">
+        <f>'Proximal Validation'!D11</f>
+        <v>0</v>
+      </c>
+      <c r="AE12" s="5">
+        <f>'Proximal Validation'!E11</f>
+        <v>0</v>
+      </c>
+      <c r="AF12" s="5">
+        <f>'Proximal Validation'!F11</f>
+        <v>0</v>
+      </c>
+      <c r="AG12" s="5">
+        <f>'Proximal Validation'!G11</f>
+        <v>-8.8630802929401398E-4</v>
+      </c>
+      <c r="AH12" s="5">
+        <f>'Proximal Validation'!H11</f>
+        <v>-6.7533724009990706E-2</v>
+      </c>
+      <c r="AI12" s="5">
+        <f>'Proximal Validation'!I11</f>
+        <v>-4.7554963384754999E-4</v>
+      </c>
+      <c r="AJ12" s="5">
+        <f>'Proximal Validation'!J11</f>
+        <v>-0.16650235652923601</v>
+      </c>
+      <c r="AK12" s="5">
+        <f>'Proximal Validation'!K11</f>
+        <v>2.7373749762773501E-3</v>
+      </c>
+      <c r="AL12" s="5">
+        <f>'Proximal Validation'!L11</f>
+        <v>0.18086977303028101</v>
+      </c>
+      <c r="AM12" s="5">
+        <v>0.29308730264969246</v>
+      </c>
+      <c r="AN12" s="5">
+        <v>0.19681112961075553</v>
+      </c>
+      <c r="AO12" s="5">
+        <v>1.5860176181752843</v>
+      </c>
+      <c r="AP12" s="11">
+        <v>7.8804648806462597E-4</v>
+      </c>
+      <c r="AQ12" s="5">
+        <f t="shared" si="5"/>
+        <v>-6.9126973503075284E-3</v>
+      </c>
+      <c r="AR12" s="5">
+        <f t="shared" si="6"/>
+        <v>-3.1888703892444803E-3</v>
+      </c>
+      <c r="AS12" s="5">
+        <f t="shared" si="7"/>
+        <v>1.5221291380387747E-2</v>
+      </c>
+      <c r="AT12" s="5">
+        <f t="shared" si="8"/>
+        <v>6.9126973503075284E-3</v>
+      </c>
+      <c r="AU12" s="5">
         <f t="shared" si="1"/>
-        <v>0.17479016254336449</v>
-      </c>
-      <c r="R11" s="5">
-        <f t="shared" si="1"/>
-        <v>-8.7633174175631282E-2</v>
-      </c>
-      <c r="S11" s="5">
-        <f t="shared" si="1"/>
-        <v>1.388245652198461E-2</v>
-      </c>
-      <c r="T11" s="5">
+        <v>3.1888703892444803E-3</v>
+      </c>
+      <c r="AV12" s="5">
         <f t="shared" si="2"/>
-        <v>0.17479016254336449</v>
-      </c>
-      <c r="U11" s="5">
-        <f t="shared" si="0"/>
-        <v>8.7633174175631282E-2</v>
-      </c>
-      <c r="V11" s="5">
-        <f t="shared" si="0"/>
-        <v>1.388245652198461E-2</v>
-      </c>
-      <c r="W11" s="7"/>
-      <c r="X11" s="7"/>
-      <c r="Y11" s="7"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
+        <v>1.5221291380387747E-2</v>
+      </c>
+      <c r="AW12" s="7"/>
+      <c r="AX12" s="7"/>
+      <c r="AY12" s="7"/>
+    </row>
+    <row r="13" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
         <f>'Proximal Validation'!A12</f>
         <v>0.7</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B13" s="5">
         <f>'Proximal Validation'!B12</f>
         <v>0.2</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C13" s="5">
         <f>'Proximal Validation'!C12</f>
         <v>1.5707963267948966</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D13" s="5">
         <f>'Proximal Validation'!D12</f>
         <v>0</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E13" s="5">
         <f>'Proximal Validation'!E12</f>
         <v>0</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F13" s="5">
         <f>'Proximal Validation'!F12</f>
         <v>0</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G13" s="5">
         <f>'Proximal Validation'!G12</f>
         <v>-2.7598871383815999E-3</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H13" s="5">
         <f>'Proximal Validation'!H12</f>
         <v>-0.127221524715424</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I13" s="5">
         <f>'Proximal Validation'!I12</f>
         <v>-8.8058260735124404E-4</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J13" s="5">
         <f>'Proximal Validation'!J12</f>
         <v>-0.67187190055847201</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K13" s="5">
         <f>'Proximal Validation'!K12</f>
         <v>1.79205909371376E-2</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L13" s="5">
         <f>'Proximal Validation'!L12</f>
         <v>6.6542282700538594E-2</v>
       </c>
-      <c r="M12" s="5">
-        <v>0.99869359530838131</v>
-      </c>
-      <c r="N12" s="5">
-        <v>0.12598629056590258</v>
-      </c>
-      <c r="O12" s="5">
-        <v>1.5920671034647809</v>
-      </c>
-      <c r="P12" s="11">
-        <v>1.8183302374965183E-5</v>
-      </c>
-      <c r="Q12" s="5">
+      <c r="M13" s="5">
+        <v>0.72285733193286927</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0.15418047171830906</v>
+      </c>
+      <c r="O13" s="5">
+        <v>1.6260376900597415</v>
+      </c>
+      <c r="P13" s="11">
+        <v>5.1373893583374309E-4</v>
+      </c>
+      <c r="Q13" s="5">
+        <f t="shared" si="3"/>
+        <v>2.2857331932869318E-2</v>
+      </c>
+      <c r="R13" s="5">
+        <f t="shared" si="3"/>
+        <v>-4.5819528281690947E-2</v>
+      </c>
+      <c r="S13" s="5">
+        <f t="shared" si="3"/>
+        <v>5.5241363264844967E-2</v>
+      </c>
+      <c r="T13" s="5">
+        <f t="shared" si="4"/>
+        <v>2.2857331932869318E-2</v>
+      </c>
+      <c r="U13" s="5">
+        <f t="shared" si="0"/>
+        <v>4.5819528281690947E-2</v>
+      </c>
+      <c r="V13" s="5">
+        <f t="shared" si="0"/>
+        <v>5.5241363264844967E-2</v>
+      </c>
+      <c r="AA13" s="5">
+        <f>'Proximal Validation'!A12</f>
+        <v>0.7</v>
+      </c>
+      <c r="AB13" s="5">
+        <f>'Proximal Validation'!B12</f>
+        <v>0.2</v>
+      </c>
+      <c r="AC13" s="5">
+        <f>'Proximal Validation'!C12</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AD13" s="5">
+        <f>'Proximal Validation'!D12</f>
+        <v>0</v>
+      </c>
+      <c r="AE13" s="5">
+        <f>'Proximal Validation'!E12</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="5">
+        <f>'Proximal Validation'!F12</f>
+        <v>0</v>
+      </c>
+      <c r="AG13" s="5">
+        <f>'Proximal Validation'!G12</f>
+        <v>-2.7598871383815999E-3</v>
+      </c>
+      <c r="AH13" s="5">
+        <f>'Proximal Validation'!H12</f>
+        <v>-0.127221524715424</v>
+      </c>
+      <c r="AI13" s="5">
+        <f>'Proximal Validation'!I12</f>
+        <v>-8.8058260735124404E-4</v>
+      </c>
+      <c r="AJ13" s="5">
+        <f>'Proximal Validation'!J12</f>
+        <v>-0.67187190055847201</v>
+      </c>
+      <c r="AK13" s="5">
+        <f>'Proximal Validation'!K12</f>
+        <v>1.79205909371376E-2</v>
+      </c>
+      <c r="AL13" s="5">
+        <f>'Proximal Validation'!L12</f>
+        <v>6.6542282700538594E-2</v>
+      </c>
+      <c r="AM13" s="5">
+        <v>0.41552371809922101</v>
+      </c>
+      <c r="AN13" s="5">
+        <v>0.16692401285066383</v>
+      </c>
+      <c r="AO13" s="5">
+        <v>1.6290407914788201</v>
+      </c>
+      <c r="AP13" s="11">
+        <v>6.3500510394708066E-4</v>
+      </c>
+      <c r="AQ13" s="5">
+        <f t="shared" si="5"/>
+        <v>-0.28447628190077895</v>
+      </c>
+      <c r="AR13" s="5">
+        <f t="shared" si="6"/>
+        <v>-3.3075987149336183E-2</v>
+      </c>
+      <c r="AS13" s="5">
+        <f t="shared" si="7"/>
+        <v>5.8244464683923525E-2</v>
+      </c>
+      <c r="AT13" s="5">
+        <f t="shared" si="8"/>
+        <v>0.28447628190077895</v>
+      </c>
+      <c r="AU13" s="5">
         <f t="shared" si="1"/>
-        <v>0.29869359530838135</v>
-      </c>
-      <c r="R12" s="5">
-        <f t="shared" si="1"/>
-        <v>-7.4013709434097436E-2</v>
-      </c>
-      <c r="S12" s="5">
-        <f t="shared" si="1"/>
-        <v>2.1270776669884306E-2</v>
-      </c>
-      <c r="T12" s="5">
+        <v>3.3075987149336183E-2</v>
+      </c>
+      <c r="AV13" s="5">
         <f t="shared" si="2"/>
-        <v>0.29869359530838135</v>
-      </c>
-      <c r="U12" s="5">
-        <f t="shared" si="0"/>
-        <v>7.4013709434097436E-2</v>
-      </c>
-      <c r="V12" s="5">
-        <f t="shared" si="0"/>
-        <v>2.1270776669884306E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="31" t="s">
+        <v>5.8244464683923525E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="32"/>
-      <c r="C14" s="33"/>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="B15" s="32"/>
+      <c r="C15" s="33"/>
+    </row>
+    <row r="16" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A16">
         <v>1</v>
       </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>0</v>
-      </c>
       <c r="B16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -6397,106 +7424,85 @@
         <v>0</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C20" s="1" t="s">
+    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="17" t="s">
+      <c r="G21" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="18"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C21" s="10">
-        <v>1</v>
-      </c>
-      <c r="D21" s="5">
-        <f t="shared" ref="D21:L21" si="3">D3</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F21" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="5">
-        <f t="shared" si="3"/>
-        <v>-2.8477585874497901E-4</v>
-      </c>
-      <c r="H21" s="5">
-        <f t="shared" si="3"/>
-        <v>-5.8327373117208502E-2</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="3"/>
-        <v>-1.50670297443867E-4</v>
-      </c>
-      <c r="J21" s="5">
-        <f t="shared" si="3"/>
-        <v>6.01342367008328E-3</v>
-      </c>
-      <c r="K21" s="5">
-        <f t="shared" si="3"/>
-        <v>2.2609531879425001E-3</v>
-      </c>
-      <c r="L21" s="5">
-        <f t="shared" si="3"/>
-        <v>0.37637501955032299</v>
-      </c>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C22" s="10">
         <v>1</v>
       </c>
       <c r="D22" s="5">
-        <v>1</v>
+        <f t="shared" ref="D22:L22" si="9">D4</f>
+        <v>0</v>
       </c>
       <c r="E22" s="5">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F22" s="5">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="G22" s="5">
-        <v>6.7423289874568603E-4</v>
+        <f t="shared" si="9"/>
+        <v>-2.8477585874497901E-4</v>
       </c>
       <c r="H22" s="5">
-        <v>-4.6691335737705203E-2</v>
+        <f t="shared" si="9"/>
+        <v>-5.8327373117208502E-2</v>
       </c>
       <c r="I22" s="5">
-        <v>-1.9840942695736901E-4</v>
+        <f t="shared" si="9"/>
+        <v>-1.50670297443867E-4</v>
       </c>
       <c r="J22" s="5">
-        <v>1.92548986524343E-2</v>
+        <f t="shared" si="9"/>
+        <v>6.01342367008328E-3</v>
       </c>
       <c r="K22" s="5">
-        <v>-2.2761523723602298E-5</v>
+        <f t="shared" si="9"/>
+        <v>2.2609531879425001E-3</v>
       </c>
       <c r="L22" s="5">
-        <v>0.30847230553626998</v>
+        <f t="shared" si="9"/>
+        <v>0.37637501955032299</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -6504,31 +7510,31 @@
         <v>1</v>
       </c>
       <c r="D23" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="5">
         <v>0</v>
       </c>
       <c r="G23" s="5">
-        <v>-6.0618203133344704E-4</v>
+        <v>6.7423289874568603E-4</v>
       </c>
       <c r="H23" s="5">
-        <v>-4.5500006526708603E-2</v>
+        <v>-4.6691335737705203E-2</v>
       </c>
       <c r="I23" s="5">
-        <v>6.9612462539225803E-5</v>
+        <v>-1.9840942695736901E-4</v>
       </c>
       <c r="J23" s="5">
-        <v>2.4782635271549201E-2</v>
+        <v>1.92548986524343E-2</v>
       </c>
       <c r="K23" s="5">
-        <v>9.4752311706543003E-3</v>
+        <v>-2.2761523723602298E-5</v>
       </c>
       <c r="L23" s="5">
-        <v>0.30106654763221702</v>
+        <v>0.30847230553626998</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -6539,33 +7545,33 @@
         <v>0</v>
       </c>
       <c r="E24" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="5">
-        <v>-1.3268133625388099E-4</v>
+        <v>-6.0618203133344704E-4</v>
       </c>
       <c r="H24" s="5">
-        <v>-7.0247285068035098E-2</v>
+        <v>-4.5500006526708603E-2</v>
       </c>
       <c r="I24" s="5">
-        <v>-1.3355066766962401E-4</v>
+        <v>6.9612462539225803E-5</v>
       </c>
       <c r="J24" s="5">
-        <v>2.3433083668351201E-2</v>
+        <v>2.4782635271549201E-2</v>
       </c>
       <c r="K24" s="5">
-        <v>6.2583163380622898E-3</v>
+        <v>9.4752311706543003E-3</v>
       </c>
       <c r="L24" s="5">
-        <v>0.46214234828949002</v>
+        <v>0.30106654763221702</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C25" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="5">
         <v>0</v>
@@ -6574,31 +7580,25 @@
         <v>0</v>
       </c>
       <c r="F25" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="5">
-        <f>G4</f>
-        <v>-1.3759520370513201E-3</v>
+        <v>-1.3268133625388099E-4</v>
       </c>
       <c r="H25" s="5">
-        <f t="shared" ref="H25:L25" si="4">H4</f>
-        <v>-0.12723180651664701</v>
+        <v>-7.0247285068035098E-2</v>
       </c>
       <c r="I25" s="5">
-        <f t="shared" si="4"/>
-        <v>-1.5217980835586799E-3</v>
+        <v>-1.3355066766962401E-4</v>
       </c>
       <c r="J25" s="5">
-        <f t="shared" si="4"/>
-        <v>-8.26666504144669E-2</v>
+        <v>2.3433083668351201E-2</v>
       </c>
       <c r="K25" s="5">
-        <f t="shared" si="4"/>
-        <v>-4.7411769628524798E-3</v>
+        <v>6.2583163380622898E-3</v>
       </c>
       <c r="L25" s="5">
-        <f t="shared" si="4"/>
-        <v>0.81632339954376198</v>
+        <v>0.46214234828949002</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -6606,7 +7606,7 @@
         <v>2</v>
       </c>
       <c r="D26" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="5">
         <v>0</v>
@@ -6615,22 +7615,28 @@
         <v>0</v>
       </c>
       <c r="G26" s="5">
-        <v>-1.7096614465117501E-4</v>
+        <f>G5</f>
+        <v>-1.3759520370513201E-3</v>
       </c>
       <c r="H26" s="5">
-        <v>-0.117183104157448</v>
+        <f t="shared" ref="H26:L26" si="10">H5</f>
+        <v>-0.12723180651664701</v>
       </c>
       <c r="I26" s="5">
-        <v>-1.8990500830113901E-3</v>
+        <f t="shared" si="10"/>
+        <v>-1.5217980835586799E-3</v>
       </c>
       <c r="J26" s="5">
-        <v>-6.6881448030471802E-2</v>
+        <f t="shared" si="10"/>
+        <v>-8.26666504144669E-2</v>
       </c>
       <c r="K26" s="5">
-        <v>-1.0641232132911699E-2</v>
+        <f t="shared" si="10"/>
+        <v>-4.7411769628524798E-3</v>
       </c>
       <c r="L26" s="5">
-        <v>0.760015308856964</v>
+        <f t="shared" si="10"/>
+        <v>0.81632339954376198</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -6638,31 +7644,31 @@
         <v>2</v>
       </c>
       <c r="D27" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="5">
         <v>0</v>
       </c>
       <c r="G27" s="5">
-        <v>-3.11067164875567E-3</v>
+        <v>-1.7096614465117501E-4</v>
       </c>
       <c r="H27" s="5">
-        <v>-0.115753546357155</v>
+        <v>-0.117183104157448</v>
       </c>
       <c r="I27" s="5">
-        <v>-3.8996658986434303E-4</v>
+        <v>-1.8990500830113901E-3</v>
       </c>
       <c r="J27" s="5">
-        <v>-6.27723783254623E-2</v>
+        <v>-6.6881448030471802E-2</v>
       </c>
       <c r="K27" s="5">
-        <v>6.8403780460357701E-3</v>
+        <v>-1.0641232132911699E-2</v>
       </c>
       <c r="L27" s="5">
-        <v>0.75269460678100597</v>
+        <v>0.760015308856964</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -6673,33 +7679,33 @@
         <v>0</v>
       </c>
       <c r="E28" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" s="5">
-        <v>-1.96084030903876E-3</v>
+        <v>-3.11067164875567E-3</v>
       </c>
       <c r="H28" s="5">
-        <v>-0.137257635593414</v>
+        <v>-0.115753546357155</v>
       </c>
       <c r="I28" s="5">
-        <v>-1.4088806929066801E-3</v>
+        <v>-3.8996658986434303E-4</v>
       </c>
       <c r="J28" s="5">
-        <v>-7.98484832048416E-2</v>
+        <v>-6.27723783254623E-2</v>
       </c>
       <c r="K28" s="5">
-        <v>-1.8499046564102201E-3</v>
+        <v>6.8403780460357701E-3</v>
       </c>
       <c r="L28" s="5">
-        <v>0.88854026794433605</v>
+        <v>0.75269460678100597</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C29" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" s="5">
         <v>0</v>
@@ -6708,31 +7714,25 @@
         <v>0</v>
       </c>
       <c r="F29" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" s="5">
-        <f>G5</f>
-        <v>-2.8428673977032298E-4</v>
+        <v>-1.96084030903876E-3</v>
       </c>
       <c r="H29" s="5">
-        <f t="shared" ref="H29:L29" si="5">H5</f>
-        <v>-4.3962169438600499E-2</v>
+        <v>-0.137257635593414</v>
       </c>
       <c r="I29" s="5">
-        <f t="shared" si="5"/>
-        <v>-1.9410930690355599E-4</v>
+        <v>-1.4088806929066801E-3</v>
       </c>
       <c r="J29" s="5">
-        <f t="shared" si="5"/>
-        <v>-1.4232989400625199E-2</v>
+        <v>-7.98484832048416E-2</v>
       </c>
       <c r="K29" s="5">
-        <f t="shared" si="5"/>
-        <v>8.0315023660659801E-4</v>
+        <v>-1.8499046564102201E-3</v>
       </c>
       <c r="L29" s="5">
-        <f t="shared" si="5"/>
-        <v>0.24872186779975899</v>
+        <v>0.88854026794433605</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -6740,7 +7740,7 @@
         <v>3</v>
       </c>
       <c r="D30" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="5">
         <v>0</v>
@@ -6749,22 +7749,28 @@
         <v>0</v>
       </c>
       <c r="G30" s="5">
-        <v>4.6094937715679402E-4</v>
+        <f>G6</f>
+        <v>-2.8428673977032298E-4</v>
       </c>
       <c r="H30" s="5">
-        <v>-2.8747312724590302E-2</v>
+        <f t="shared" ref="H30:L30" si="11">H6</f>
+        <v>-4.3962169438600499E-2</v>
       </c>
       <c r="I30" s="5">
-        <v>-1.7448040307499501E-4</v>
+        <f t="shared" si="11"/>
+        <v>-1.9410930690355599E-4</v>
       </c>
       <c r="J30" s="5">
-        <v>-7.4924039654433695E-4</v>
+        <f t="shared" si="11"/>
+        <v>-1.4232989400625199E-2</v>
       </c>
       <c r="K30" s="5">
-        <v>-1.9123740494251299E-3</v>
+        <f t="shared" si="11"/>
+        <v>8.0315023660659801E-4</v>
       </c>
       <c r="L30" s="5">
-        <v>0.16522677242755901</v>
+        <f t="shared" si="11"/>
+        <v>0.24872186779975899</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -6772,31 +7778,31 @@
         <v>3</v>
       </c>
       <c r="D31" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" s="5">
         <v>0</v>
       </c>
       <c r="G31" s="5">
-        <v>-7.6827022712677696E-4</v>
+        <v>4.6094937715679402E-4</v>
       </c>
       <c r="H31" s="5">
-        <v>-2.7165766805410399E-2</v>
+        <v>-2.8747312724590302E-2</v>
       </c>
       <c r="I31" s="5">
-        <v>2.1368774469010501E-5</v>
+        <v>-1.7448040307499501E-4</v>
       </c>
       <c r="J31" s="5">
-        <v>4.7830417752265904E-3</v>
+        <v>-7.4924039654433695E-4</v>
       </c>
       <c r="K31" s="5">
-        <v>5.7868864387273797E-3</v>
+        <v>-1.9123740494251299E-3</v>
       </c>
       <c r="L31" s="5">
-        <v>0.15646727383136699</v>
+        <v>0.16522677242755901</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -6807,33 +7813,33 @@
         <v>0</v>
       </c>
       <c r="E32" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" s="5">
-        <v>-5.3039402700960604E-4</v>
+        <v>-7.6827022712677696E-4</v>
       </c>
       <c r="H32" s="5">
-        <v>-6.1754897236824001E-2</v>
+        <v>-2.7165766805410399E-2</v>
       </c>
       <c r="I32" s="5">
-        <v>-1.3558880891650899E-4</v>
+        <v>2.1368774469010501E-5</v>
       </c>
       <c r="J32" s="5">
-        <v>-1.08502134680748E-2</v>
+        <v>4.7830417752265904E-3</v>
       </c>
       <c r="K32" s="5">
-        <v>3.17833945155144E-3</v>
+        <v>5.7868864387273797E-3</v>
       </c>
       <c r="L32" s="5">
-        <v>0.35227984189987199</v>
+        <v>0.15646727383136699</v>
       </c>
     </row>
     <row r="33" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C33" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33" s="5">
         <v>0</v>
@@ -6842,31 +7848,25 @@
         <v>0</v>
       </c>
       <c r="F33" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" s="5">
-        <f>G6</f>
-        <v>-9.02065541595221E-4</v>
+        <v>-5.3039402700960604E-4</v>
       </c>
       <c r="H33" s="5">
-        <f t="shared" ref="H33:L33" si="6">H6</f>
-        <v>-9.5010705292224898E-2</v>
+        <v>-6.1754897236824001E-2</v>
       </c>
       <c r="I33" s="5">
-        <f t="shared" si="6"/>
-        <v>-3.1485431827604798E-4</v>
+        <v>-1.3558880891650899E-4</v>
       </c>
       <c r="J33" s="5">
-        <f t="shared" si="6"/>
-        <v>-0.14170777797699</v>
+        <v>-1.08502134680748E-2</v>
       </c>
       <c r="K33" s="5">
-        <f t="shared" si="6"/>
-        <v>3.2724365592002899E-3</v>
+        <v>3.17833945155144E-3</v>
       </c>
       <c r="L33" s="5">
-        <f t="shared" si="6"/>
-        <v>0.46851912140846302</v>
+        <v>0.35227984189987199</v>
       </c>
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.25">
@@ -6874,7 +7874,7 @@
         <v>4</v>
       </c>
       <c r="D34" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="5">
         <v>0</v>
@@ -6883,22 +7883,28 @@
         <v>0</v>
       </c>
       <c r="G34" s="5">
-        <v>1.11998070497066E-3</v>
+        <f>G7</f>
+        <v>-9.02065541595221E-4</v>
       </c>
       <c r="H34" s="5">
-        <v>-8.2509450614452404E-2</v>
+        <f t="shared" ref="H34:L34" si="12">H7</f>
+        <v>-9.5010705292224898E-2</v>
       </c>
       <c r="I34" s="5">
-        <v>-1.41473882831633E-3</v>
+        <f t="shared" si="12"/>
+        <v>-3.1485431827604798E-4</v>
       </c>
       <c r="J34" s="5">
-        <v>-0.115338027477264</v>
+        <f t="shared" si="12"/>
+        <v>-0.14170777797699</v>
       </c>
       <c r="K34" s="5">
-        <v>-6.8659633398056004E-3</v>
+        <f t="shared" si="12"/>
+        <v>3.2724365592002899E-3</v>
       </c>
       <c r="L34" s="5">
-        <v>0.41186845302581798</v>
+        <f t="shared" si="12"/>
+        <v>0.46851912140846302</v>
       </c>
     </row>
     <row r="35" spans="3:12" x14ac:dyDescent="0.25">
@@ -6906,31 +7912,31 @@
         <v>4</v>
       </c>
       <c r="D35" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="5">
         <v>0</v>
       </c>
       <c r="G35" s="5">
-        <v>-3.0216267332434702E-3</v>
+        <v>1.11998070497066E-3</v>
       </c>
       <c r="H35" s="5">
-        <v>-8.1563368439674405E-2</v>
+        <v>-8.2509450614452404E-2</v>
       </c>
       <c r="I35" s="5">
-        <v>1.24832289293408E-3</v>
+        <v>-1.41473882831633E-3</v>
       </c>
       <c r="J35" s="5">
-        <v>-0.112349167466164</v>
+        <v>-0.115338027477264</v>
       </c>
       <c r="K35" s="5">
-        <v>1.6722420230507899E-2</v>
+        <v>-6.8659633398056004E-3</v>
       </c>
       <c r="L35" s="5">
-        <v>0.407246112823486</v>
+        <v>0.41186845302581798</v>
       </c>
     </row>
     <row r="36" spans="3:12" x14ac:dyDescent="0.25">
@@ -6941,33 +7947,33 @@
         <v>0</v>
       </c>
       <c r="E36" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="5">
-        <v>-1.32783397566527E-3</v>
+        <v>-3.0216267332434702E-3</v>
       </c>
       <c r="H36" s="5">
-        <v>-0.106191068887711</v>
+        <v>-8.1563368439674405E-2</v>
       </c>
       <c r="I36" s="5">
-        <v>-5.5953569244593402E-5</v>
+        <v>1.24832289293408E-3</v>
       </c>
       <c r="J36" s="5">
-        <v>-0.15105041861534099</v>
+        <v>-0.112349167466164</v>
       </c>
       <c r="K36" s="5">
-        <v>7.1365274488925899E-3</v>
+        <v>1.6722420230507899E-2</v>
       </c>
       <c r="L36" s="5">
-        <v>0.52852129936218295</v>
+        <v>0.407246112823486</v>
       </c>
     </row>
     <row r="37" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C37" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D37" s="5">
         <v>0</v>
@@ -6976,31 +7982,25 @@
         <v>0</v>
       </c>
       <c r="F37" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" s="5">
-        <f>G7</f>
-        <v>-1.3697715476155301E-3</v>
+        <v>-1.32783397566527E-3</v>
       </c>
       <c r="H37" s="5">
-        <f t="shared" ref="H37:L37" si="7">H7</f>
-        <v>-0.129899337887764</v>
+        <v>-0.106191068887711</v>
       </c>
       <c r="I37" s="5">
-        <f t="shared" si="7"/>
-        <v>-1.1154995299875699E-3</v>
+        <v>-5.5953569244593402E-5</v>
       </c>
       <c r="J37" s="5">
-        <f t="shared" si="7"/>
-        <v>-0.27736902236938499</v>
+        <v>-0.15105041861534099</v>
       </c>
       <c r="K37" s="5">
-        <f t="shared" si="7"/>
-        <v>2.9984340071678201E-3</v>
+        <v>7.1365274488925899E-3</v>
       </c>
       <c r="L37" s="5">
-        <f t="shared" si="7"/>
-        <v>0.62586665153503396</v>
+        <v>0.52852129936218295</v>
       </c>
     </row>
     <row r="38" spans="3:12" x14ac:dyDescent="0.25">
@@ -7008,7 +8008,7 @@
         <v>5</v>
       </c>
       <c r="D38" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" s="5">
         <v>0</v>
@@ -7017,22 +8017,28 @@
         <v>0</v>
       </c>
       <c r="G38" s="5">
-        <v>1.0789594380184999E-3</v>
+        <f>G8</f>
+        <v>-1.3697715476155301E-3</v>
       </c>
       <c r="H38" s="5">
-        <v>-0.11674865335226101</v>
+        <f t="shared" ref="H38:L38" si="13">H8</f>
+        <v>-0.129899337887764</v>
       </c>
       <c r="I38" s="5">
-        <v>-2.3895120248198501E-3</v>
+        <f t="shared" si="13"/>
+        <v>-1.1154995299875699E-3</v>
       </c>
       <c r="J38" s="5">
-        <v>-0.239661380648613</v>
+        <f t="shared" si="13"/>
+        <v>-0.27736902236938499</v>
       </c>
       <c r="K38" s="5">
-        <v>-9.9661052227020298E-3</v>
+        <f t="shared" si="13"/>
+        <v>2.9984340071678201E-3</v>
       </c>
       <c r="L38" s="5">
-        <v>0.56697064638137795</v>
+        <f t="shared" si="13"/>
+        <v>0.62586665153503396</v>
       </c>
     </row>
     <row r="39" spans="3:12" x14ac:dyDescent="0.25">
@@ -7040,31 +8046,31 @@
         <v>5</v>
       </c>
       <c r="D39" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" s="5">
         <v>0</v>
       </c>
       <c r="G39" s="5">
-        <v>-4.3625882826745501E-3</v>
+        <v>1.0789594380184999E-3</v>
       </c>
       <c r="H39" s="5">
-        <v>-0.114450730383396</v>
+        <v>-0.11674865335226101</v>
       </c>
       <c r="I39" s="5">
-        <v>9.970135288313029E-4</v>
+        <v>-2.3895120248198501E-3</v>
       </c>
       <c r="J39" s="5">
-        <v>-0.23323938250541701</v>
+        <v>-0.239661380648613</v>
       </c>
       <c r="K39" s="5">
-        <v>2.1434955298900601E-2</v>
+        <v>-9.9661052227020298E-3</v>
       </c>
       <c r="L39" s="5">
-        <v>0.55733346939086903</v>
+        <v>0.56697064638137795</v>
       </c>
     </row>
     <row r="40" spans="3:12" x14ac:dyDescent="0.25">
@@ -7075,33 +8081,33 @@
         <v>0</v>
       </c>
       <c r="E40" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" s="5">
-        <v>-2.1919934079051E-3</v>
+        <v>-4.3625882826745501E-3</v>
       </c>
       <c r="H40" s="5">
-        <v>-0.14200709760189101</v>
+        <v>-0.114450730383396</v>
       </c>
       <c r="I40" s="5">
-        <v>-7.6931557850912202E-4</v>
+        <v>9.970135288313029E-4</v>
       </c>
       <c r="J40" s="5">
-        <v>-0.29801037907600397</v>
+        <v>-0.23323938250541701</v>
       </c>
       <c r="K40" s="5">
-        <v>8.01820307970047E-3</v>
+        <v>2.1434955298900601E-2</v>
       </c>
       <c r="L40" s="5">
-        <v>0.68905413150787398</v>
+        <v>0.55733346939086903</v>
       </c>
     </row>
     <row r="41" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C41" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D41" s="5">
         <v>0</v>
@@ -7110,31 +8116,25 @@
         <v>0</v>
       </c>
       <c r="F41" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" s="5">
-        <f>G8</f>
-        <v>-1.30162085406482E-3</v>
+        <v>-2.1919934079051E-3</v>
       </c>
       <c r="H41" s="5">
-        <f t="shared" ref="H41:L41" si="8">H8</f>
-        <v>-9.1771319508552607E-2</v>
+        <v>-0.14200709760189101</v>
       </c>
       <c r="I41" s="5">
-        <f t="shared" si="8"/>
-        <v>-6.8558257771655895E-4</v>
+        <v>-7.6931557850912202E-4</v>
       </c>
       <c r="J41" s="5">
-        <f t="shared" si="8"/>
-        <v>-0.188138782978058</v>
+        <v>-0.29801037907600397</v>
       </c>
       <c r="K41" s="5">
-        <f t="shared" si="8"/>
-        <v>3.5599116235971499E-3</v>
+        <v>8.01820307970047E-3</v>
       </c>
       <c r="L41" s="5">
-        <f t="shared" si="8"/>
-        <v>0.316497713327408</v>
+        <v>0.68905413150787398</v>
       </c>
     </row>
     <row r="42" spans="3:12" x14ac:dyDescent="0.25">
@@ -7142,7 +8142,7 @@
         <v>6</v>
       </c>
       <c r="D42" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" s="5">
         <v>0</v>
@@ -7151,22 +8151,28 @@
         <v>0</v>
       </c>
       <c r="G42" s="5">
-        <v>2.1334765478968599E-3</v>
+        <f>G9</f>
+        <v>-1.30162085406482E-3</v>
       </c>
       <c r="H42" s="5">
-        <v>-7.8673288226127597E-2</v>
+        <f t="shared" ref="H42:L42" si="14">H9</f>
+        <v>-9.1771319508552607E-2</v>
       </c>
       <c r="I42" s="5">
-        <v>-3.3856690861284698E-3</v>
+        <f t="shared" si="14"/>
+        <v>-6.8558257771655895E-4</v>
       </c>
       <c r="J42" s="5">
-        <v>-0.15782742202281999</v>
+        <f t="shared" si="14"/>
+        <v>-0.188138782978058</v>
       </c>
       <c r="K42" s="5">
-        <v>-1.3936560600996E-2</v>
+        <f t="shared" si="14"/>
+        <v>3.5599116235971499E-3</v>
       </c>
       <c r="L42" s="5">
-        <v>0.27476710081100503</v>
+        <f t="shared" si="14"/>
+        <v>0.316497713327408</v>
       </c>
     </row>
     <row r="43" spans="3:12" x14ac:dyDescent="0.25">
@@ -7174,31 +8180,31 @@
         <v>6</v>
       </c>
       <c r="D43" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" s="5">
         <v>0</v>
       </c>
       <c r="G43" s="5">
-        <v>-5.3475773893296701E-3</v>
+        <v>2.1334765478968599E-3</v>
       </c>
       <c r="H43" s="5">
-        <v>-7.7887043356895405E-2</v>
+        <v>-7.8673288226127597E-2</v>
       </c>
       <c r="I43" s="5">
-        <v>3.1169473659247199E-3</v>
+        <v>-3.3856690861284698E-3</v>
       </c>
       <c r="J43" s="5">
-        <v>-0.15005394816398601</v>
+        <v>-0.15782742202281999</v>
       </c>
       <c r="K43" s="5">
-        <v>2.6179488748312E-2</v>
+        <v>-1.3936560600996E-2</v>
       </c>
       <c r="L43" s="5">
-        <v>0.272424846887589</v>
+        <v>0.27476710081100503</v>
       </c>
     </row>
     <row r="44" spans="3:12" x14ac:dyDescent="0.25">
@@ -7209,33 +8215,33 @@
         <v>0</v>
       </c>
       <c r="E44" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" s="5">
-        <v>-2.4072818923741601E-3</v>
+        <v>-5.3475773893296701E-3</v>
       </c>
       <c r="H44" s="5">
-        <v>-0.10561495274305301</v>
+        <v>-7.7887043356895405E-2</v>
       </c>
       <c r="I44" s="5">
-        <v>5.1816481573041501E-5</v>
+        <v>3.1169473659247199E-3</v>
       </c>
       <c r="J44" s="5">
-        <v>-0.21281039714813199</v>
+        <v>-0.15005394816398601</v>
       </c>
       <c r="K44" s="5">
-        <v>9.7759189084172197E-3</v>
+        <v>2.6179488748312E-2</v>
       </c>
       <c r="L44" s="5">
-        <v>0.36723855137825001</v>
+        <v>0.272424846887589</v>
       </c>
     </row>
     <row r="45" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C45" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D45" s="5">
         <v>0</v>
@@ -7244,31 +8250,25 @@
         <v>0</v>
       </c>
       <c r="F45" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" s="5">
-        <f>G9</f>
-        <v>-2.1819151006638999E-3</v>
+        <v>-2.4072818923741601E-3</v>
       </c>
       <c r="H45" s="5">
-        <f t="shared" ref="H45:L45" si="9">H9</f>
-        <v>-0.134275212883949</v>
+        <v>-0.10561495274305301</v>
       </c>
       <c r="I45" s="5">
-        <f t="shared" si="9"/>
-        <v>-2.8121363720856602E-4</v>
+        <v>5.1816481573041501E-5</v>
       </c>
       <c r="J45" s="5">
-        <f t="shared" si="9"/>
-        <v>-0.47822567820549</v>
+        <v>-0.21281039714813199</v>
       </c>
       <c r="K45" s="5">
-        <f t="shared" si="9"/>
-        <v>1.2040870264172601E-2</v>
+        <v>9.7759189084172197E-3</v>
       </c>
       <c r="L45" s="5">
-        <f t="shared" si="9"/>
-        <v>0.39143002033233598</v>
+        <v>0.36723855137825001</v>
       </c>
     </row>
     <row r="46" spans="3:12" x14ac:dyDescent="0.25">
@@ -7276,7 +8276,7 @@
         <v>7</v>
       </c>
       <c r="D46" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" s="5">
         <v>0</v>
@@ -7285,22 +8285,28 @@
         <v>0</v>
       </c>
       <c r="G46" s="5">
-        <v>2.81068682670593E-3</v>
+        <f>G10</f>
+        <v>-2.1819151006638999E-3</v>
       </c>
       <c r="H46" s="5">
-        <v>-0.121507167816162</v>
+        <f t="shared" ref="H46:L46" si="15">H10</f>
+        <v>-0.134275212883949</v>
       </c>
       <c r="I46" s="5">
-        <v>-3.3819505479186799E-3</v>
+        <f t="shared" si="15"/>
+        <v>-2.8121363720856602E-4</v>
       </c>
       <c r="J46" s="5">
-        <v>-0.42114067077636702</v>
+        <f t="shared" si="15"/>
+        <v>-0.47822567820549</v>
       </c>
       <c r="K46" s="5">
-        <v>-1.4590077102184301E-2</v>
+        <f t="shared" si="15"/>
+        <v>1.2040870264172601E-2</v>
       </c>
       <c r="L46" s="5">
-        <v>0.35988470911979697</v>
+        <f t="shared" si="15"/>
+        <v>0.39143002033233598</v>
       </c>
     </row>
     <row r="47" spans="3:12" x14ac:dyDescent="0.25">
@@ -7308,31 +8314,31 @@
         <v>7</v>
       </c>
       <c r="D47" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" s="5">
         <v>0</v>
       </c>
       <c r="G47" s="5">
-        <v>-8.4775444120168703E-3</v>
+        <v>2.81068682670593E-3</v>
       </c>
       <c r="H47" s="5">
-        <v>-0.120613545179367</v>
+        <v>-0.121507167816162</v>
       </c>
       <c r="I47" s="5">
-        <v>4.2216349393129297E-3</v>
+        <v>-3.3819505479186799E-3</v>
       </c>
       <c r="J47" s="5">
-        <v>-0.41639053821563698</v>
+        <v>-0.42114067077636702</v>
       </c>
       <c r="K47" s="5">
-        <v>4.9453981220722198E-2</v>
+        <v>-1.4590077102184301E-2</v>
       </c>
       <c r="L47" s="5">
-        <v>0.358586966991425</v>
+        <v>0.35988470911979697</v>
       </c>
     </row>
     <row r="48" spans="3:12" x14ac:dyDescent="0.25">
@@ -7343,33 +8349,33 @@
         <v>0</v>
       </c>
       <c r="E48" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" s="5">
-        <v>-3.8649328052997602E-3</v>
+        <v>-8.4775444120168703E-3</v>
       </c>
       <c r="H48" s="5">
-        <v>-0.14329923689365401</v>
+        <v>-0.120613545179367</v>
       </c>
       <c r="I48" s="5">
-        <v>8.1204215530306101E-4</v>
+        <v>4.2216349393129297E-3</v>
       </c>
       <c r="J48" s="5">
-        <v>-0.50669300556182895</v>
+        <v>-0.41639053821563698</v>
       </c>
       <c r="K48" s="5">
-        <v>2.37305648624897E-2</v>
+        <v>4.9453981220722198E-2</v>
       </c>
       <c r="L48" s="5">
-        <v>0.41881522536277799</v>
+        <v>0.358586966991425</v>
       </c>
     </row>
     <row r="49" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C49" s="10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D49" s="5">
         <v>0</v>
@@ -7378,31 +8384,25 @@
         <v>0</v>
       </c>
       <c r="F49" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" s="5">
-        <f>G10</f>
-        <v>-1.05854228604585E-3</v>
+        <v>-3.8649328052997602E-3</v>
       </c>
       <c r="H49" s="5">
-        <f t="shared" ref="H49:L49" si="10">H10</f>
-        <v>-0.13548035919666301</v>
+        <v>-0.14329923689365401</v>
       </c>
       <c r="I49" s="5">
-        <f t="shared" si="10"/>
-        <v>-1.24974839854985E-3</v>
+        <v>8.1204215530306101E-4</v>
       </c>
       <c r="J49" s="5">
-        <f t="shared" si="10"/>
-        <v>-0.72550737857818604</v>
+        <v>-0.50669300556182895</v>
       </c>
       <c r="K49" s="5">
-        <f t="shared" si="10"/>
-        <v>2.9684353619813902E-2</v>
+        <v>2.37305648624897E-2</v>
       </c>
       <c r="L49" s="5">
-        <f t="shared" si="10"/>
-        <v>0.13168570399284399</v>
+        <v>0.41881522536277799</v>
       </c>
     </row>
     <row r="50" spans="3:12" x14ac:dyDescent="0.25">
@@ -7410,7 +8410,7 @@
         <v>8</v>
       </c>
       <c r="D50" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" s="5">
         <v>0</v>
@@ -7419,22 +8419,28 @@
         <v>0</v>
       </c>
       <c r="G50" s="5">
-        <v>4.3551013804972198E-3</v>
+        <f>G11</f>
+        <v>-1.05854228604585E-3</v>
       </c>
       <c r="H50" s="5">
-        <v>-0.12111333012580899</v>
+        <f t="shared" ref="H50:L50" si="16">H11</f>
+        <v>-0.13548035919666301</v>
       </c>
       <c r="I50" s="5">
-        <v>-4.0987683460116404E-3</v>
+        <f t="shared" si="16"/>
+        <v>-1.24974839854985E-3</v>
       </c>
       <c r="J50" s="5">
-        <v>-0.64230233430862405</v>
+        <f t="shared" si="16"/>
+        <v>-0.72550737857818604</v>
       </c>
       <c r="K50" s="5">
-        <v>-4.7432221472263301E-3</v>
+        <f t="shared" si="16"/>
+        <v>2.9684353619813902E-2</v>
       </c>
       <c r="L50" s="5">
-        <v>0.117863103747368</v>
+        <f t="shared" si="16"/>
+        <v>0.13168570399284399</v>
       </c>
     </row>
     <row r="51" spans="3:12" x14ac:dyDescent="0.25">
@@ -7442,31 +8448,31 @@
         <v>8</v>
       </c>
       <c r="D51" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" s="5">
         <v>0</v>
       </c>
       <c r="G51" s="5">
-        <v>-8.6691416800022108E-3</v>
+        <v>4.3551013804972198E-3</v>
       </c>
       <c r="H51" s="5">
-        <v>-0.11911778151989</v>
+        <v>-0.12111333012580899</v>
       </c>
       <c r="I51" s="5">
-        <v>3.4015933051705399E-3</v>
+        <v>-4.0987683460116404E-3</v>
       </c>
       <c r="J51" s="5">
-        <v>-0.631633281707764</v>
+        <v>-0.64230233430862405</v>
       </c>
       <c r="K51" s="5">
-        <v>7.2991877794265705E-2</v>
+        <v>-4.7432221472263301E-3</v>
       </c>
       <c r="L51" s="5">
-        <v>0.116507813334465</v>
+        <v>0.117863103747368</v>
       </c>
     </row>
     <row r="52" spans="3:12" x14ac:dyDescent="0.25">
@@ -7477,33 +8483,33 @@
         <v>0</v>
       </c>
       <c r="E52" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" s="5">
-        <v>-3.5518379881978E-3</v>
+        <v>-8.6691416800022108E-3</v>
       </c>
       <c r="H52" s="5">
-        <v>-0.13410493731498699</v>
+        <v>-0.11911778151989</v>
       </c>
       <c r="I52" s="5">
-        <v>9.7808660939335796E-5</v>
+        <v>3.4015933051705399E-3</v>
       </c>
       <c r="J52" s="5">
-        <v>-0.72411191463470503</v>
+        <v>-0.631633281707764</v>
       </c>
       <c r="K52" s="5">
-        <v>4.3264478445053101E-2</v>
+        <v>7.2991877794265705E-2</v>
       </c>
       <c r="L52" s="5">
-        <v>0.117512196302414</v>
+        <v>0.116507813334465</v>
       </c>
     </row>
     <row r="53" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C53" s="10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D53" s="5">
         <v>0</v>
@@ -7512,31 +8518,25 @@
         <v>0</v>
       </c>
       <c r="F53" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" s="5">
-        <f>G11</f>
-        <v>-8.8630802929401398E-4</v>
+        <v>-3.5518379881978E-3</v>
       </c>
       <c r="H53" s="5">
-        <f t="shared" ref="H53:L53" si="11">H11</f>
-        <v>-6.7533724009990706E-2</v>
+        <v>-0.13410493731498699</v>
       </c>
       <c r="I53" s="5">
-        <f t="shared" si="11"/>
-        <v>-4.7554963384754999E-4</v>
+        <v>9.7808660939335796E-5</v>
       </c>
       <c r="J53" s="5">
-        <f t="shared" si="11"/>
-        <v>-0.16650235652923601</v>
+        <v>-0.72411191463470503</v>
       </c>
       <c r="K53" s="5">
-        <f t="shared" si="11"/>
-        <v>2.7373749762773501E-3</v>
+        <v>4.3264478445053101E-2</v>
       </c>
       <c r="L53" s="5">
-        <f t="shared" si="11"/>
-        <v>0.18086977303028101</v>
+        <v>0.117512196302414</v>
       </c>
     </row>
     <row r="54" spans="3:12" x14ac:dyDescent="0.25">
@@ -7544,7 +8544,7 @@
         <v>9</v>
       </c>
       <c r="D54" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" s="5">
         <v>0</v>
@@ -7553,22 +8553,28 @@
         <v>0</v>
       </c>
       <c r="G54" s="5">
-        <v>2.5487027596682301E-3</v>
+        <f>G12</f>
+        <v>-8.8630802929401398E-4</v>
       </c>
       <c r="H54" s="5">
-        <v>-5.5173795670270899E-2</v>
+        <f t="shared" ref="H54:L54" si="17">H12</f>
+        <v>-6.7533724009990706E-2</v>
       </c>
       <c r="I54" s="5">
-        <v>-3.4908521920442599E-3</v>
+        <f t="shared" si="17"/>
+        <v>-4.7554963384754999E-4</v>
       </c>
       <c r="J54" s="5">
-        <v>-0.130110248923302</v>
+        <f t="shared" si="17"/>
+        <v>-0.16650235652923601</v>
       </c>
       <c r="K54" s="5">
-        <v>-1.5624847263097799E-2</v>
+        <f t="shared" si="17"/>
+        <v>2.7373749762773501E-3</v>
       </c>
       <c r="L54" s="5">
-        <v>0.14968892931938199</v>
+        <f t="shared" si="17"/>
+        <v>0.18086977303028101</v>
       </c>
     </row>
     <row r="55" spans="3:12" x14ac:dyDescent="0.25">
@@ -7576,31 +8582,31 @@
         <v>9</v>
       </c>
       <c r="D55" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" s="5">
         <v>0</v>
       </c>
       <c r="G55" s="5">
-        <v>-4.73329424858093E-3</v>
+        <v>2.5487027596682301E-3</v>
       </c>
       <c r="H55" s="5">
-        <v>-5.60480542480946E-2</v>
+        <v>-5.5173795670270899E-2</v>
       </c>
       <c r="I55" s="5">
-        <v>3.4013029653579001E-3</v>
+        <v>-3.4908521920442599E-3</v>
       </c>
       <c r="J55" s="5">
-        <v>-0.13074302673339799</v>
+        <v>-0.130110248923302</v>
       </c>
       <c r="K55" s="5">
-        <v>2.2813741117715801E-2</v>
+        <v>-1.5624847263097799E-2</v>
       </c>
       <c r="L55" s="5">
-        <v>0.152383208274841</v>
+        <v>0.14968892931938199</v>
       </c>
     </row>
     <row r="56" spans="3:12" x14ac:dyDescent="0.25">
@@ -7611,33 +8617,33 @@
         <v>0</v>
       </c>
       <c r="E56" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" s="5">
-        <v>-1.7024042317643801E-3</v>
+        <v>-4.73329424858093E-3</v>
       </c>
       <c r="H56" s="5">
-        <v>-8.0940060317516299E-2</v>
+        <v>-5.60480542480946E-2</v>
       </c>
       <c r="I56" s="5">
-        <v>1.9386454368941499E-5</v>
+        <v>3.4013029653579001E-3</v>
       </c>
       <c r="J56" s="5">
-        <v>-0.19877098500728599</v>
+        <v>-0.13074302673339799</v>
       </c>
       <c r="K56" s="5">
-        <v>6.3251033425331098E-3</v>
+        <v>2.2813741117715801E-2</v>
       </c>
       <c r="L56" s="5">
-        <v>0.22032138705253601</v>
+        <v>0.152383208274841</v>
       </c>
     </row>
     <row r="57" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C57" s="10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D57" s="5">
         <v>0</v>
@@ -7646,31 +8652,25 @@
         <v>0</v>
       </c>
       <c r="F57" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" s="5">
-        <f>G12</f>
-        <v>-2.7598871383815999E-3</v>
+        <v>-1.7024042317643801E-3</v>
       </c>
       <c r="H57" s="5">
-        <f t="shared" ref="H57:L57" si="12">H12</f>
-        <v>-0.127221524715424</v>
+        <v>-8.0940060317516299E-2</v>
       </c>
       <c r="I57" s="5">
-        <f t="shared" si="12"/>
-        <v>-8.8058260735124404E-4</v>
+        <v>1.9386454368941499E-5</v>
       </c>
       <c r="J57" s="5">
-        <f t="shared" si="12"/>
-        <v>-0.67187190055847201</v>
+        <v>-0.19877098500728599</v>
       </c>
       <c r="K57" s="5">
-        <f t="shared" si="12"/>
-        <v>1.79205909371376E-2</v>
+        <v>6.3251033425331098E-3</v>
       </c>
       <c r="L57" s="5">
-        <f t="shared" si="12"/>
-        <v>6.6542282700538594E-2</v>
+        <v>0.22032138705253601</v>
       </c>
     </row>
     <row r="58" spans="3:12" x14ac:dyDescent="0.25">
@@ -7678,7 +8678,7 @@
         <v>10</v>
       </c>
       <c r="D58" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" s="5">
         <v>0</v>
@@ -7687,22 +8687,28 @@
         <v>0</v>
       </c>
       <c r="G58" s="5">
-        <v>3.9539658464491402E-3</v>
+        <f>G13</f>
+        <v>-2.7598871383815999E-3</v>
       </c>
       <c r="H58" s="5">
-        <v>-0.113986387848854</v>
+        <f t="shared" ref="H58:L58" si="18">H13</f>
+        <v>-0.127221524715424</v>
       </c>
       <c r="I58" s="5">
-        <v>-5.0774128176271898E-3</v>
+        <f t="shared" si="18"/>
+        <v>-8.8058260735124404E-4</v>
       </c>
       <c r="J58" s="5">
-        <v>-0.59424072504043601</v>
+        <f t="shared" si="18"/>
+        <v>-0.67187190055847201</v>
       </c>
       <c r="K58" s="5">
-        <v>-2.05840114504099E-2</v>
+        <f t="shared" si="18"/>
+        <v>1.79205909371376E-2</v>
       </c>
       <c r="L58" s="5">
-        <v>6.1202116310596501E-2</v>
+        <f t="shared" si="18"/>
+        <v>6.6542282700538594E-2</v>
       </c>
     </row>
     <row r="59" spans="3:12" x14ac:dyDescent="0.25">
@@ -7710,31 +8716,31 @@
         <v>10</v>
       </c>
       <c r="D59" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" s="5">
         <v>0</v>
       </c>
       <c r="G59" s="5">
-        <v>-1.15294195711613E-2</v>
+        <v>3.9539658464491402E-3</v>
       </c>
       <c r="H59" s="5">
-        <v>-0.112579241394997</v>
+        <v>-0.113986387848854</v>
       </c>
       <c r="I59" s="5">
-        <v>5.4107047617435499E-3</v>
+        <v>-5.0774128176271898E-3</v>
       </c>
       <c r="J59" s="5">
-        <v>-0.589094638824463</v>
+        <v>-0.59424072504043601</v>
       </c>
       <c r="K59" s="5">
-        <v>6.7401126027107197E-2</v>
+        <v>-2.05840114504099E-2</v>
       </c>
       <c r="L59" s="5">
-        <v>5.8719873428344699E-2</v>
+        <v>6.1202116310596501E-2</v>
       </c>
     </row>
     <row r="60" spans="3:12" x14ac:dyDescent="0.25">
@@ -7745,42 +8751,84 @@
         <v>0</v>
       </c>
       <c r="E60" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="5">
+        <v>0</v>
+      </c>
+      <c r="G60" s="5">
+        <v>-1.15294195711613E-2</v>
+      </c>
+      <c r="H60" s="5">
+        <v>-0.112579241394997</v>
+      </c>
+      <c r="I60" s="5">
+        <v>5.4107047617435499E-3</v>
+      </c>
+      <c r="J60" s="5">
+        <v>-0.589094638824463</v>
+      </c>
+      <c r="K60" s="5">
+        <v>6.7401126027107197E-2</v>
+      </c>
+      <c r="L60" s="5">
+        <v>5.8719873428344699E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C61" s="10">
+        <v>10</v>
+      </c>
+      <c r="D61" s="5">
+        <v>0</v>
+      </c>
+      <c r="E61" s="5">
+        <v>0</v>
+      </c>
+      <c r="F61" s="5">
         <v>1</v>
       </c>
-      <c r="G60" s="5">
+      <c r="G61" s="5">
         <v>-4.62295254692435E-3</v>
       </c>
-      <c r="H60" s="5">
+      <c r="H61" s="5">
         <v>-0.12288958579301799</v>
       </c>
-      <c r="I60" s="5">
+      <c r="I61" s="5">
         <v>4.8266863450407998E-4</v>
       </c>
-      <c r="J60" s="5">
+      <c r="J61" s="5">
         <v>-0.65276098251342796</v>
       </c>
-      <c r="K60" s="5">
+      <c r="K61" s="5">
         <v>2.8584428131580401E-2</v>
       </c>
-      <c r="L60" s="5">
+      <c r="L61" s="5">
         <v>5.4238036274910001E-2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="W5:Y5"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="G20:L20"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="M1:P1"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="W1:Y1"/>
+  <mergeCells count="20">
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="W6:Y6"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="G21:L21"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="G2:L2"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="Q2:S2"/>
     <mergeCell ref="W2:Y2"/>
-    <mergeCell ref="T1:V1"/>
+    <mergeCell ref="W3:Y3"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="AW3:AY3"/>
+    <mergeCell ref="AW6:AY6"/>
+    <mergeCell ref="AA1:AY1"/>
+    <mergeCell ref="AA2:AF2"/>
+    <mergeCell ref="AG2:AL2"/>
+    <mergeCell ref="AM2:AP2"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AW2:AY2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7840,7 +8888,7 @@
       <c r="R1" s="27"/>
       <c r="S1" s="27"/>
       <c r="T1" s="30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U1" s="30"/>
       <c r="V1" s="30"/>
@@ -7970,41 +9018,33 @@
         <f>'Proximal Validation'!L3</f>
         <v>0.37637501955032299</v>
       </c>
-      <c r="M3" s="5">
-        <v>0.32089378576119326</v>
-      </c>
-      <c r="N3" s="5">
-        <v>7.4134038334444138E-2</v>
-      </c>
-      <c r="O3" s="5">
-        <v>1.5818861967538926</v>
-      </c>
-      <c r="P3" s="11">
-        <v>7.2424488166406732E-6</v>
-      </c>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="11"/>
       <c r="Q3" s="5">
         <f>M3-A3</f>
-        <v>-7.910621423880676E-2</v>
+        <v>-0.4</v>
       </c>
       <c r="R3" s="5">
         <f>N3-B3</f>
-        <v>1.4134038334444141E-2</v>
+        <v>-0.06</v>
       </c>
       <c r="S3" s="5">
         <f>O3-C3</f>
-        <v>1.1089869958996079E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T3" s="5">
         <f>ABS(Q3)</f>
-        <v>7.910621423880676E-2</v>
+        <v>0.4</v>
       </c>
       <c r="U3" s="5">
         <f t="shared" ref="U3:V12" si="0">ABS(R3)</f>
-        <v>1.4134038334444141E-2</v>
+        <v>0.06</v>
       </c>
       <c r="V3" s="5">
         <f t="shared" si="0"/>
-        <v>1.1089869958996079E-2</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="W3" s="1" t="s">
         <v>23</v>
@@ -8065,53 +9105,45 @@
         <f>'Proximal Validation'!L4</f>
         <v>0.81632339954376198</v>
       </c>
-      <c r="M4" s="8">
-        <v>0.6996350590125997</v>
-      </c>
-      <c r="N4" s="8">
-        <v>7.3914091825146147E-2</v>
-      </c>
-      <c r="O4" s="8">
-        <v>1.5912923693483643</v>
-      </c>
-      <c r="P4" s="12">
-        <v>1.6443019805775209E-5</v>
-      </c>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="12"/>
       <c r="Q4" s="5">
         <f t="shared" ref="Q4:S12" si="1">M4-A4</f>
-        <v>-0.10036494098740034</v>
+        <v>-0.8</v>
       </c>
       <c r="R4" s="5">
         <f t="shared" si="1"/>
-        <v>1.3914091825146149E-2</v>
+        <v>-0.06</v>
       </c>
       <c r="S4" s="5">
         <f t="shared" si="1"/>
-        <v>2.0496042553467708E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T4" s="5">
         <f t="shared" ref="T4:T12" si="2">ABS(Q4)</f>
-        <v>0.10036494098740034</v>
+        <v>0.8</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" si="0"/>
-        <v>1.3914091825146149E-2</v>
+        <v>0.06</v>
       </c>
       <c r="V4" s="5">
         <f t="shared" si="0"/>
-        <v>2.0496042553467708E-2</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="W4" s="6" cm="1">
-        <f t="array" ref="W4">AVERAGE(ABS(Q3:Q12))</f>
-        <v>0.15695819486834212</v>
+        <f t="array" ref="W4">AVERAGE(ABS(Q7:Q12))</f>
+        <v>3.009046304483946E-2</v>
       </c>
       <c r="X4" s="6" cm="1">
-        <f t="array" ref="X4">AVERAGE(ABS(R3:R12))</f>
-        <v>3.9368966861958364E-2</v>
+        <f t="array" ref="X4">AVERAGE(ABS(R7:R12))</f>
+        <v>2.5983872009844849E-2</v>
       </c>
       <c r="Y4" s="6" cm="1">
-        <f t="array" ref="Y4">AVERAGE(ABS(S3:S12))</f>
-        <v>1.6908018436586625E-2</v>
+        <f t="array" ref="Y4">AVERAGE(ABS(S7:S12))</f>
+        <v>1.5338393505722378E-2</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
@@ -8163,41 +9195,33 @@
         <f>'Proximal Validation'!L5</f>
         <v>0.24872186779975899</v>
       </c>
-      <c r="M5" s="5">
-        <v>0.39334509151852798</v>
-      </c>
-      <c r="N5" s="5">
-        <v>5.4736146088105148E-2</v>
-      </c>
-      <c r="O5" s="5">
-        <v>1.5810935756518101</v>
-      </c>
-      <c r="P5" s="11">
-        <v>1.0389510531553127E-6</v>
-      </c>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="11"/>
       <c r="Q5" s="5">
         <f t="shared" si="1"/>
-        <v>9.3345091518527989E-2</v>
+        <v>-0.3</v>
       </c>
       <c r="R5" s="5">
         <f t="shared" si="1"/>
-        <v>-2.5263853911894854E-2</v>
+        <v>-0.08</v>
       </c>
       <c r="S5" s="5">
         <f t="shared" si="1"/>
-        <v>1.0297248856913521E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T5" s="5">
         <f t="shared" si="2"/>
-        <v>9.3345091518527989E-2</v>
+        <v>0.3</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="0"/>
-        <v>2.5263853911894854E-2</v>
+        <v>0.08</v>
       </c>
       <c r="V5" s="5">
         <f t="shared" si="0"/>
-        <v>1.0297248856913521E-2</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="W5" s="24"/>
       <c r="X5" s="24"/>
@@ -8252,41 +9276,33 @@
         <f>'Proximal Validation'!L6</f>
         <v>0.46851912140846302</v>
       </c>
-      <c r="M6" s="5">
-        <v>0.46843562041768616</v>
-      </c>
-      <c r="N6" s="5">
-        <v>0.11438406646457094</v>
-      </c>
-      <c r="O6" s="5">
-        <v>1.582210361993478</v>
-      </c>
-      <c r="P6" s="11">
-        <v>2.4518242047126064E-6</v>
-      </c>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="11"/>
       <c r="Q6" s="5">
         <f t="shared" si="1"/>
-        <v>-3.156437958231384E-2</v>
+        <v>-0.5</v>
       </c>
       <c r="R6" s="5">
         <f t="shared" si="1"/>
-        <v>1.4384066464570938E-2</v>
+        <v>-0.1</v>
       </c>
       <c r="S6" s="5">
         <f t="shared" si="1"/>
-        <v>1.1414035198581418E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T6" s="5">
         <f t="shared" si="2"/>
-        <v>3.156437958231384E-2</v>
+        <v>0.5</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="0"/>
-        <v>1.4384066464570938E-2</v>
+        <v>0.1</v>
       </c>
       <c r="V6" s="5">
         <f t="shared" si="0"/>
-        <v>1.1414035198581418E-2</v>
+        <v>1.5707963267948966</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
@@ -8339,40 +9355,40 @@
         <v>0.62586665153503396</v>
       </c>
       <c r="M7" s="5">
-        <v>0.66485793082741185</v>
+        <v>0.68297026231905456</v>
       </c>
       <c r="N7" s="5">
-        <v>0.11356618486006727</v>
+        <v>0.13933140088115567</v>
       </c>
       <c r="O7" s="5">
-        <v>1.5895812614566727</v>
+        <v>1.5866582432652172</v>
       </c>
       <c r="P7" s="11">
-        <v>4.7680219596148753E-6</v>
+        <v>1.5167950364546642E-3</v>
       </c>
       <c r="Q7" s="5">
         <f t="shared" si="1"/>
-        <v>-3.5142069172588108E-2</v>
+        <v>-1.70297376809454E-2</v>
       </c>
       <c r="R7" s="5">
         <f t="shared" si="1"/>
-        <v>1.3566184860067262E-2</v>
+        <v>3.9331400881155665E-2</v>
       </c>
       <c r="S7" s="5">
         <f t="shared" si="1"/>
-        <v>1.8784934661776109E-2</v>
+        <v>1.5861916470320647E-2</v>
       </c>
       <c r="T7" s="5">
         <f t="shared" si="2"/>
-        <v>3.5142069172588108E-2</v>
+        <v>1.70297376809454E-2</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="0"/>
-        <v>1.3566184860067262E-2</v>
+        <v>3.9331400881155665E-2</v>
       </c>
       <c r="V7" s="5">
         <f t="shared" si="0"/>
-        <v>1.8784934661776109E-2</v>
+        <v>1.5861916470320647E-2</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
@@ -8425,40 +9441,40 @@
         <v>0.316497713327408</v>
       </c>
       <c r="M8" s="5">
-        <v>0.81295624525342181</v>
+        <v>0.40640589156575424</v>
       </c>
       <c r="N8" s="5">
-        <v>7.8153386233021566E-2</v>
+        <v>0.19999999999995946</v>
       </c>
       <c r="O8" s="5">
-        <v>1.5871640744157403</v>
+        <v>1.5811910258947344</v>
       </c>
       <c r="P8" s="11">
-        <v>4.6295100778507645E-6</v>
+        <v>3.3214077866668329E-2</v>
       </c>
       <c r="Q8" s="5">
         <f t="shared" si="1"/>
-        <v>0.41295624525342178</v>
+        <v>6.4058915657542181E-3</v>
       </c>
       <c r="R8" s="5">
         <f t="shared" si="1"/>
-        <v>-8.1846613766978438E-2</v>
+        <v>3.9999999999959457E-2</v>
       </c>
       <c r="S8" s="5">
         <f t="shared" si="1"/>
-        <v>1.6367747620843698E-2</v>
+        <v>1.0394699099837812E-2</v>
       </c>
       <c r="T8" s="5">
         <f t="shared" si="2"/>
-        <v>0.41295624525342178</v>
+        <v>6.4058915657542181E-3</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="0"/>
-        <v>8.1846613766978438E-2</v>
+        <v>3.9999999999959457E-2</v>
       </c>
       <c r="V8" s="5">
         <f t="shared" si="0"/>
-        <v>1.6367747620843698E-2</v>
+        <v>1.0394699099837812E-2</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
@@ -8511,40 +9527,40 @@
         <v>0.39143002033233598</v>
       </c>
       <c r="M9" s="5">
-        <v>0.88705919662658761</v>
+        <v>0.62327999688776803</v>
       </c>
       <c r="N9" s="5">
-        <v>0.1152205736141424</v>
+        <v>0.19180256885610766</v>
       </c>
       <c r="O9" s="5">
-        <v>1.5846639797520534</v>
+        <v>1.5791817036747455</v>
       </c>
       <c r="P9" s="11">
-        <v>6.8443937909857615E-6</v>
+        <v>1.0687967136026393E-2</v>
       </c>
       <c r="Q9" s="5">
         <f t="shared" si="1"/>
-        <v>0.28705919662658763</v>
+        <v>2.3279996887768051E-2</v>
       </c>
       <c r="R9" s="5">
         <f t="shared" si="1"/>
-        <v>-4.4779426385857607E-2</v>
+        <v>3.180256885610766E-2</v>
       </c>
       <c r="S9" s="5">
         <f t="shared" si="1"/>
-        <v>1.3867652957156862E-2</v>
+        <v>8.3853768798489714E-3</v>
       </c>
       <c r="T9" s="5">
         <f t="shared" si="2"/>
-        <v>0.28705919662658763</v>
+        <v>2.3279996887768051E-2</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="0"/>
-        <v>4.4779426385857607E-2</v>
+        <v>3.180256885610766E-2</v>
       </c>
       <c r="V9" s="5">
         <f t="shared" si="0"/>
-        <v>1.3867652957156862E-2</v>
+        <v>8.3853768798489714E-3</v>
       </c>
       <c r="W9" s="7"/>
       <c r="X9" s="7"/>
@@ -8600,40 +9616,40 @@
         <v>0.13168570399284399</v>
       </c>
       <c r="M10" s="5">
-        <v>0.96128878295624809</v>
+        <v>0.75041769408300663</v>
       </c>
       <c r="N10" s="5">
-        <v>0.13752255231462213</v>
+        <v>0.14059847501826422</v>
       </c>
       <c r="O10" s="5">
-        <v>1.602661944896262</v>
+        <v>1.5452699186482521</v>
       </c>
       <c r="P10" s="11">
-        <v>2.285984613514944E-5</v>
+        <v>6.3608251062703151E-3</v>
       </c>
       <c r="Q10" s="5">
         <f t="shared" si="1"/>
-        <v>0.16128878295624804</v>
+        <v>-4.9582305916993419E-2</v>
       </c>
       <c r="R10" s="5">
         <f t="shared" si="1"/>
-        <v>-4.2477447685377867E-2</v>
+        <v>-3.9401524981735769E-2</v>
       </c>
       <c r="S10" s="5">
         <f t="shared" si="1"/>
-        <v>3.1865618101365456E-2</v>
+        <v>-2.5526408146644419E-2</v>
       </c>
       <c r="T10" s="5">
         <f t="shared" si="2"/>
-        <v>0.16128878295624804</v>
+        <v>4.9582305916993419E-2</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="0"/>
-        <v>4.2477447685377867E-2</v>
+        <v>3.9401524981735769E-2</v>
       </c>
       <c r="V10" s="5">
         <f t="shared" si="0"/>
-        <v>3.1865618101365456E-2</v>
+        <v>2.5526408146644419E-2</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
@@ -8686,40 +9702,40 @@
         <v>0.18086977303028101</v>
       </c>
       <c r="M11" s="5">
-        <v>0.46777017945158822</v>
+        <v>0.3727073209734087</v>
       </c>
       <c r="N11" s="5">
-        <v>0.11412156807923182</v>
+        <v>0.19999999999952101</v>
       </c>
       <c r="O11" s="5">
-        <v>1.5849629936853504</v>
+        <v>1.5905315247833587</v>
       </c>
       <c r="P11" s="11">
-        <v>1.2243866934773631E-5</v>
+        <v>5.2515857632866779E-2</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" si="1"/>
-        <v>0.16777017945158823</v>
+        <v>7.2707320973408707E-2</v>
       </c>
       <c r="R11" s="5">
         <f t="shared" si="1"/>
-        <v>-8.5878431920768189E-2</v>
+        <v>-4.7900572397452379E-13</v>
       </c>
       <c r="S11" s="5">
         <f t="shared" si="1"/>
-        <v>1.4166666890453872E-2</v>
+        <v>1.9735197988462128E-2</v>
       </c>
       <c r="T11" s="5">
         <f t="shared" si="2"/>
-        <v>0.16777017945158823</v>
+        <v>7.2707320973408707E-2</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="0"/>
-        <v>8.5878431920768189E-2</v>
+        <v>4.7900572397452379E-13</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" si="0"/>
-        <v>1.4166666890453872E-2</v>
+        <v>1.9735197988462128E-2</v>
       </c>
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
@@ -8775,40 +9791,40 @@
         <v>6.6542282700538594E-2</v>
       </c>
       <c r="M12" s="5">
-        <v>0.90098484889593833</v>
+        <v>0.688462474755833</v>
       </c>
       <c r="N12" s="5">
-        <v>0.14255448653552177</v>
+        <v>0.19463226266036848</v>
       </c>
       <c r="O12" s="5">
-        <v>1.5915266943612081</v>
+        <v>1.5829230892441168</v>
       </c>
       <c r="P12" s="11">
-        <v>1.7785552068166674E-5</v>
+        <v>1.6370899689140885E-2</v>
       </c>
       <c r="Q12" s="5">
         <f t="shared" si="1"/>
-        <v>0.20098484889593837</v>
+        <v>-1.1537525244166957E-2</v>
       </c>
       <c r="R12" s="5">
         <f t="shared" si="1"/>
-        <v>-5.7445513464478237E-2</v>
+        <v>-5.3677373396315287E-3</v>
       </c>
       <c r="S12" s="5">
         <f t="shared" si="1"/>
-        <v>2.0730367566311525E-2</v>
+        <v>1.2126762449220285E-2</v>
       </c>
       <c r="T12" s="5">
         <f t="shared" si="2"/>
-        <v>0.20098484889593837</v>
+        <v>1.1537525244166957E-2</v>
       </c>
       <c r="U12" s="5">
         <f t="shared" si="0"/>
-        <v>5.7445513464478237E-2</v>
+        <v>5.3677373396315287E-3</v>
       </c>
       <c r="V12" s="5">
         <f t="shared" si="0"/>
-        <v>2.0730367566311525E-2</v>
+        <v>1.2126762449220285E-2</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
@@ -10241,7 +11257,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>21</v>
       </c>
       <c r="B1" s="32"/>
@@ -10249,7 +11265,7 @@
       <c r="D1" s="32"/>
       <c r="E1" s="32"/>
       <c r="F1" s="33"/>
-      <c r="H1" s="34" t="s">
+      <c r="H1" s="35" t="s">
         <v>22</v>
       </c>
       <c r="I1" s="32"/>
@@ -17612,16 +18628,16 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Raw Data/single force (10 trials)(perturbed)/Validation(1.5)(3tendon).xlsx
+++ b/Raw Data/single force (10 trials)(perturbed)/Validation(1.5)(3tendon).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/Raw Data/single force (10 trials)(perturbed)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4394" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6F38BCE-4A35-4BEE-B254-BF9BA35E0E1B}"/>
+  <xr:revisionPtr revIDLastSave="4404" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15AB3707-EE7A-4907-A66F-1EF3C06E8E78}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
@@ -562,10 +562,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -8809,6 +8805,15 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="AW3:AY3"/>
+    <mergeCell ref="AW6:AY6"/>
+    <mergeCell ref="AA1:AY1"/>
+    <mergeCell ref="AA2:AF2"/>
+    <mergeCell ref="AG2:AL2"/>
+    <mergeCell ref="AM2:AP2"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AW2:AY2"/>
     <mergeCell ref="A1:Y1"/>
     <mergeCell ref="W6:Y6"/>
     <mergeCell ref="A15:C15"/>
@@ -8820,15 +8825,6 @@
     <mergeCell ref="W2:Y2"/>
     <mergeCell ref="W3:Y3"/>
     <mergeCell ref="T2:V2"/>
-    <mergeCell ref="AW3:AY3"/>
-    <mergeCell ref="AW6:AY6"/>
-    <mergeCell ref="AA1:AY1"/>
-    <mergeCell ref="AA2:AF2"/>
-    <mergeCell ref="AG2:AL2"/>
-    <mergeCell ref="AM2:AP2"/>
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AW2:AY2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -9135,15 +9131,15 @@
       </c>
       <c r="W4" s="6" cm="1">
         <f t="array" ref="W4">AVERAGE(ABS(Q7:Q12))</f>
-        <v>3.009046304483946E-2</v>
+        <v>0.22261180692711868</v>
       </c>
       <c r="X4" s="6" cm="1">
         <f t="array" ref="X4">AVERAGE(ABS(R7:R12))</f>
-        <v>2.5983872009844849E-2</v>
+        <v>4.9827157306768989E-2</v>
       </c>
       <c r="Y4" s="6" cm="1">
         <f t="array" ref="Y4">AVERAGE(ABS(S7:S12))</f>
-        <v>1.5338393505722378E-2</v>
+        <v>1.8926135578701597E-2</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
@@ -9355,40 +9351,40 @@
         <v>0.62586665153503396</v>
       </c>
       <c r="M7" s="5">
-        <v>0.68297026231905456</v>
+        <v>0.78976850420307076</v>
       </c>
       <c r="N7" s="5">
-        <v>0.13933140088115567</v>
+        <v>9.9547185959334442E-2</v>
       </c>
       <c r="O7" s="5">
-        <v>1.5866582432652172</v>
+        <v>1.5872341940579229</v>
       </c>
       <c r="P7" s="11">
-        <v>1.5167950364546642E-3</v>
+        <v>1.6459389963341053E-3</v>
       </c>
       <c r="Q7" s="5">
         <f t="shared" si="1"/>
-        <v>-1.70297376809454E-2</v>
+        <v>8.9768504203070809E-2</v>
       </c>
       <c r="R7" s="5">
         <f t="shared" si="1"/>
-        <v>3.9331400881155665E-2</v>
+        <v>-4.5281404066556397E-4</v>
       </c>
       <c r="S7" s="5">
         <f t="shared" si="1"/>
-        <v>1.5861916470320647E-2</v>
+        <v>1.6437867263026318E-2</v>
       </c>
       <c r="T7" s="5">
         <f t="shared" si="2"/>
-        <v>1.70297376809454E-2</v>
+        <v>8.9768504203070809E-2</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="0"/>
-        <v>3.9331400881155665E-2</v>
+        <v>4.5281404066556397E-4</v>
       </c>
       <c r="V7" s="5">
         <f t="shared" si="0"/>
-        <v>1.5861916470320647E-2</v>
+        <v>1.6437867263026318E-2</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
@@ -9441,40 +9437,40 @@
         <v>0.316497713327408</v>
       </c>
       <c r="M8" s="5">
-        <v>0.40640589156575424</v>
+        <v>0.78111143307034248</v>
       </c>
       <c r="N8" s="5">
-        <v>0.19999999999995946</v>
+        <v>9.1808431359136008E-2</v>
       </c>
       <c r="O8" s="5">
-        <v>1.5811910258947344</v>
+        <v>1.5835866638447427</v>
       </c>
       <c r="P8" s="11">
-        <v>3.3214077866668329E-2</v>
+        <v>3.3037298469856015E-2</v>
       </c>
       <c r="Q8" s="5">
         <f t="shared" si="1"/>
-        <v>6.4058915657542181E-3</v>
+        <v>0.38111143307034245</v>
       </c>
       <c r="R8" s="5">
         <f t="shared" si="1"/>
-        <v>3.9999999999959457E-2</v>
+        <v>-6.8191568640863995E-2</v>
       </c>
       <c r="S8" s="5">
         <f t="shared" si="1"/>
-        <v>1.0394699099837812E-2</v>
+        <v>1.2790337049846112E-2</v>
       </c>
       <c r="T8" s="5">
         <f t="shared" si="2"/>
-        <v>6.4058915657542181E-3</v>
+        <v>0.38111143307034245</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="0"/>
-        <v>3.9999999999959457E-2</v>
+        <v>6.8191568640863995E-2</v>
       </c>
       <c r="V8" s="5">
         <f t="shared" si="0"/>
-        <v>1.0394699099837812E-2</v>
+        <v>1.2790337049846112E-2</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
@@ -9527,40 +9523,40 @@
         <v>0.39143002033233598</v>
       </c>
       <c r="M9" s="5">
-        <v>0.62327999688776803</v>
+        <v>0.83001903226354135</v>
       </c>
       <c r="N9" s="5">
-        <v>0.19180256885610766</v>
+        <v>0.12533089634460573</v>
       </c>
       <c r="O9" s="5">
-        <v>1.5791817036747455</v>
+        <v>1.5805607763395348</v>
       </c>
       <c r="P9" s="11">
-        <v>1.0687967136026393E-2</v>
+        <v>1.0687608834281478E-2</v>
       </c>
       <c r="Q9" s="5">
         <f t="shared" si="1"/>
-        <v>2.3279996887768051E-2</v>
+        <v>0.23001903226354137</v>
       </c>
       <c r="R9" s="5">
         <f t="shared" si="1"/>
-        <v>3.180256885610766E-2</v>
+        <v>-3.4669103655394273E-2</v>
       </c>
       <c r="S9" s="5">
         <f t="shared" si="1"/>
-        <v>8.3853768798489714E-3</v>
+        <v>9.7644495446382873E-3</v>
       </c>
       <c r="T9" s="5">
         <f t="shared" si="2"/>
-        <v>2.3279996887768051E-2</v>
+        <v>0.23001903226354137</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="0"/>
-        <v>3.180256885610766E-2</v>
+        <v>3.4669103655394273E-2</v>
       </c>
       <c r="V9" s="5">
         <f t="shared" si="0"/>
-        <v>8.3853768798489714E-3</v>
+        <v>9.7644495446382873E-3</v>
       </c>
       <c r="W9" s="7"/>
       <c r="X9" s="7"/>
@@ -9616,40 +9612,40 @@
         <v>0.13168570399284399</v>
       </c>
       <c r="M10" s="5">
-        <v>0.75041769408300663</v>
+        <v>0.85564646845875614</v>
       </c>
       <c r="N10" s="5">
-        <v>0.14059847501826422</v>
+        <v>0.13988919191860472</v>
       </c>
       <c r="O10" s="5">
-        <v>1.5452699186482521</v>
+        <v>1.5321318374178001</v>
       </c>
       <c r="P10" s="11">
-        <v>6.3608251062703151E-3</v>
+        <v>8.2963146605440231E-3</v>
       </c>
       <c r="Q10" s="5">
         <f t="shared" si="1"/>
-        <v>-4.9582305916993419E-2</v>
+        <v>5.5646468458756093E-2</v>
       </c>
       <c r="R10" s="5">
         <f t="shared" si="1"/>
-        <v>-3.9401524981735769E-2</v>
+        <v>-4.0110808081395277E-2</v>
       </c>
       <c r="S10" s="5">
         <f t="shared" si="1"/>
-        <v>-2.5526408146644419E-2</v>
+        <v>-3.8664489377096434E-2</v>
       </c>
       <c r="T10" s="5">
         <f t="shared" si="2"/>
-        <v>4.9582305916993419E-2</v>
+        <v>5.5646468458756093E-2</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="0"/>
-        <v>3.9401524981735769E-2</v>
+        <v>4.0110808081395277E-2</v>
       </c>
       <c r="V10" s="5">
         <f t="shared" si="0"/>
-        <v>2.5526408146644419E-2</v>
+        <v>3.8664489377096434E-2</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
@@ -9702,40 +9698,40 @@
         <v>0.18086977303028101</v>
       </c>
       <c r="M11" s="5">
-        <v>0.3727073209734087</v>
+        <v>0.74008865040570559</v>
       </c>
       <c r="N11" s="5">
-        <v>0.19999999999952101</v>
+        <v>9.1741523107677331E-2</v>
       </c>
       <c r="O11" s="5">
-        <v>1.5905315247833587</v>
+        <v>1.5926037418228494</v>
       </c>
       <c r="P11" s="11">
-        <v>5.2515857632866779E-2</v>
+        <v>5.0844863544484871E-2</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" si="1"/>
-        <v>7.2707320973408707E-2</v>
+        <v>0.44008865040570561</v>
       </c>
       <c r="R11" s="5">
         <f t="shared" si="1"/>
-        <v>-4.7900572397452379E-13</v>
+        <v>-0.10825847689232268</v>
       </c>
       <c r="S11" s="5">
         <f t="shared" si="1"/>
-        <v>1.9735197988462128E-2</v>
+        <v>2.1807415027952803E-2</v>
       </c>
       <c r="T11" s="5">
         <f t="shared" si="2"/>
-        <v>7.2707320973408707E-2</v>
+        <v>0.44008865040570561</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="0"/>
-        <v>4.7900572397452379E-13</v>
+        <v>0.10825847689232268</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" si="0"/>
-        <v>1.9735197988462128E-2</v>
+        <v>2.1807415027952803E-2</v>
       </c>
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
@@ -9791,40 +9787,40 @@
         <v>6.6542282700538594E-2</v>
       </c>
       <c r="M12" s="5">
-        <v>0.688462474755833</v>
+        <v>0.83903675316129567</v>
       </c>
       <c r="N12" s="5">
-        <v>0.19463226266036848</v>
+        <v>0.15271982747002785</v>
       </c>
       <c r="O12" s="5">
-        <v>1.5829230892441168</v>
+        <v>1.5848885820045462</v>
       </c>
       <c r="P12" s="11">
-        <v>1.6370899689140885E-2</v>
+        <v>1.620397466615673E-2</v>
       </c>
       <c r="Q12" s="5">
         <f t="shared" si="1"/>
-        <v>-1.1537525244166957E-2</v>
+        <v>0.13903675316129571</v>
       </c>
       <c r="R12" s="5">
         <f t="shared" si="1"/>
-        <v>-5.3677373396315287E-3</v>
+        <v>-4.7280172529972159E-2</v>
       </c>
       <c r="S12" s="5">
         <f t="shared" si="1"/>
-        <v>1.2126762449220285E-2</v>
+        <v>1.4092255209649629E-2</v>
       </c>
       <c r="T12" s="5">
         <f t="shared" si="2"/>
-        <v>1.1537525244166957E-2</v>
+        <v>0.13903675316129571</v>
       </c>
       <c r="U12" s="5">
         <f t="shared" si="0"/>
-        <v>5.3677373396315287E-3</v>
+        <v>4.7280172529972159E-2</v>
       </c>
       <c r="V12" s="5">
         <f t="shared" si="0"/>
-        <v>1.2126762449220285E-2</v>
+        <v>1.4092255209649629E-2</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
@@ -18357,14 +18353,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E12580AD17ADB64691A1BA4C2E042DA4" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6532fc6a52f3455fe895a4f720bca71c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xmlns:ns4="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d9a2f75daf18a7097de825f86ff3fec6" ns3:_="" ns4:_="">
     <xsd:import namespace="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
@@ -18617,6 +18605,14 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
   <ds:schemaRefs>
@@ -18626,23 +18622,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65923CC5-95C4-4597-AADE-A0DCE38786F0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18659,4 +18638,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Raw Data/single force (10 trials)(perturbed)/Validation(1.5)(3tendon).xlsx
+++ b/Raw Data/single force (10 trials)(perturbed)/Validation(1.5)(3tendon).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/Raw Data/single force (10 trials)(perturbed)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4404" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15AB3707-EE7A-4907-A66F-1EF3C06E8E78}"/>
+  <xr:revisionPtr revIDLastSave="4422" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{414E18F2-5071-4197-8667-78D0192BCB1F}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="46">
   <si>
     <t>Fx (N)</t>
   </si>
@@ -193,6 +193,15 @@
   </si>
   <si>
     <t>3 Perturbations (relative only)</t>
+  </si>
+  <si>
+    <t>SoRoSim get_distal_value (3 perturbations)</t>
+  </si>
+  <si>
+    <t>SoRoSim get_distal_value (2 perturbations)</t>
+  </si>
+  <si>
+    <t>SoRoSim get_distal_value (1 perturbations)</t>
   </si>
 </sst>
 </file>
@@ -562,6 +571,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -8805,15 +8818,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="AW3:AY3"/>
-    <mergeCell ref="AW6:AY6"/>
-    <mergeCell ref="AA1:AY1"/>
-    <mergeCell ref="AA2:AF2"/>
-    <mergeCell ref="AG2:AL2"/>
-    <mergeCell ref="AM2:AP2"/>
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AW2:AY2"/>
     <mergeCell ref="A1:Y1"/>
     <mergeCell ref="W6:Y6"/>
     <mergeCell ref="A15:C15"/>
@@ -8825,6 +8829,15 @@
     <mergeCell ref="W2:Y2"/>
     <mergeCell ref="W3:Y3"/>
     <mergeCell ref="T2:V2"/>
+    <mergeCell ref="AW3:AY3"/>
+    <mergeCell ref="AW6:AY6"/>
+    <mergeCell ref="AA1:AY1"/>
+    <mergeCell ref="AA2:AF2"/>
+    <mergeCell ref="AG2:AL2"/>
+    <mergeCell ref="AM2:AP2"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AW2:AY2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -8846,7 +8859,7 @@
     <col min="13" max="13" width="6.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.140625" customWidth="1"/>
     <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -8873,7 +8886,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="18"/>
       <c r="M1" s="25" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="N1" s="26"/>
       <c r="O1" s="26"/>
@@ -9823,14 +9836,70 @@
         <v>1.4092255209649629E-2</v>
       </c>
     </row>
+    <row r="13" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="M13" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="N13" s="26"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="26"/>
+      <c r="Q13" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="R13" s="27"/>
+      <c r="S13" s="27"/>
+      <c r="T13" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="U13" s="30"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="28"/>
+      <c r="X13" s="28"/>
+      <c r="Y13" s="28"/>
+    </row>
     <row r="14" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="31" t="s">
         <v>31</v>
       </c>
       <c r="B14" s="32"/>
       <c r="C14" s="33"/>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="M14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W14" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="X14" s="29"/>
+      <c r="Y14" s="29"/>
+    </row>
+    <row r="15" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1.5</v>
       </c>
@@ -9840,6 +9909,43 @@
       <c r="C15">
         <v>0</v>
       </c>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="5">
+        <f>M15-A3</f>
+        <v>-0.4</v>
+      </c>
+      <c r="R15" s="5">
+        <f t="shared" ref="R15:S15" si="3">N15-B3</f>
+        <v>-0.06</v>
+      </c>
+      <c r="S15" s="5">
+        <f t="shared" si="3"/>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="T15" s="5">
+        <f>ABS(Q15)</f>
+        <v>0.4</v>
+      </c>
+      <c r="U15" s="5">
+        <f t="shared" ref="U15:U24" si="4">ABS(R15)</f>
+        <v>0.06</v>
+      </c>
+      <c r="V15" s="5">
+        <f t="shared" ref="V15:V24" si="5">ABS(S15)</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="W15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y15" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16">
@@ -9851,8 +9957,48 @@
       <c r="C16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="5">
+        <f t="shared" ref="Q16:Q24" si="6">M16-A4</f>
+        <v>-0.8</v>
+      </c>
+      <c r="R16" s="5">
+        <f t="shared" ref="R16:R24" si="7">N16-B4</f>
+        <v>-0.06</v>
+      </c>
+      <c r="S16" s="5">
+        <f t="shared" ref="S16:S24" si="8">O16-C4</f>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="T16" s="5">
+        <f t="shared" ref="T16:T24" si="9">ABS(Q16)</f>
+        <v>0.8</v>
+      </c>
+      <c r="U16" s="5">
+        <f t="shared" si="4"/>
+        <v>0.06</v>
+      </c>
+      <c r="V16" s="5">
+        <f t="shared" si="5"/>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="W16" s="6" cm="1">
+        <f t="array" ref="W16">AVERAGE(ABS(Q19:Q24))</f>
+        <v>0.41453415637793611</v>
+      </c>
+      <c r="X16" s="6" cm="1">
+        <f t="array" ref="X16">AVERAGE(ABS(R19:R24))</f>
+        <v>7.099191217124208E-2</v>
+      </c>
+      <c r="Y16" s="6" cm="1">
+        <f t="array" ref="Y16">AVERAGE(ABS(S19:S24))</f>
+        <v>2.8823511231169847E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>0</v>
       </c>
@@ -9862,9 +10008,107 @@
       <c r="C17">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="5">
+        <f t="shared" si="6"/>
+        <v>-0.3</v>
+      </c>
+      <c r="R17" s="5">
+        <f t="shared" si="7"/>
+        <v>-0.08</v>
+      </c>
+      <c r="S17" s="5">
+        <f t="shared" si="8"/>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="T17" s="5">
+        <f t="shared" si="9"/>
+        <v>0.3</v>
+      </c>
+      <c r="U17" s="5">
+        <f t="shared" si="4"/>
+        <v>0.08</v>
+      </c>
+      <c r="V17" s="5">
+        <f t="shared" si="5"/>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="W17" s="24"/>
+      <c r="X17" s="24"/>
+      <c r="Y17" s="24"/>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="5">
+        <f t="shared" si="6"/>
+        <v>-0.5</v>
+      </c>
+      <c r="R18" s="5">
+        <f t="shared" si="7"/>
+        <v>-0.1</v>
+      </c>
+      <c r="S18" s="5">
+        <f t="shared" si="8"/>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="T18" s="5">
+        <f t="shared" si="9"/>
+        <v>0.5</v>
+      </c>
+      <c r="U18" s="5">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="V18" s="5">
+        <f t="shared" si="5"/>
+        <v>1.5707963267948966</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M19" s="5">
+        <v>0.99999999999043832</v>
+      </c>
+      <c r="N19" s="5">
+        <v>7.808914400058907E-2</v>
+      </c>
+      <c r="O19" s="5">
+        <v>1.5877229610591919</v>
+      </c>
+      <c r="P19" s="11">
+        <v>1.605636373842141E-3</v>
+      </c>
+      <c r="Q19" s="5">
+        <f t="shared" si="6"/>
+        <v>0.29999999999043836</v>
+      </c>
+      <c r="R19" s="5">
+        <f t="shared" si="7"/>
+        <v>-2.1910855999410936E-2</v>
+      </c>
+      <c r="S19" s="5">
+        <f t="shared" si="8"/>
+        <v>1.6926634264295304E-2</v>
+      </c>
+      <c r="T19" s="5">
+        <f t="shared" si="9"/>
+        <v>0.29999999999043836</v>
+      </c>
+      <c r="U19" s="5">
+        <f t="shared" si="4"/>
+        <v>2.1910855999410936E-2</v>
+      </c>
+      <c r="V19" s="5">
+        <f t="shared" si="5"/>
+        <v>1.6926634264295304E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C20" s="1" t="s">
         <v>33</v>
       </c>
@@ -9885,49 +10129,124 @@
       <c r="J20" s="18"/>
       <c r="K20" s="18"/>
       <c r="L20" s="18"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M20" s="5">
+        <v>0.9999999999915965</v>
+      </c>
+      <c r="N20" s="5">
+        <v>7.077919699991761E-2</v>
+      </c>
+      <c r="O20" s="5">
+        <v>1.6012212024620862</v>
+      </c>
+      <c r="P20" s="11">
+        <v>3.1529306909527648E-2</v>
+      </c>
+      <c r="Q20" s="5">
+        <f t="shared" si="6"/>
+        <v>0.59999999999159648</v>
+      </c>
+      <c r="R20" s="5">
+        <f t="shared" si="7"/>
+        <v>-8.9220803000082394E-2</v>
+      </c>
+      <c r="S20" s="5">
+        <f t="shared" si="8"/>
+        <v>3.0424875667189655E-2</v>
+      </c>
+      <c r="T20" s="5">
+        <f t="shared" si="9"/>
+        <v>0.59999999999159648</v>
+      </c>
+      <c r="U20" s="5">
+        <f t="shared" si="4"/>
+        <v>8.9220803000082394E-2</v>
+      </c>
+      <c r="V20" s="5">
+        <f t="shared" si="5"/>
+        <v>3.0424875667189655E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C21" s="10">
         <v>1</v>
       </c>
       <c r="D21" s="5">
-        <f t="shared" ref="D21:L21" si="3">D3</f>
+        <f t="shared" ref="D21:L21" si="10">D3</f>
         <v>0</v>
       </c>
       <c r="E21" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F21" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G21" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>-2.8477585874497901E-4</v>
       </c>
       <c r="H21" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>-5.8327373117208502E-2</v>
       </c>
       <c r="I21" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>-1.50670297443867E-4</v>
       </c>
       <c r="J21" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>6.01342367008328E-3</v>
       </c>
       <c r="K21" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>2.2609531879425001E-3</v>
       </c>
       <c r="L21" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>0.37637501955032299</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M21" s="5">
+        <v>0.99999998964751557</v>
+      </c>
+      <c r="N21" s="5">
+        <v>0.10245949158597613</v>
+      </c>
+      <c r="O21" s="5">
+        <v>1.5874469651591985</v>
+      </c>
+      <c r="P21" s="11">
+        <v>1.0466521040588268E-2</v>
+      </c>
+      <c r="Q21" s="5">
+        <f t="shared" si="6"/>
+        <v>0.3999999896475156</v>
+      </c>
+      <c r="R21" s="5">
+        <f t="shared" si="7"/>
+        <v>-5.7540508414023875E-2</v>
+      </c>
+      <c r="S21" s="5">
+        <f t="shared" si="8"/>
+        <v>1.6650638364301917E-2</v>
+      </c>
+      <c r="T21" s="5">
+        <f t="shared" si="9"/>
+        <v>0.3999999896475156</v>
+      </c>
+      <c r="U21" s="5">
+        <f t="shared" si="4"/>
+        <v>5.7540508414023875E-2</v>
+      </c>
+      <c r="V21" s="5">
+        <f t="shared" si="5"/>
+        <v>1.6650638364301917E-2</v>
+      </c>
+      <c r="W21" s="7"/>
+      <c r="X21" s="7"/>
+      <c r="Y21" s="7"/>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C22" s="10">
         <v>1</v>
       </c>
@@ -9958,8 +10277,44 @@
       <c r="L22" s="5">
         <v>0.25999218225479098</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M22" s="5">
+        <v>0.98720495998754387</v>
+      </c>
+      <c r="N22" s="5">
+        <v>0.13232949639335892</v>
+      </c>
+      <c r="O22" s="5">
+        <v>1.6046347577244562</v>
+      </c>
+      <c r="P22" s="11">
+        <v>2.5904098685380905E-4</v>
+      </c>
+      <c r="Q22" s="5">
+        <f t="shared" si="6"/>
+        <v>0.18720495998754383</v>
+      </c>
+      <c r="R22" s="5">
+        <f t="shared" si="7"/>
+        <v>-4.7670503606641074E-2</v>
+      </c>
+      <c r="S22" s="5">
+        <f t="shared" si="8"/>
+        <v>3.3838430929559626E-2</v>
+      </c>
+      <c r="T22" s="5">
+        <f t="shared" si="9"/>
+        <v>0.18720495998754383</v>
+      </c>
+      <c r="U22" s="5">
+        <f t="shared" si="4"/>
+        <v>4.7670503606641074E-2</v>
+      </c>
+      <c r="V22" s="5">
+        <f t="shared" si="5"/>
+        <v>3.3838430929559626E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C23" s="10">
         <v>1</v>
       </c>
@@ -9990,8 +10345,47 @@
       <c r="L23" s="5">
         <v>0.26262807846069303</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M23" s="5">
+        <v>0.99999999894731717</v>
+      </c>
+      <c r="N23" s="5">
+        <v>6.6227538893402368E-2</v>
+      </c>
+      <c r="O23" s="5">
+        <v>1.6100460948610689</v>
+      </c>
+      <c r="P23" s="11">
+        <v>4.9255432098804036E-2</v>
+      </c>
+      <c r="Q23" s="5">
+        <f t="shared" si="6"/>
+        <v>0.69999999894731713</v>
+      </c>
+      <c r="R23" s="5">
+        <f t="shared" si="7"/>
+        <v>-0.13377246110659763</v>
+      </c>
+      <c r="S23" s="5">
+        <f t="shared" si="8"/>
+        <v>3.9249768066172308E-2</v>
+      </c>
+      <c r="T23" s="5">
+        <f t="shared" si="9"/>
+        <v>0.69999999894731713</v>
+      </c>
+      <c r="U23" s="5">
+        <f t="shared" si="4"/>
+        <v>0.13377246110659763</v>
+      </c>
+      <c r="V23" s="5">
+        <f t="shared" si="5"/>
+        <v>3.9249768066172308E-2</v>
+      </c>
+      <c r="W23" s="7"/>
+      <c r="X23" s="7"/>
+      <c r="Y23" s="7"/>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C24" s="10">
         <v>1</v>
       </c>
@@ -10022,8 +10416,44 @@
       <c r="L24" s="5">
         <v>0.50434404611587502</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M24" s="5">
+        <v>0.99999998970320547</v>
+      </c>
+      <c r="N24" s="5">
+        <v>0.12416365909930344</v>
+      </c>
+      <c r="O24" s="5">
+        <v>1.6066470468903968</v>
+      </c>
+      <c r="P24" s="11">
+        <v>1.4596612597414639E-2</v>
+      </c>
+      <c r="Q24" s="5">
+        <f t="shared" si="6"/>
+        <v>0.29999998970320552</v>
+      </c>
+      <c r="R24" s="5">
+        <f t="shared" si="7"/>
+        <v>-7.5836340900696575E-2</v>
+      </c>
+      <c r="S24" s="5">
+        <f t="shared" si="8"/>
+        <v>3.5850720095500277E-2</v>
+      </c>
+      <c r="T24" s="5">
+        <f t="shared" si="9"/>
+        <v>0.29999998970320552</v>
+      </c>
+      <c r="U24" s="5">
+        <f t="shared" si="4"/>
+        <v>7.5836340900696575E-2</v>
+      </c>
+      <c r="V24" s="5">
+        <f t="shared" si="5"/>
+        <v>3.5850720095500277E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C25" s="10">
         <v>2</v>
       </c>
@@ -10041,27 +10471,46 @@
         <v>-1.3759520370513201E-3</v>
       </c>
       <c r="H25" s="5">
-        <f t="shared" ref="H25:L25" si="4">H4</f>
+        <f t="shared" ref="H25:L25" si="11">H4</f>
         <v>-0.12723180651664701</v>
       </c>
       <c r="I25" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>-1.5217980835586799E-3</v>
       </c>
       <c r="J25" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>-8.26666504144669E-2</v>
       </c>
       <c r="K25" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>-4.7411769628524798E-3</v>
       </c>
       <c r="L25" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>0.81632339954376198</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M25" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="N25" s="26"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="26"/>
+      <c r="Q25" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="R25" s="27"/>
+      <c r="S25" s="27"/>
+      <c r="T25" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="U25" s="30"/>
+      <c r="V25" s="30"/>
+      <c r="W25" s="28"/>
+      <c r="X25" s="28"/>
+      <c r="Y25" s="28"/>
+    </row>
+    <row r="26" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C26" s="10">
         <v>2</v>
       </c>
@@ -10092,8 +10541,43 @@
       <c r="L26" s="5">
         <v>0.72908455133438099</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M26" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="V26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W26" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="X26" s="29"/>
+      <c r="Y26" s="29"/>
+    </row>
+    <row r="27" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C27" s="10">
         <v>2</v>
       </c>
@@ -10124,8 +10608,45 @@
       <c r="L27" s="5">
         <v>0.72120183706283603</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="5">
+        <f>M27-A3</f>
+        <v>-0.4</v>
+      </c>
+      <c r="R27" s="5">
+        <f t="shared" ref="R27:S27" si="12">N27-B3</f>
+        <v>-0.06</v>
+      </c>
+      <c r="S27" s="5">
+        <f t="shared" si="12"/>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="T27" s="5">
+        <f>ABS(Q27)</f>
+        <v>0.4</v>
+      </c>
+      <c r="U27" s="5">
+        <f t="shared" ref="U27:U36" si="13">ABS(R27)</f>
+        <v>0.06</v>
+      </c>
+      <c r="V27" s="5">
+        <f t="shared" ref="V27:V36" si="14">ABS(S27)</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="W27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y27" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C28" s="10">
         <v>2</v>
       </c>
@@ -10156,8 +10677,48 @@
       <c r="L28" s="5">
         <v>0.92903923988342296</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="12"/>
+      <c r="Q28" s="5">
+        <f t="shared" ref="Q28:Q36" si="15">M28-A4</f>
+        <v>-0.8</v>
+      </c>
+      <c r="R28" s="5">
+        <f t="shared" ref="R28:R36" si="16">N28-B4</f>
+        <v>-0.06</v>
+      </c>
+      <c r="S28" s="5">
+        <f t="shared" ref="S28:S36" si="17">O28-C4</f>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="T28" s="5">
+        <f t="shared" ref="T28:T36" si="18">ABS(Q28)</f>
+        <v>0.8</v>
+      </c>
+      <c r="U28" s="5">
+        <f t="shared" si="13"/>
+        <v>0.06</v>
+      </c>
+      <c r="V28" s="5">
+        <f t="shared" si="14"/>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="W28" s="6" cm="1">
+        <f t="array" ref="W28">AVERAGE(ABS(Q31:Q36))</f>
+        <v>0.12115048439583324</v>
+      </c>
+      <c r="X28" s="6" cm="1">
+        <f t="array" ref="X28">AVERAGE(ABS(R31:R36))</f>
+        <v>3.1747039777984751E-2</v>
+      </c>
+      <c r="Y28" s="6" cm="1">
+        <f t="array" ref="Y28">AVERAGE(ABS(S31:S36))</f>
+        <v>0.12689221492525818</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C29" s="10">
         <v>3</v>
       </c>
@@ -10175,27 +10736,58 @@
         <v>-2.8428673977032298E-4</v>
       </c>
       <c r="H29" s="5">
-        <f t="shared" ref="H29:L29" si="5">H5</f>
+        <f t="shared" ref="H29:L29" si="19">H5</f>
         <v>-4.3962169438600499E-2</v>
       </c>
       <c r="I29" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="19"/>
         <v>-1.9410930690355599E-4</v>
       </c>
       <c r="J29" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="19"/>
         <v>-1.4232989400625199E-2</v>
       </c>
       <c r="K29" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="19"/>
         <v>8.0315023660659801E-4</v>
       </c>
       <c r="L29" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="19"/>
         <v>0.24872186779975899</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="11"/>
+      <c r="Q29" s="5">
+        <f t="shared" si="15"/>
+        <v>-0.3</v>
+      </c>
+      <c r="R29" s="5">
+        <f t="shared" si="16"/>
+        <v>-0.08</v>
+      </c>
+      <c r="S29" s="5">
+        <f t="shared" si="17"/>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="T29" s="5">
+        <f t="shared" si="18"/>
+        <v>0.3</v>
+      </c>
+      <c r="U29" s="5">
+        <f t="shared" si="13"/>
+        <v>0.08</v>
+      </c>
+      <c r="V29" s="5">
+        <f t="shared" si="14"/>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="W29" s="24"/>
+      <c r="X29" s="24"/>
+      <c r="Y29" s="24"/>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C30" s="10">
         <v>3</v>
       </c>
@@ -10226,8 +10818,36 @@
       <c r="L30" s="5">
         <v>0.111019782721996</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="11"/>
+      <c r="Q30" s="5">
+        <f t="shared" si="15"/>
+        <v>-0.5</v>
+      </c>
+      <c r="R30" s="5">
+        <f t="shared" si="16"/>
+        <v>-0.1</v>
+      </c>
+      <c r="S30" s="5">
+        <f t="shared" si="17"/>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="T30" s="5">
+        <f t="shared" si="18"/>
+        <v>0.5</v>
+      </c>
+      <c r="U30" s="5">
+        <f t="shared" si="13"/>
+        <v>0.1</v>
+      </c>
+      <c r="V30" s="5">
+        <f t="shared" si="14"/>
+        <v>1.5707963267948966</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C31" s="10">
         <v>3</v>
       </c>
@@ -10258,8 +10878,44 @@
       <c r="L31" s="5">
         <v>0.110123753547668</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M31" s="5">
+        <v>0.61585568404864499</v>
+      </c>
+      <c r="N31" s="5">
+        <v>0.12478348829765686</v>
+      </c>
+      <c r="O31" s="5">
+        <v>1.5402166469505407</v>
+      </c>
+      <c r="P31" s="11">
+        <v>4.6140866627988299E-17</v>
+      </c>
+      <c r="Q31" s="5">
+        <f t="shared" si="15"/>
+        <v>-8.4144315951354964E-2</v>
+      </c>
+      <c r="R31" s="5">
+        <f t="shared" si="16"/>
+        <v>2.478348829765685E-2</v>
+      </c>
+      <c r="S31" s="5">
+        <f t="shared" si="17"/>
+        <v>-3.0579679844355834E-2</v>
+      </c>
+      <c r="T31" s="5">
+        <f t="shared" si="18"/>
+        <v>8.4144315951354964E-2</v>
+      </c>
+      <c r="U31" s="5">
+        <f t="shared" si="13"/>
+        <v>2.478348829765685E-2</v>
+      </c>
+      <c r="V31" s="5">
+        <f t="shared" si="14"/>
+        <v>3.0579679844355834E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C32" s="10">
         <v>3</v>
       </c>
@@ -10290,8 +10946,44 @@
       <c r="L32" s="5">
         <v>0.41071912646293601</v>
       </c>
-    </row>
-    <row r="33" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="M32" s="5">
+        <v>0.62009833355690314</v>
+      </c>
+      <c r="N32" s="5">
+        <v>0.11348388530537551</v>
+      </c>
+      <c r="O32" s="5">
+        <v>1.4600004623528557</v>
+      </c>
+      <c r="P32" s="11">
+        <v>2.1703295963737887E-4</v>
+      </c>
+      <c r="Q32" s="5">
+        <f t="shared" si="15"/>
+        <v>0.22009833355690311</v>
+      </c>
+      <c r="R32" s="5">
+        <f t="shared" si="16"/>
+        <v>-4.6516114694624494E-2</v>
+      </c>
+      <c r="S32" s="5">
+        <f t="shared" si="17"/>
+        <v>-0.11079586444204081</v>
+      </c>
+      <c r="T32" s="5">
+        <f t="shared" si="18"/>
+        <v>0.22009833355690311</v>
+      </c>
+      <c r="U32" s="5">
+        <f t="shared" si="13"/>
+        <v>4.6516114694624494E-2</v>
+      </c>
+      <c r="V32" s="5">
+        <f t="shared" si="14"/>
+        <v>0.11079586444204081</v>
+      </c>
+    </row>
+    <row r="33" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C33" s="10">
         <v>4</v>
       </c>
@@ -10309,27 +11001,66 @@
         <v>-9.02065541595221E-4</v>
       </c>
       <c r="H33" s="5">
-        <f t="shared" ref="H33:L33" si="6">H6</f>
+        <f t="shared" ref="H33:L33" si="20">H6</f>
         <v>-9.5010705292224898E-2</v>
       </c>
       <c r="I33" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>-3.1485431827604798E-4</v>
       </c>
       <c r="J33" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>-0.14170777797699</v>
       </c>
       <c r="K33" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>3.2724365592002899E-3</v>
       </c>
       <c r="L33" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>0.46851912140846302</v>
       </c>
-    </row>
-    <row r="34" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="M33" s="5">
+        <v>0.68391317473059643</v>
+      </c>
+      <c r="N33" s="5">
+        <v>0.15381951418329837</v>
+      </c>
+      <c r="O33" s="5">
+        <v>1.439265940382809</v>
+      </c>
+      <c r="P33" s="11">
+        <v>7.9730603476053955E-18</v>
+      </c>
+      <c r="Q33" s="5">
+        <f t="shared" si="15"/>
+        <v>8.3913174730596451E-2</v>
+      </c>
+      <c r="R33" s="5">
+        <f t="shared" si="16"/>
+        <v>-6.1804858167016363E-3</v>
+      </c>
+      <c r="S33" s="5">
+        <f t="shared" si="17"/>
+        <v>-0.13153038641208759</v>
+      </c>
+      <c r="T33" s="5">
+        <f t="shared" si="18"/>
+        <v>8.3913174730596451E-2</v>
+      </c>
+      <c r="U33" s="5">
+        <f t="shared" si="13"/>
+        <v>6.1804858167016363E-3</v>
+      </c>
+      <c r="V33" s="5">
+        <f t="shared" si="14"/>
+        <v>0.13153038641208759</v>
+      </c>
+      <c r="W33" s="7"/>
+      <c r="X33" s="7"/>
+      <c r="Y33" s="7"/>
+    </row>
+    <row r="34" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C34" s="10">
         <v>4</v>
       </c>
@@ -10360,8 +11091,44 @@
       <c r="L34" s="5">
         <v>0.37433075904846203</v>
       </c>
-    </row>
-    <row r="35" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="M34" s="5">
+        <v>0.77607030962302415</v>
+      </c>
+      <c r="N34" s="5">
+        <v>0.18257272688618925</v>
+      </c>
+      <c r="O34" s="5">
+        <v>1.4140274483039532</v>
+      </c>
+      <c r="P34" s="11">
+        <v>5.2205527619378083E-25</v>
+      </c>
+      <c r="Q34" s="5">
+        <f t="shared" si="15"/>
+        <v>-2.3929690376975898E-2</v>
+      </c>
+      <c r="R34" s="5">
+        <f t="shared" si="16"/>
+        <v>2.5727268861892583E-3</v>
+      </c>
+      <c r="S34" s="5">
+        <f t="shared" si="17"/>
+        <v>-0.15676887849094334</v>
+      </c>
+      <c r="T34" s="5">
+        <f t="shared" si="18"/>
+        <v>2.3929690376975898E-2</v>
+      </c>
+      <c r="U34" s="5">
+        <f t="shared" si="13"/>
+        <v>2.5727268861892583E-3</v>
+      </c>
+      <c r="V34" s="5">
+        <f t="shared" si="14"/>
+        <v>0.15676887849094334</v>
+      </c>
+    </row>
+    <row r="35" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C35" s="10">
         <v>4</v>
       </c>
@@ -10392,8 +11159,47 @@
       <c r="L35" s="5">
         <v>0.37116280198097201</v>
       </c>
-    </row>
-    <row r="36" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="M35" s="5">
+        <v>0.56013196807389265</v>
+      </c>
+      <c r="N35" s="5">
+        <v>0.11354057192350756</v>
+      </c>
+      <c r="O35" s="5">
+        <v>1.4388737273319911</v>
+      </c>
+      <c r="P35" s="11">
+        <v>8.156006566467007E-5</v>
+      </c>
+      <c r="Q35" s="5">
+        <f t="shared" si="15"/>
+        <v>0.26013196807389266</v>
+      </c>
+      <c r="R35" s="5">
+        <f t="shared" si="16"/>
+        <v>-8.6459428076492456E-2</v>
+      </c>
+      <c r="S35" s="5">
+        <f t="shared" si="17"/>
+        <v>-0.13192259946290541</v>
+      </c>
+      <c r="T35" s="5">
+        <f t="shared" si="18"/>
+        <v>0.26013196807389266</v>
+      </c>
+      <c r="U35" s="5">
+        <f t="shared" si="13"/>
+        <v>8.6459428076492456E-2</v>
+      </c>
+      <c r="V35" s="5">
+        <f t="shared" si="14"/>
+        <v>0.13192259946290541</v>
+      </c>
+      <c r="W35" s="7"/>
+      <c r="X35" s="7"/>
+      <c r="Y35" s="7"/>
+    </row>
+    <row r="36" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C36" s="10">
         <v>4</v>
       </c>
@@ -10424,8 +11230,44 @@
       <c r="L36" s="5">
         <v>0.58599090576171897</v>
       </c>
-    </row>
-    <row r="37" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="M36" s="5">
+        <v>0.75468542368527625</v>
+      </c>
+      <c r="N36" s="5">
+        <v>0.17603000510375619</v>
+      </c>
+      <c r="O36" s="5">
+        <v>1.3710404458956804</v>
+      </c>
+      <c r="P36" s="11">
+        <v>4.1298489952310973E-21</v>
+      </c>
+      <c r="Q36" s="5">
+        <f t="shared" si="15"/>
+        <v>5.4685423685276291E-2</v>
+      </c>
+      <c r="R36" s="5">
+        <f t="shared" si="16"/>
+        <v>-2.3969994896243824E-2</v>
+      </c>
+      <c r="S36" s="5">
+        <f t="shared" si="17"/>
+        <v>-0.19975588089921614</v>
+      </c>
+      <c r="T36" s="5">
+        <f t="shared" si="18"/>
+        <v>5.4685423685276291E-2</v>
+      </c>
+      <c r="U36" s="5">
+        <f t="shared" si="13"/>
+        <v>2.3969994896243824E-2</v>
+      </c>
+      <c r="V36" s="5">
+        <f t="shared" si="14"/>
+        <v>0.19975588089921614</v>
+      </c>
+    </row>
+    <row r="37" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C37" s="10">
         <v>5</v>
       </c>
@@ -10443,27 +11285,27 @@
         <v>-1.3697715476155301E-3</v>
       </c>
       <c r="H37" s="5">
-        <f t="shared" ref="H37:L37" si="7">H7</f>
+        <f t="shared" ref="H37:L37" si="21">H7</f>
         <v>-0.129899337887764</v>
       </c>
       <c r="I37" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="21"/>
         <v>-1.1154995299875699E-3</v>
       </c>
       <c r="J37" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="21"/>
         <v>-0.27736902236938499</v>
       </c>
       <c r="K37" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="21"/>
         <v>2.9984340071678201E-3</v>
       </c>
       <c r="L37" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="21"/>
         <v>0.62586665153503396</v>
       </c>
     </row>
-    <row r="38" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C38" s="10">
         <v>5</v>
       </c>
@@ -10495,7 +11337,7 @@
         <v>0.52928400039672896</v>
       </c>
     </row>
-    <row r="39" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C39" s="10">
         <v>5</v>
       </c>
@@ -10527,7 +11369,7 @@
         <v>0.52430135011672996</v>
       </c>
     </row>
-    <row r="40" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C40" s="10">
         <v>5</v>
       </c>
@@ -10559,7 +11401,7 @@
         <v>0.72825366258621205</v>
       </c>
     </row>
-    <row r="41" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C41" s="10">
         <v>6</v>
       </c>
@@ -10577,27 +11419,27 @@
         <v>-1.30162085406482E-3</v>
       </c>
       <c r="H41" s="5">
-        <f t="shared" ref="H41:L41" si="8">H8</f>
+        <f t="shared" ref="H41:L41" si="22">H8</f>
         <v>-9.1771319508552607E-2</v>
       </c>
       <c r="I41" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="22"/>
         <v>-6.8558257771655895E-4</v>
       </c>
       <c r="J41" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="22"/>
         <v>-0.188138782978058</v>
       </c>
       <c r="K41" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="22"/>
         <v>3.5599116235971499E-3</v>
       </c>
       <c r="L41" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="22"/>
         <v>0.316497713327408</v>
       </c>
     </row>
-    <row r="42" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C42" s="10">
         <v>6</v>
       </c>
@@ -10629,7 +11471,7 @@
         <v>0.25275784730911299</v>
       </c>
     </row>
-    <row r="43" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C43" s="10">
         <v>6</v>
       </c>
@@ -10661,7 +11503,7 @@
         <v>0.25089681148529103</v>
       </c>
     </row>
-    <row r="44" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C44" s="10">
         <v>6</v>
       </c>
@@ -10693,7 +11535,7 @@
         <v>0.38772404193878202</v>
       </c>
     </row>
-    <row r="45" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C45" s="10">
         <v>7</v>
       </c>
@@ -10711,27 +11553,27 @@
         <v>-2.1819151006638999E-3</v>
       </c>
       <c r="H45" s="5">
-        <f t="shared" ref="H45:L45" si="9">H9</f>
+        <f t="shared" ref="H45:L45" si="23">H9</f>
         <v>-0.134275212883949</v>
       </c>
       <c r="I45" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="23"/>
         <v>-2.8121363720856602E-4</v>
       </c>
       <c r="J45" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="23"/>
         <v>-0.47822567820549</v>
       </c>
       <c r="K45" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="23"/>
         <v>1.2040870264172601E-2</v>
       </c>
       <c r="L45" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="23"/>
         <v>0.39143002033233598</v>
       </c>
     </row>
-    <row r="46" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C46" s="10">
         <v>7</v>
       </c>
@@ -10763,7 +11605,7 @@
         <v>0.342921882867813</v>
       </c>
     </row>
-    <row r="47" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C47" s="10">
         <v>7</v>
       </c>
@@ -10795,7 +11637,7 @@
         <v>0.33994320034980802</v>
       </c>
     </row>
-    <row r="48" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C48" s="10">
         <v>7</v>
       </c>
@@ -10845,23 +11687,23 @@
         <v>-1.05854228604585E-3</v>
       </c>
       <c r="H49" s="5">
-        <f t="shared" ref="H49:L49" si="10">H10</f>
+        <f t="shared" ref="H49:L49" si="24">H10</f>
         <v>-0.13548035919666301</v>
       </c>
       <c r="I49" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="24"/>
         <v>-1.24974839854985E-3</v>
       </c>
       <c r="J49" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="24"/>
         <v>-0.72550737857818604</v>
       </c>
       <c r="K49" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="24"/>
         <v>2.9684353619813902E-2</v>
       </c>
       <c r="L49" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="24"/>
         <v>0.13168570399284399</v>
       </c>
     </row>
@@ -10979,23 +11821,23 @@
         <v>-8.8630802929401398E-4</v>
       </c>
       <c r="H53" s="5">
-        <f t="shared" ref="H53:L53" si="11">H11</f>
+        <f t="shared" ref="H53:L53" si="25">H11</f>
         <v>-6.7533724009990706E-2</v>
       </c>
       <c r="I53" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v>-4.7554963384754999E-4</v>
       </c>
       <c r="J53" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v>-0.16650235652923601</v>
       </c>
       <c r="K53" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v>2.7373749762773501E-3</v>
       </c>
       <c r="L53" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v>0.18086977303028101</v>
       </c>
     </row>
@@ -11113,23 +11955,23 @@
         <v>-2.7598871383815999E-3</v>
       </c>
       <c r="H57" s="5">
-        <f t="shared" ref="H57:L57" si="12">H12</f>
+        <f t="shared" ref="H57:L57" si="26">H12</f>
         <v>-0.127221524715424</v>
       </c>
       <c r="I57" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="26"/>
         <v>-8.8058260735124404E-4</v>
       </c>
       <c r="J57" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="26"/>
         <v>-0.67187190055847201</v>
       </c>
       <c r="K57" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="26"/>
         <v>1.79205909371376E-2</v>
       </c>
       <c r="L57" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="26"/>
         <v>6.6542282700538594E-2</v>
       </c>
     </row>
@@ -11230,7 +12072,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="22">
+    <mergeCell ref="W29:Y29"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="T25:V25"/>
+    <mergeCell ref="W25:Y25"/>
+    <mergeCell ref="W26:Y26"/>
     <mergeCell ref="W5:Y5"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="G20:L20"/>
@@ -11241,6 +12089,12 @@
     <mergeCell ref="W1:Y1"/>
     <mergeCell ref="W2:Y2"/>
     <mergeCell ref="T1:V1"/>
+    <mergeCell ref="M13:P13"/>
+    <mergeCell ref="Q13:S13"/>
+    <mergeCell ref="T13:V13"/>
+    <mergeCell ref="W13:Y13"/>
+    <mergeCell ref="W14:Y14"/>
+    <mergeCell ref="W17:Y17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -18344,15 +19198,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E12580AD17ADB64691A1BA4C2E042DA4" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6532fc6a52f3455fe895a4f720bca71c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xmlns:ns4="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d9a2f75daf18a7097de825f86ff3fec6" ns3:_="" ns4:_="">
     <xsd:import namespace="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
@@ -18605,6 +19450,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -18614,14 +19468,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65923CC5-95C4-4597-AADE-A0DCE38786F0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18636,6 +19482,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Raw Data/single force (10 trials)(perturbed)/Validation(1.5)(3tendon).xlsx
+++ b/Raw Data/single force (10 trials)(perturbed)/Validation(1.5)(3tendon).xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/Raw Data/single force (10 trials)(perturbed)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4422" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{414E18F2-5071-4197-8667-78D0192BCB1F}"/>
+  <xr:revisionPtr revIDLastSave="4428" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B12FD8B5-FF71-4148-BC86-6916C5D9D8B7}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Proximal Validation" sheetId="12" r:id="rId1"/>
     <sheet name="Distal Vali (0N perturb)" sheetId="37" r:id="rId2"/>
-    <sheet name="Distal Vali (0.5N perturb)" sheetId="19" r:id="rId3"/>
-    <sheet name="Distal Vali (1N perturb)" sheetId="38" r:id="rId4"/>
-    <sheet name="Distal Vali (1.5N perturb)" sheetId="39" r:id="rId5"/>
-    <sheet name="Conversion" sheetId="4" r:id="rId6"/>
-    <sheet name="Sheet5" sheetId="36" r:id="rId7"/>
+    <sheet name="Distal Vali (0N pert 6 prox)" sheetId="40" r:id="rId3"/>
+    <sheet name="Distal Vali (0.5N perturb)" sheetId="19" r:id="rId4"/>
+    <sheet name="Distal Vali (1N perturb)" sheetId="38" r:id="rId5"/>
+    <sheet name="Distal Vali (1.5N perturb)" sheetId="39" r:id="rId6"/>
+    <sheet name="Conversion" sheetId="4" r:id="rId7"/>
+    <sheet name="Sheet5" sheetId="36" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="46">
   <si>
     <t>Fx (N)</t>
   </si>
@@ -2898,6 +2899,1014 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0776D563-8DBD-45DC-BF52-C964ADBADB98}">
+  <dimension ref="A1:Y12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+    </row>
+    <row r="2" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W2" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="X2" s="29"/>
+      <c r="Y2" s="29"/>
+    </row>
+    <row r="3" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <f>'Proximal Validation'!A3</f>
+        <v>0.4</v>
+      </c>
+      <c r="B3" s="5">
+        <f>'Proximal Validation'!B3</f>
+        <v>0.06</v>
+      </c>
+      <c r="C3" s="5">
+        <f>'Proximal Validation'!C3</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="D3" s="5">
+        <f>'Proximal Validation'!D3</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="5">
+        <f>'Proximal Validation'!E3</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <f>'Proximal Validation'!F3</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <f>'Proximal Validation'!G3</f>
+        <v>-2.8477585874497901E-4</v>
+      </c>
+      <c r="H3" s="5">
+        <f>'Proximal Validation'!H3</f>
+        <v>-5.8327373117208502E-2</v>
+      </c>
+      <c r="I3" s="5">
+        <f>'Proximal Validation'!I3</f>
+        <v>-1.50670297443867E-4</v>
+      </c>
+      <c r="J3" s="5">
+        <f>'Proximal Validation'!J3</f>
+        <v>6.01342367008328E-3</v>
+      </c>
+      <c r="K3" s="5">
+        <f>'Proximal Validation'!K3</f>
+        <v>2.2609531879425001E-3</v>
+      </c>
+      <c r="L3" s="5">
+        <f>'Proximal Validation'!L3</f>
+        <v>0.37637501955032299</v>
+      </c>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="5">
+        <f>M3-A3</f>
+        <v>-0.4</v>
+      </c>
+      <c r="R3" s="5">
+        <f>N3-B3</f>
+        <v>-0.06</v>
+      </c>
+      <c r="S3" s="5">
+        <f>O3-C3</f>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="T3" s="5">
+        <f>ABS(Q3)</f>
+        <v>0.4</v>
+      </c>
+      <c r="U3" s="5">
+        <f t="shared" ref="U3:V12" si="0">ABS(R3)</f>
+        <v>0.06</v>
+      </c>
+      <c r="V3" s="5">
+        <f t="shared" si="0"/>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <f>'Proximal Validation'!A4</f>
+        <v>0.8</v>
+      </c>
+      <c r="B4" s="8">
+        <f>'Proximal Validation'!B4</f>
+        <v>0.06</v>
+      </c>
+      <c r="C4" s="8">
+        <f>'Proximal Validation'!C4</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="D4" s="8">
+        <f>'Proximal Validation'!D4</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="8">
+        <f>'Proximal Validation'!E4</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="8">
+        <f>'Proximal Validation'!F4</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8">
+        <f>'Proximal Validation'!G4</f>
+        <v>-1.3759520370513201E-3</v>
+      </c>
+      <c r="H4" s="8">
+        <f>'Proximal Validation'!H4</f>
+        <v>-0.12723180651664701</v>
+      </c>
+      <c r="I4" s="8">
+        <f>'Proximal Validation'!I4</f>
+        <v>-1.5217980835586799E-3</v>
+      </c>
+      <c r="J4" s="8">
+        <f>'Proximal Validation'!J4</f>
+        <v>-8.26666504144669E-2</v>
+      </c>
+      <c r="K4" s="8">
+        <f>'Proximal Validation'!K4</f>
+        <v>-4.7411769628524798E-3</v>
+      </c>
+      <c r="L4" s="8">
+        <f>'Proximal Validation'!L4</f>
+        <v>0.81632339954376198</v>
+      </c>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="5">
+        <f t="shared" ref="Q4:S12" si="1">M4-A4</f>
+        <v>-0.8</v>
+      </c>
+      <c r="R4" s="5">
+        <f t="shared" si="1"/>
+        <v>-0.06</v>
+      </c>
+      <c r="S4" s="5">
+        <f t="shared" si="1"/>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="T4" s="5">
+        <f t="shared" ref="T4:T12" si="2">ABS(Q4)</f>
+        <v>0.8</v>
+      </c>
+      <c r="U4" s="5">
+        <f t="shared" si="0"/>
+        <v>0.06</v>
+      </c>
+      <c r="V4" s="5">
+        <f t="shared" si="0"/>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="W4" s="6" cm="1">
+        <f t="array" ref="W4">AVERAGE(ABS(Q7:Q12))</f>
+        <v>3.1730969846375578E-2</v>
+      </c>
+      <c r="X4" s="6" cm="1">
+        <f t="array" ref="X4">AVERAGE(ABS(R7:R12))</f>
+        <v>9.7509644761511281E-3</v>
+      </c>
+      <c r="Y4" s="6" cm="1">
+        <f t="array" ref="Y4">AVERAGE(ABS(S7:S12))</f>
+        <v>1.3980338325821351E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <f>'Proximal Validation'!A5</f>
+        <v>0.3</v>
+      </c>
+      <c r="B5" s="5">
+        <f>'Proximal Validation'!B5</f>
+        <v>0.08</v>
+      </c>
+      <c r="C5" s="5">
+        <f>'Proximal Validation'!C5</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="D5" s="5">
+        <f>'Proximal Validation'!D5</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <f>'Proximal Validation'!E5</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <f>'Proximal Validation'!F5</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <f>'Proximal Validation'!G5</f>
+        <v>-2.8428673977032298E-4</v>
+      </c>
+      <c r="H5" s="5">
+        <f>'Proximal Validation'!H5</f>
+        <v>-4.3962169438600499E-2</v>
+      </c>
+      <c r="I5" s="5">
+        <f>'Proximal Validation'!I5</f>
+        <v>-1.9410930690355599E-4</v>
+      </c>
+      <c r="J5" s="5">
+        <f>'Proximal Validation'!J5</f>
+        <v>-1.4232989400625199E-2</v>
+      </c>
+      <c r="K5" s="5">
+        <f>'Proximal Validation'!K5</f>
+        <v>8.0315023660659801E-4</v>
+      </c>
+      <c r="L5" s="5">
+        <f>'Proximal Validation'!L5</f>
+        <v>0.24872186779975899</v>
+      </c>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="5">
+        <f t="shared" si="1"/>
+        <v>-0.3</v>
+      </c>
+      <c r="R5" s="5">
+        <f t="shared" si="1"/>
+        <v>-0.08</v>
+      </c>
+      <c r="S5" s="5">
+        <f t="shared" si="1"/>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="T5" s="5">
+        <f t="shared" si="2"/>
+        <v>0.3</v>
+      </c>
+      <c r="U5" s="5">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+      <c r="V5" s="5">
+        <f t="shared" si="0"/>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="W5" s="24"/>
+      <c r="X5" s="24"/>
+      <c r="Y5" s="24"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <f>'Proximal Validation'!A6</f>
+        <v>0.5</v>
+      </c>
+      <c r="B6" s="5">
+        <f>'Proximal Validation'!B6</f>
+        <v>0.1</v>
+      </c>
+      <c r="C6" s="5">
+        <f>'Proximal Validation'!C6</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="D6" s="5">
+        <f>'Proximal Validation'!D6</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <f>'Proximal Validation'!E6</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <f>'Proximal Validation'!F6</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <f>'Proximal Validation'!G6</f>
+        <v>-9.02065541595221E-4</v>
+      </c>
+      <c r="H6" s="5">
+        <f>'Proximal Validation'!H6</f>
+        <v>-9.5010705292224898E-2</v>
+      </c>
+      <c r="I6" s="5">
+        <f>'Proximal Validation'!I6</f>
+        <v>-3.1485431827604798E-4</v>
+      </c>
+      <c r="J6" s="5">
+        <f>'Proximal Validation'!J6</f>
+        <v>-0.14170777797699</v>
+      </c>
+      <c r="K6" s="5">
+        <f>'Proximal Validation'!K6</f>
+        <v>3.2724365592002899E-3</v>
+      </c>
+      <c r="L6" s="5">
+        <f>'Proximal Validation'!L6</f>
+        <v>0.46851912140846302</v>
+      </c>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="5">
+        <f t="shared" si="1"/>
+        <v>-0.5</v>
+      </c>
+      <c r="R6" s="5">
+        <f t="shared" si="1"/>
+        <v>-0.1</v>
+      </c>
+      <c r="S6" s="5">
+        <f t="shared" si="1"/>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="T6" s="5">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="U6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="V6" s="5">
+        <f t="shared" si="0"/>
+        <v>1.5707963267948966</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <f>'Proximal Validation'!A7</f>
+        <v>0.7</v>
+      </c>
+      <c r="B7" s="5">
+        <f>'Proximal Validation'!B7</f>
+        <v>0.1</v>
+      </c>
+      <c r="C7" s="5">
+        <f>'Proximal Validation'!C7</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="D7" s="5">
+        <f>'Proximal Validation'!D7</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <f>'Proximal Validation'!E7</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <f>'Proximal Validation'!F7</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <f>'Proximal Validation'!G7</f>
+        <v>-1.3697715476155301E-3</v>
+      </c>
+      <c r="H7" s="5">
+        <f>'Proximal Validation'!H7</f>
+        <v>-0.129899337887764</v>
+      </c>
+      <c r="I7" s="5">
+        <f>'Proximal Validation'!I7</f>
+        <v>-1.1154995299875699E-3</v>
+      </c>
+      <c r="J7" s="5">
+        <f>'Proximal Validation'!J7</f>
+        <v>-0.27736902236938499</v>
+      </c>
+      <c r="K7" s="5">
+        <f>'Proximal Validation'!K7</f>
+        <v>2.9984340071678201E-3</v>
+      </c>
+      <c r="L7" s="5">
+        <f>'Proximal Validation'!L7</f>
+        <v>0.62586665153503396</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0.68118702694274647</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0.11069439685610816</v>
+      </c>
+      <c r="O7" s="5">
+        <v>1.5797576119086036</v>
+      </c>
+      <c r="P7" s="11">
+        <v>4.1736092682460039E-4</v>
+      </c>
+      <c r="Q7" s="5">
+        <f t="shared" si="1"/>
+        <v>-1.881297305725349E-2</v>
+      </c>
+      <c r="R7" s="5">
+        <f t="shared" si="1"/>
+        <v>1.0694396856108151E-2</v>
+      </c>
+      <c r="S7" s="5">
+        <f t="shared" si="1"/>
+        <v>8.9612851137070848E-3</v>
+      </c>
+      <c r="T7" s="5">
+        <f t="shared" si="2"/>
+        <v>1.881297305725349E-2</v>
+      </c>
+      <c r="U7" s="5">
+        <f t="shared" si="0"/>
+        <v>1.0694396856108151E-2</v>
+      </c>
+      <c r="V7" s="5">
+        <f t="shared" si="0"/>
+        <v>8.9612851137070848E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <f>'Proximal Validation'!A8</f>
+        <v>0.4</v>
+      </c>
+      <c r="B8" s="5">
+        <f>'Proximal Validation'!B8</f>
+        <v>0.16</v>
+      </c>
+      <c r="C8" s="5">
+        <f>'Proximal Validation'!C8</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="D8" s="5">
+        <f>'Proximal Validation'!D8</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <f>'Proximal Validation'!E8</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <f>'Proximal Validation'!F8</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <f>'Proximal Validation'!G8</f>
+        <v>-1.30162085406482E-3</v>
+      </c>
+      <c r="H8" s="5">
+        <f>'Proximal Validation'!H8</f>
+        <v>-9.1771319508552607E-2</v>
+      </c>
+      <c r="I8" s="5">
+        <f>'Proximal Validation'!I8</f>
+        <v>-6.8558257771655895E-4</v>
+      </c>
+      <c r="J8" s="5">
+        <f>'Proximal Validation'!J8</f>
+        <v>-0.188138782978058</v>
+      </c>
+      <c r="K8" s="5">
+        <f>'Proximal Validation'!K8</f>
+        <v>3.5599116235971499E-3</v>
+      </c>
+      <c r="L8" s="5">
+        <f>'Proximal Validation'!L8</f>
+        <v>0.316497713327408</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0.37093282497834851</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0.17455942719844422</v>
+      </c>
+      <c r="O8" s="5">
+        <v>1.5812390407904158</v>
+      </c>
+      <c r="P8" s="11">
+        <v>2.6759736791444582E-4</v>
+      </c>
+      <c r="Q8" s="5">
+        <f t="shared" si="1"/>
+        <v>-2.9067175021651515E-2</v>
+      </c>
+      <c r="R8" s="5">
+        <f t="shared" si="1"/>
+        <v>1.4559427198444219E-2</v>
+      </c>
+      <c r="S8" s="5">
+        <f t="shared" si="1"/>
+        <v>1.0442713995519215E-2</v>
+      </c>
+      <c r="T8" s="5">
+        <f t="shared" si="2"/>
+        <v>2.9067175021651515E-2</v>
+      </c>
+      <c r="U8" s="5">
+        <f t="shared" si="0"/>
+        <v>1.4559427198444219E-2</v>
+      </c>
+      <c r="V8" s="5">
+        <f t="shared" si="0"/>
+        <v>1.0442713995519215E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <f>'Proximal Validation'!A9</f>
+        <v>0.6</v>
+      </c>
+      <c r="B9" s="5">
+        <f>'Proximal Validation'!B9</f>
+        <v>0.16</v>
+      </c>
+      <c r="C9" s="5">
+        <f>'Proximal Validation'!C9</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="D9" s="5">
+        <f>'Proximal Validation'!D9</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="5">
+        <f>'Proximal Validation'!E9</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <f>'Proximal Validation'!F9</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <f>'Proximal Validation'!G9</f>
+        <v>-2.1819151006638999E-3</v>
+      </c>
+      <c r="H9" s="5">
+        <f>'Proximal Validation'!H9</f>
+        <v>-0.134275212883949</v>
+      </c>
+      <c r="I9" s="5">
+        <f>'Proximal Validation'!I9</f>
+        <v>-2.8121363720856602E-4</v>
+      </c>
+      <c r="J9" s="5">
+        <f>'Proximal Validation'!J9</f>
+        <v>-0.47822567820549</v>
+      </c>
+      <c r="K9" s="5">
+        <f>'Proximal Validation'!K9</f>
+        <v>1.2040870264172601E-2</v>
+      </c>
+      <c r="L9" s="5">
+        <f>'Proximal Validation'!L9</f>
+        <v>0.39143002033233598</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0.61813795433225582</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0.17325196279387556</v>
+      </c>
+      <c r="O9" s="5">
+        <v>1.5785590974767594</v>
+      </c>
+      <c r="P9" s="11">
+        <v>7.3911050691437958E-4</v>
+      </c>
+      <c r="Q9" s="5">
+        <f t="shared" si="1"/>
+        <v>1.8137954332255846E-2</v>
+      </c>
+      <c r="R9" s="5">
+        <f t="shared" si="1"/>
+        <v>1.3251962793875555E-2</v>
+      </c>
+      <c r="S9" s="5">
+        <f t="shared" si="1"/>
+        <v>7.7627706818628184E-3</v>
+      </c>
+      <c r="T9" s="5">
+        <f t="shared" si="2"/>
+        <v>1.8137954332255846E-2</v>
+      </c>
+      <c r="U9" s="5">
+        <f t="shared" si="0"/>
+        <v>1.3251962793875555E-2</v>
+      </c>
+      <c r="V9" s="5">
+        <f t="shared" si="0"/>
+        <v>7.7627706818628184E-3</v>
+      </c>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <f>'Proximal Validation'!A10</f>
+        <v>0.8</v>
+      </c>
+      <c r="B10" s="5">
+        <f>'Proximal Validation'!B10</f>
+        <v>0.18</v>
+      </c>
+      <c r="C10" s="5">
+        <f>'Proximal Validation'!C10</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="D10" s="5">
+        <f>'Proximal Validation'!D10</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <f>'Proximal Validation'!E10</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <f>'Proximal Validation'!F10</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <f>'Proximal Validation'!G10</f>
+        <v>-1.05854228604585E-3</v>
+      </c>
+      <c r="H10" s="5">
+        <f>'Proximal Validation'!H10</f>
+        <v>-0.13548035919666301</v>
+      </c>
+      <c r="I10" s="5">
+        <f>'Proximal Validation'!I10</f>
+        <v>-1.24974839854985E-3</v>
+      </c>
+      <c r="J10" s="5">
+        <f>'Proximal Validation'!J10</f>
+        <v>-0.72550737857818604</v>
+      </c>
+      <c r="K10" s="5">
+        <f>'Proximal Validation'!K10</f>
+        <v>2.9684353619813902E-2</v>
+      </c>
+      <c r="L10" s="5">
+        <f>'Proximal Validation'!L10</f>
+        <v>0.13168570399284399</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0.76314101264820078</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0.1999999999999775</v>
+      </c>
+      <c r="O10" s="5">
+        <v>1.5990499161137131</v>
+      </c>
+      <c r="P10" s="11">
+        <v>2.4474851507129106E-3</v>
+      </c>
+      <c r="Q10" s="5">
+        <f t="shared" si="1"/>
+        <v>-3.6858987351799266E-2</v>
+      </c>
+      <c r="R10" s="5">
+        <f t="shared" si="1"/>
+        <v>1.9999999999977508E-2</v>
+      </c>
+      <c r="S10" s="5">
+        <f t="shared" si="1"/>
+        <v>2.8253589318816497E-2</v>
+      </c>
+      <c r="T10" s="5">
+        <f t="shared" si="2"/>
+        <v>3.6858987351799266E-2</v>
+      </c>
+      <c r="U10" s="5">
+        <f t="shared" si="0"/>
+        <v>1.9999999999977508E-2</v>
+      </c>
+      <c r="V10" s="5">
+        <f t="shared" si="0"/>
+        <v>2.8253589318816497E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <f>'Proximal Validation'!A11</f>
+        <v>0.3</v>
+      </c>
+      <c r="B11" s="5">
+        <f>'Proximal Validation'!B11</f>
+        <v>0.2</v>
+      </c>
+      <c r="C11" s="5">
+        <f>'Proximal Validation'!C11</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="D11" s="5">
+        <f>'Proximal Validation'!D11</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <f>'Proximal Validation'!E11</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <f>'Proximal Validation'!F11</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <f>'Proximal Validation'!G11</f>
+        <v>-8.8630802929401398E-4</v>
+      </c>
+      <c r="H11" s="5">
+        <f>'Proximal Validation'!H11</f>
+        <v>-6.7533724009990706E-2</v>
+      </c>
+      <c r="I11" s="5">
+        <f>'Proximal Validation'!I11</f>
+        <v>-4.7554963384754999E-4</v>
+      </c>
+      <c r="J11" s="5">
+        <f>'Proximal Validation'!J11</f>
+        <v>-0.16650235652923601</v>
+      </c>
+      <c r="K11" s="5">
+        <f>'Proximal Validation'!K11</f>
+        <v>2.7373749762773501E-3</v>
+      </c>
+      <c r="L11" s="5">
+        <f>'Proximal Validation'!L11</f>
+        <v>0.18086977303028101</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0.26631059051539396</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0.19999999999170265</v>
+      </c>
+      <c r="O11" s="5">
+        <v>1.5808428498536367</v>
+      </c>
+      <c r="P11" s="11">
+        <v>4.3007979121243338E-3</v>
+      </c>
+      <c r="Q11" s="5">
+        <f t="shared" si="1"/>
+        <v>-3.3689409484606025E-2</v>
+      </c>
+      <c r="R11" s="5">
+        <f t="shared" si="1"/>
+        <v>-8.2973627968385699E-12</v>
+      </c>
+      <c r="S11" s="5">
+        <f t="shared" si="1"/>
+        <v>1.0046523058740098E-2</v>
+      </c>
+      <c r="T11" s="5">
+        <f t="shared" si="2"/>
+        <v>3.3689409484606025E-2</v>
+      </c>
+      <c r="U11" s="5">
+        <f t="shared" si="0"/>
+        <v>8.2973627968385699E-12</v>
+      </c>
+      <c r="V11" s="5">
+        <f t="shared" si="0"/>
+        <v>1.0046523058740098E-2</v>
+      </c>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <f>'Proximal Validation'!A12</f>
+        <v>0.7</v>
+      </c>
+      <c r="B12" s="5">
+        <f>'Proximal Validation'!B12</f>
+        <v>0.2</v>
+      </c>
+      <c r="C12" s="5">
+        <f>'Proximal Validation'!C12</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="D12" s="5">
+        <f>'Proximal Validation'!D12</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <f>'Proximal Validation'!E12</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <f>'Proximal Validation'!F12</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <f>'Proximal Validation'!G12</f>
+        <v>-2.7598871383815999E-3</v>
+      </c>
+      <c r="H12" s="5">
+        <f>'Proximal Validation'!H12</f>
+        <v>-0.127221524715424</v>
+      </c>
+      <c r="I12" s="5">
+        <f>'Proximal Validation'!I12</f>
+        <v>-8.8058260735124404E-4</v>
+      </c>
+      <c r="J12" s="5">
+        <f>'Proximal Validation'!J12</f>
+        <v>-0.67187190055847201</v>
+      </c>
+      <c r="K12" s="5">
+        <f>'Proximal Validation'!K12</f>
+        <v>1.79205909371376E-2</v>
+      </c>
+      <c r="L12" s="5">
+        <f>'Proximal Validation'!L12</f>
+        <v>6.6542282700538594E-2</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0.75381931983068728</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0.19999999999979604</v>
+      </c>
+      <c r="O12" s="5">
+        <v>1.589211474581179</v>
+      </c>
+      <c r="P12" s="11">
+        <v>1.5559916060650748E-2</v>
+      </c>
+      <c r="Q12" s="5">
+        <f t="shared" si="1"/>
+        <v>5.3819319830687329E-2</v>
+      </c>
+      <c r="R12" s="5">
+        <f t="shared" si="1"/>
+        <v>-2.0397572519925689E-13</v>
+      </c>
+      <c r="S12" s="5">
+        <f t="shared" si="1"/>
+        <v>1.8415147786282393E-2</v>
+      </c>
+      <c r="T12" s="5">
+        <f t="shared" si="2"/>
+        <v>5.3819319830687329E-2</v>
+      </c>
+      <c r="U12" s="5">
+        <f t="shared" si="0"/>
+        <v>2.0397572519925689E-13</v>
+      </c>
+      <c r="V12" s="5">
+        <f t="shared" si="0"/>
+        <v>1.8415147786282393E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="W5:Y5"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="T1:V1"/>
+    <mergeCell ref="W1:Y1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309BE333-3BAE-4E8D-AF02-67A9E2013036}">
   <dimension ref="A1:Y60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5354,7 +6363,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EAE0736-1722-4350-9DE0-8A911956EF0F}">
   <dimension ref="A1:AY61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8818,6 +9827,15 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="AW3:AY3"/>
+    <mergeCell ref="AW6:AY6"/>
+    <mergeCell ref="AA1:AY1"/>
+    <mergeCell ref="AA2:AF2"/>
+    <mergeCell ref="AG2:AL2"/>
+    <mergeCell ref="AM2:AP2"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AW2:AY2"/>
     <mergeCell ref="A1:Y1"/>
     <mergeCell ref="W6:Y6"/>
     <mergeCell ref="A15:C15"/>
@@ -8829,22 +9847,13 @@
     <mergeCell ref="W2:Y2"/>
     <mergeCell ref="W3:Y3"/>
     <mergeCell ref="T2:V2"/>
-    <mergeCell ref="AW3:AY3"/>
-    <mergeCell ref="AW6:AY6"/>
-    <mergeCell ref="AA1:AY1"/>
-    <mergeCell ref="AA2:AF2"/>
-    <mergeCell ref="AG2:AL2"/>
-    <mergeCell ref="AM2:AP2"/>
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AW2:AY2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F05555DD-E413-4EEB-B18C-66E0D2A3A5AE}">
   <dimension ref="A1:Y60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12073,12 +13082,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="W29:Y29"/>
-    <mergeCell ref="M25:P25"/>
-    <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="T25:V25"/>
-    <mergeCell ref="W25:Y25"/>
-    <mergeCell ref="W26:Y26"/>
     <mergeCell ref="W5:Y5"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="G20:L20"/>
@@ -12095,13 +13098,19 @@
     <mergeCell ref="W13:Y13"/>
     <mergeCell ref="W14:Y14"/>
     <mergeCell ref="W17:Y17"/>
+    <mergeCell ref="W29:Y29"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="T25:V25"/>
+    <mergeCell ref="W25:Y25"/>
+    <mergeCell ref="W26:Y26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048D6981-73D2-4F8C-88D7-D5FA77AC2EB0}">
   <dimension ref="A1:M62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14595,7 +15604,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2AD273E-DEC3-4584-9987-9255339758ED}">
   <dimension ref="A3:AW80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -19198,6 +20207,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E12580AD17ADB64691A1BA4C2E042DA4" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6532fc6a52f3455fe895a4f720bca71c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xmlns:ns4="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d9a2f75daf18a7097de825f86ff3fec6" ns3:_="" ns4:_="">
     <xsd:import namespace="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
@@ -19450,24 +20476,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65923CC5-95C4-4597-AADE-A0DCE38786F0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19484,29 +20518,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>